--- a/database/event/7485/event_7485_evp_summary.xlsx
+++ b/database/event/7485/event_7485_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -508,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.246</v>
+        <v>9.3149</v>
       </c>
       <c r="C2" t="n">
-        <v>7.0091</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3.017283802686733</v>
+        <v>3.3417</v>
       </c>
       <c r="E2" t="n">
-        <v>93.8556</v>
+        <v>9.3149</v>
       </c>
       <c r="F2" t="n">
-        <v>33.16066787497177</v>
+        <v>4.454</v>
       </c>
       <c r="G2" t="n">
-        <v>60.69495098203828</v>
+        <v>4.8609</v>
       </c>
       <c r="H2" t="n">
-        <v>45.48641204583738</v>
+        <v>5.3591</v>
       </c>
       <c r="I2" t="n">
-        <v>44.16970011819473</v>
+        <v>4.3437</v>
       </c>
       <c r="J2" t="n">
-        <v>60.69495098203828</v>
+        <v>4.8609</v>
       </c>
       <c r="K2" t="n">
         <v>99</v>
@@ -541,7 +529,7 @@
         <v>148</v>
       </c>
       <c r="M2" t="n">
-        <v>104.8647</v>
+        <v>9.204599999999999</v>
       </c>
       <c r="N2" t="n">
         <v>247</v>
@@ -554,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.041399999999999</v>
+        <v>7.8432</v>
       </c>
       <c r="C3" t="n">
-        <v>6.835189999999999</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.876861601997837</v>
+        <v>2.7471</v>
       </c>
       <c r="E3" t="n">
-        <v>89.4876</v>
+        <v>7.8432</v>
       </c>
       <c r="F3" t="n">
-        <v>22.9023303799974</v>
+        <v>3.4401</v>
       </c>
       <c r="G3" t="n">
-        <v>66.58531601940558</v>
+        <v>4.4032</v>
       </c>
       <c r="H3" t="n">
-        <v>24.30719361951727</v>
+        <v>3.4401</v>
       </c>
       <c r="I3" t="n">
-        <v>23.60356433053125</v>
+        <v>2.7883</v>
       </c>
       <c r="J3" t="n">
-        <v>66.58531601940558</v>
+        <v>4.4032</v>
       </c>
       <c r="K3" t="n">
         <v>99</v>
@@ -587,7 +575,7 @@
         <v>148</v>
       </c>
       <c r="M3" t="n">
-        <v>90.1889</v>
+        <v>7.1915</v>
       </c>
       <c r="N3" t="n">
         <v>247</v>
@@ -596,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.3421</v>
+        <v>7.4704</v>
       </c>
       <c r="C4" t="n">
-        <v>6.240785</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.432901578503194</v>
+        <v>2.5965</v>
       </c>
       <c r="E4" t="n">
-        <v>75.6778</v>
+        <v>7.4704</v>
       </c>
       <c r="F4" t="n">
-        <v>17.49211256166742</v>
+        <v>3.0782</v>
       </c>
       <c r="G4" t="n">
-        <v>58.18571498153145</v>
+        <v>4.3922</v>
       </c>
       <c r="H4" t="n">
-        <v>17.46647816705951</v>
+        <v>3.0782</v>
       </c>
       <c r="I4" t="n">
-        <v>18.67408873889687</v>
+        <v>2.4949</v>
       </c>
       <c r="J4" t="n">
-        <v>58.18571498153145</v>
+        <v>4.3922</v>
       </c>
       <c r="K4" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="L4" t="n">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="M4" t="n">
-        <v>76.85980000000001</v>
+        <v>6.8871</v>
       </c>
       <c r="N4" t="n">
-        <v>229</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.3158</v>
+        <v>7.1465</v>
       </c>
       <c r="C5" t="n">
-        <v>6.21843</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2.417274141007874</v>
+        <v>2.4657</v>
       </c>
       <c r="E5" t="n">
-        <v>75.1917</v>
+        <v>7.1465</v>
       </c>
       <c r="F5" t="n">
-        <v>20.93393010862815</v>
+        <v>2.8563</v>
       </c>
       <c r="G5" t="n">
-        <v>54.25779042138012</v>
+        <v>4.2902</v>
       </c>
       <c r="H5" t="n">
-        <v>21.55333466133549</v>
+        <v>2.8563</v>
       </c>
       <c r="I5" t="n">
-        <v>20.92942234219157</v>
+        <v>2.3151</v>
       </c>
       <c r="J5" t="n">
-        <v>54.25779042138012</v>
+        <v>4.2902</v>
       </c>
       <c r="K5" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L5" t="n">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="M5" t="n">
-        <v>75.1872</v>
+        <v>6.6053</v>
       </c>
       <c r="N5" t="n">
-        <v>247</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6">
@@ -692,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7387</v>
+        <v>5.7396</v>
       </c>
       <c r="C6" t="n">
-        <v>4.877895</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1.597499479037688</v>
+        <v>1.8973</v>
       </c>
       <c r="E6" t="n">
-        <v>49.6918</v>
+        <v>5.7396</v>
       </c>
       <c r="F6" t="n">
-        <v>26.83304348865514</v>
+        <v>3.1848</v>
       </c>
       <c r="G6" t="n">
-        <v>22.85876942444396</v>
+        <v>2.5548</v>
       </c>
       <c r="H6" t="n">
-        <v>30.90395202588726</v>
+        <v>3.1848</v>
       </c>
       <c r="I6" t="n">
-        <v>36.98123637164786</v>
+        <v>3.1996</v>
       </c>
       <c r="J6" t="n">
-        <v>22.85876942444396</v>
+        <v>2.5548</v>
       </c>
       <c r="K6" t="n">
         <v>122</v>
@@ -725,7 +713,7 @@
         <v>127</v>
       </c>
       <c r="M6" t="n">
-        <v>59.84</v>
+        <v>5.7544</v>
       </c>
       <c r="N6" t="n">
         <v>249</v>
@@ -734,403 +722,403 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.2713</v>
+        <v>4.4034</v>
       </c>
       <c r="C7" t="n">
-        <v>4.480605</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.394732389757624</v>
+        <v>1.3575</v>
       </c>
       <c r="E7" t="n">
-        <v>43.3845</v>
+        <v>4.4034</v>
       </c>
       <c r="F7" t="n">
-        <v>2.106248469142836</v>
+        <v>3.7781</v>
       </c>
       <c r="G7" t="n">
-        <v>41.27829211138052</v>
+        <v>0.6253</v>
       </c>
       <c r="H7" t="n">
-        <v>2.106248469142836</v>
+        <v>3.7781</v>
       </c>
       <c r="I7" t="n">
-        <v>2.520443742261356</v>
+        <v>3.0623</v>
       </c>
       <c r="J7" t="n">
-        <v>41.27829211138052</v>
+        <v>0.6253</v>
       </c>
       <c r="K7" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="L7" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="M7" t="n">
-        <v>43.7987</v>
+        <v>3.6876</v>
       </c>
       <c r="N7" t="n">
-        <v>249</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2708</v>
+        <v>4.0678</v>
       </c>
       <c r="C8" t="n">
-        <v>3.63018</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1.012279374352868</v>
+        <v>1.2219</v>
       </c>
       <c r="E8" t="n">
-        <v>31.488</v>
+        <v>4.0678</v>
       </c>
       <c r="F8" t="n">
-        <v>14.84007168217333</v>
+        <v>0.8304</v>
       </c>
       <c r="G8" t="n">
-        <v>16.64788680932676</v>
+        <v>3.2373</v>
       </c>
       <c r="H8" t="n">
-        <v>14.84007168217333</v>
+        <v>0.8304</v>
       </c>
       <c r="I8" t="n">
-        <v>16.88501935895128</v>
+        <v>0.8343</v>
       </c>
       <c r="J8" t="n">
-        <v>16.64788680932676</v>
+        <v>3.2373</v>
       </c>
       <c r="K8" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="L8" t="n">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="M8" t="n">
-        <v>33.5329</v>
+        <v>4.0716</v>
       </c>
       <c r="N8" t="n">
-        <v>175</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2752</v>
+        <v>3.3438</v>
       </c>
       <c r="C9" t="n">
-        <v>2.78392</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6923431525904349</v>
+        <v>0.9295</v>
       </c>
       <c r="E9" t="n">
-        <v>21.536</v>
+        <v>3.3438</v>
       </c>
       <c r="F9" t="n">
-        <v>15.2134452414729</v>
+        <v>2.2154</v>
       </c>
       <c r="G9" t="n">
-        <v>6.322578313860902</v>
+        <v>1.1284</v>
       </c>
       <c r="H9" t="n">
-        <v>15.19685847989871</v>
+        <v>2.2154</v>
       </c>
       <c r="I9" t="n">
-        <v>12.07386770615876</v>
+        <v>2.2257</v>
       </c>
       <c r="J9" t="n">
-        <v>6.322578313860902</v>
+        <v>1.1284</v>
       </c>
       <c r="K9" t="n">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M9" t="n">
-        <v>18.3964</v>
+        <v>3.3541</v>
       </c>
       <c r="N9" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1775</v>
+        <v>2.6901</v>
       </c>
       <c r="C10" t="n">
-        <v>2.700875</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6638497954139547</v>
+        <v>0.6654</v>
       </c>
       <c r="E10" t="n">
-        <v>20.6497</v>
+        <v>2.6901</v>
       </c>
       <c r="F10" t="n">
-        <v>7.22603417569391</v>
+        <v>2.1134</v>
       </c>
       <c r="G10" t="n">
-        <v>13.42367511621823</v>
+        <v>0.5767</v>
       </c>
       <c r="H10" t="n">
-        <v>7.22603417569391</v>
+        <v>2.1134</v>
       </c>
       <c r="I10" t="n">
-        <v>7.725633189276575</v>
+        <v>2.1232</v>
       </c>
       <c r="J10" t="n">
-        <v>13.42367511621823</v>
+        <v>0.5767</v>
       </c>
       <c r="K10" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="L10" t="n">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="M10" t="n">
-        <v>21.1493</v>
+        <v>2.6999</v>
       </c>
       <c r="N10" t="n">
-        <v>229</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0724</v>
+        <v>2.6347</v>
       </c>
       <c r="C11" t="n">
-        <v>2.61154</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6337028794022974</v>
+        <v>0.643</v>
       </c>
       <c r="E11" t="n">
-        <v>19.712</v>
+        <v>2.6347</v>
       </c>
       <c r="F11" t="n">
-        <v>11.75165336837616</v>
+        <v>1.2955</v>
       </c>
       <c r="G11" t="n">
-        <v>7.960306065075567</v>
+        <v>1.3392</v>
       </c>
       <c r="H11" t="n">
-        <v>11.75165336837616</v>
+        <v>1.2955</v>
       </c>
       <c r="I11" t="n">
-        <v>13.37101995693708</v>
+        <v>1.05</v>
       </c>
       <c r="J11" t="n">
-        <v>7.960306065075567</v>
+        <v>1.3392</v>
       </c>
       <c r="K11" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L11" t="n">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="M11" t="n">
-        <v>21.3313</v>
+        <v>2.3892</v>
       </c>
       <c r="N11" t="n">
-        <v>175</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0416</v>
+        <v>2.5777</v>
       </c>
       <c r="C12" t="n">
-        <v>2.58536</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6249746272742659</v>
+        <v>0.62</v>
       </c>
       <c r="E12" t="n">
-        <v>19.4405</v>
+        <v>2.5777</v>
       </c>
       <c r="F12" t="n">
-        <v>1.449439493894508</v>
+        <v>1.7979</v>
       </c>
       <c r="G12" t="n">
-        <v>17.99101896099929</v>
+        <v>0.7798</v>
       </c>
       <c r="H12" t="n">
-        <v>1.449439493894508</v>
+        <v>1.7979</v>
       </c>
       <c r="I12" t="n">
-        <v>1.507000966618548</v>
+        <v>1.7979</v>
       </c>
       <c r="J12" t="n">
-        <v>17.99101896099929</v>
+        <v>0.7798</v>
       </c>
       <c r="K12" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="L12" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>19.498</v>
+        <v>2.5777</v>
       </c>
       <c r="N12" t="n">
-        <v>190</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9387</v>
+        <v>2.2769</v>
       </c>
       <c r="C13" t="n">
-        <v>2.497895</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5961674983623536</v>
+        <v>0.4985</v>
       </c>
       <c r="E13" t="n">
-        <v>18.5444</v>
+        <v>2.2769</v>
       </c>
       <c r="F13" t="n">
-        <v>2.020193777839876</v>
+        <v>0.4648</v>
       </c>
       <c r="G13" t="n">
-        <v>16.52419023118521</v>
+        <v>1.8121</v>
       </c>
       <c r="H13" t="n">
-        <v>2.020193777839876</v>
+        <v>0.4648</v>
       </c>
       <c r="I13" t="n">
-        <v>2.298574547226423</v>
+        <v>0.4648</v>
       </c>
       <c r="J13" t="n">
-        <v>16.52419023118521</v>
+        <v>1.8121</v>
       </c>
       <c r="K13" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="L13" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="M13" t="n">
-        <v>18.8228</v>
+        <v>2.2769</v>
       </c>
       <c r="N13" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1162</v>
+        <v>2.0329</v>
       </c>
       <c r="C14" t="n">
-        <v>1.79877</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3834110688993113</v>
+        <v>0.3999</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9264</v>
+        <v>2.0329</v>
       </c>
       <c r="F14" t="n">
-        <v>11.92638329749743</v>
+        <v>2.0529</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="H14" t="n">
-        <v>11.92638329749743</v>
+        <v>2.0529</v>
       </c>
       <c r="I14" t="n">
-        <v>13.45284623150727</v>
+        <v>2.0529</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="K14" t="n">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M14" t="n">
-        <v>13.4528</v>
+        <v>2.0329</v>
       </c>
       <c r="N14" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0761</v>
+        <v>1.7207</v>
       </c>
       <c r="C15" t="n">
-        <v>1.764685</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3738004819599421</v>
+        <v>0.2738</v>
       </c>
       <c r="E15" t="n">
-        <v>11.6274</v>
+        <v>1.7207</v>
       </c>
       <c r="F15" t="n">
-        <v>25.61866065183926</v>
+        <v>1.6362</v>
       </c>
       <c r="G15" t="n">
-        <v>-13.99122423629255</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>28.69440694422999</v>
+        <v>1.6362</v>
       </c>
       <c r="I15" t="n">
-        <v>30.67830254396263</v>
+        <v>1.3262</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.99122423629255</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>109</v>
@@ -1139,7 +1127,7 @@
         <v>120</v>
       </c>
       <c r="M15" t="n">
-        <v>16.6871</v>
+        <v>1.4107</v>
       </c>
       <c r="N15" t="n">
         <v>229</v>
@@ -1148,35 +1136,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7041</v>
+        <v>1.7192</v>
       </c>
       <c r="C16" t="n">
-        <v>1.448485</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2877339934634321</v>
+        <v>0.2732</v>
       </c>
       <c r="E16" t="n">
-        <v>8.9503</v>
+        <v>1.7192</v>
       </c>
       <c r="F16" t="n">
-        <v>4.50536760452711</v>
+        <v>0.9322</v>
       </c>
       <c r="G16" t="n">
-        <v>4.44488493673612</v>
+        <v>0.787</v>
       </c>
       <c r="H16" t="n">
-        <v>4.50536760452711</v>
+        <v>0.9322</v>
       </c>
       <c r="I16" t="n">
-        <v>5.126202949074386</v>
+        <v>0.9365</v>
       </c>
       <c r="J16" t="n">
-        <v>4.44488493673612</v>
+        <v>0.787</v>
       </c>
       <c r="K16" t="n">
         <v>116</v>
@@ -1185,7 +1173,7 @@
         <v>59</v>
       </c>
       <c r="M16" t="n">
-        <v>9.571099999999999</v>
+        <v>1.7235</v>
       </c>
       <c r="N16" t="n">
         <v>175</v>
@@ -1194,231 +1182,231 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4929</v>
+        <v>1.5389</v>
       </c>
       <c r="C17" t="n">
-        <v>1.268965</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2412865303999288</v>
+        <v>0.2003</v>
       </c>
       <c r="E17" t="n">
-        <v>7.5055</v>
+        <v>1.5389</v>
       </c>
       <c r="F17" t="n">
-        <v>12.96864365295899</v>
+        <v>2.1215</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.463185726733776</v>
+        <v>-0.5826</v>
       </c>
       <c r="H17" t="n">
-        <v>12.96864365295899</v>
+        <v>2.1215</v>
       </c>
       <c r="I17" t="n">
-        <v>10.30355635681263</v>
+        <v>2.1314</v>
       </c>
       <c r="J17" t="n">
-        <v>-5.463185726733776</v>
+        <v>-0.5826</v>
       </c>
       <c r="K17" t="n">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="L17" t="n">
-        <v>44</v>
+        <v>127</v>
       </c>
       <c r="M17" t="n">
-        <v>4.8404</v>
+        <v>1.5488</v>
       </c>
       <c r="N17" t="n">
-        <v>125</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5901999999999999</v>
+        <v>1.4297</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5016699999999999</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0609587259819988</v>
+        <v>0.1562</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8962</v>
+        <v>1.4297</v>
       </c>
       <c r="F18" t="n">
-        <v>1.896181905951592</v>
+        <v>1.9566</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.5269</v>
       </c>
       <c r="H18" t="n">
-        <v>1.896181905951592</v>
+        <v>1.9566</v>
       </c>
       <c r="I18" t="n">
-        <v>2.138875044631999</v>
+        <v>1.5859</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.5269</v>
       </c>
       <c r="K18" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1389</v>
+        <v>1.059</v>
       </c>
       <c r="N18" t="n">
-        <v>115</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4305</v>
+        <v>1.2014</v>
       </c>
       <c r="C19" t="n">
-        <v>0.365925</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.03188089583913175</v>
+        <v>0.064</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9917</v>
+        <v>1.2014</v>
       </c>
       <c r="F19" t="n">
-        <v>4.792078098278308</v>
+        <v>0.755</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.800391069688823</v>
+        <v>0.4464</v>
       </c>
       <c r="H19" t="n">
-        <v>4.792078098278308</v>
+        <v>0.755</v>
       </c>
       <c r="I19" t="n">
-        <v>5.123396416556401</v>
+        <v>0.7585</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.800391069688823</v>
+        <v>0.4464</v>
       </c>
       <c r="K19" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="M19" t="n">
-        <v>1.323</v>
+        <v>1.2049</v>
       </c>
       <c r="N19" t="n">
-        <v>229</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2717</v>
+        <v>1.0696</v>
       </c>
       <c r="C20" t="n">
-        <v>0.230945</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.003781759461694285</v>
+        <v>0.0107</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1176</v>
+        <v>1.0696</v>
       </c>
       <c r="F20" t="n">
-        <v>17.05528395806988</v>
+        <v>1.0696</v>
       </c>
       <c r="G20" t="n">
-        <v>-16.93764856217851</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>17.00656383106431</v>
+        <v>1.0696</v>
       </c>
       <c r="I20" t="n">
-        <v>20.35091681411092</v>
+        <v>1.0696</v>
       </c>
       <c r="J20" t="n">
-        <v>-16.93764856217851</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="L20" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4133</v>
+        <v>1.0696</v>
       </c>
       <c r="N20" t="n">
-        <v>249</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2641</v>
+        <v>1.0464</v>
       </c>
       <c r="C21" t="n">
-        <v>0.224485</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00245198498870712</v>
+        <v>0.0014</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07630000000000001</v>
+        <v>1.0464</v>
       </c>
       <c r="F21" t="n">
-        <v>-9.390558208232685</v>
+        <v>0.628</v>
       </c>
       <c r="G21" t="n">
-        <v>9.466829644263424</v>
+        <v>0.4184</v>
       </c>
       <c r="H21" t="n">
-        <v>-9.390558208232685</v>
+        <v>0.628</v>
       </c>
       <c r="I21" t="n">
-        <v>-11.23721821951672</v>
+        <v>0.628</v>
       </c>
       <c r="J21" t="n">
-        <v>9.466829644263424</v>
+        <v>0.4184</v>
       </c>
       <c r="K21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="L21" t="n">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7704</v>
+        <v>1.0464</v>
       </c>
       <c r="N21" t="n">
-        <v>249</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22">
@@ -1428,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1705</v>
+        <v>0.851</v>
       </c>
       <c r="C22" t="n">
-        <v>0.144925</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.01391941553148811</v>
+        <v>-0.0776</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.433</v>
+        <v>0.851</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4329772882724521</v>
+        <v>0.851</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4329772882724521</v>
+        <v>0.851</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3737277646141166</v>
+        <v>0.851</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1461,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3737</v>
+        <v>0.851</v>
       </c>
       <c r="N22" t="n">
         <v>88</v>
@@ -1470,219 +1458,219 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1153</v>
+        <v>0.7231</v>
       </c>
       <c r="C23" t="n">
-        <v>0.09800499999999999</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.023699781643046</v>
+        <v>-0.1292</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7372</v>
+        <v>0.7231</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0155632703684845</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7527685908966415</v>
+        <v>1.3153</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0155632703684845</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01618133325871618</v>
+        <v>-0.595</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7527685908966415</v>
+        <v>1.3153</v>
       </c>
       <c r="K23" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="L23" t="n">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7366</v>
+        <v>0.7202999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>190</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.6051</v>
+        <v>0.6754</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.514335</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1603312767816741</v>
+        <v>-0.1485</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9873</v>
+        <v>0.6754</v>
       </c>
       <c r="F24" t="n">
-        <v>4.741792307523632</v>
+        <v>0.6754</v>
       </c>
       <c r="G24" t="n">
-        <v>-9.729056412769264</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>4.741792307523632</v>
+        <v>0.6754</v>
       </c>
       <c r="I24" t="n">
-        <v>5.069633928785432</v>
+        <v>0.6754</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.729056412769264</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="L24" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.6594</v>
+        <v>0.6754</v>
       </c>
       <c r="N24" t="n">
-        <v>229</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.7993</v>
+        <v>0.4246</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.679405</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2002033367317746</v>
+        <v>-0.2498</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.2275</v>
+        <v>0.4246</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.227524255248175</v>
+        <v>1.4246</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.227524255248175</v>
+        <v>1.4246</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.481752197252389</v>
+        <v>1.4246</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K25" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.4818</v>
+        <v>0.4246000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>57</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.0325</v>
+        <v>0.3098</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.877625</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2498811788894577</v>
+        <v>-0.2962</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.7728</v>
+        <v>0.3098</v>
       </c>
       <c r="F26" t="n">
-        <v>9.795031080542959</v>
+        <v>0.1826</v>
       </c>
       <c r="G26" t="n">
-        <v>-17.56783411103875</v>
+        <v>0.1272</v>
       </c>
       <c r="H26" t="n">
-        <v>9.795031080542959</v>
+        <v>0.1826</v>
       </c>
       <c r="I26" t="n">
-        <v>9.511490707158821</v>
+        <v>0.1826</v>
       </c>
       <c r="J26" t="n">
-        <v>-17.56783411103875</v>
+        <v>0.1272</v>
       </c>
       <c r="K26" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L26" t="n">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.0563</v>
+        <v>0.3098</v>
       </c>
       <c r="N26" t="n">
-        <v>247</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.1091</v>
+        <v>0.2814</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.942735</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2666283242568376</v>
+        <v>-0.3077</v>
       </c>
       <c r="E27" t="n">
-        <v>-8.293699999999999</v>
+        <v>0.2814</v>
       </c>
       <c r="F27" t="n">
-        <v>11.14421242029893</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>-19.43795209293097</v>
+        <v>-0.4086</v>
       </c>
       <c r="H27" t="n">
-        <v>11.14421242029893</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>8.854050107132233</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>-19.43795209293097</v>
+        <v>-0.4086</v>
       </c>
       <c r="K27" t="n">
         <v>81</v>
@@ -1691,7 +1679,7 @@
         <v>44</v>
       </c>
       <c r="M27" t="n">
-        <v>-10.5839</v>
+        <v>0.2813999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>125</v>
@@ -1700,400 +1688,400 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.5959</v>
+        <v>0.1346</v>
       </c>
       <c r="C28" t="n">
-        <v>-1.356515</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3785314057735646</v>
+        <v>-0.367</v>
       </c>
       <c r="E28" t="n">
-        <v>-11.7746</v>
+        <v>0.1346</v>
       </c>
       <c r="F28" t="n">
-        <v>-8.182596105042217</v>
+        <v>0.4876</v>
       </c>
       <c r="G28" t="n">
-        <v>-3.59200040923221</v>
+        <v>-0.353</v>
       </c>
       <c r="H28" t="n">
-        <v>-8.182596105042217</v>
+        <v>0.4876</v>
       </c>
       <c r="I28" t="n">
-        <v>-8.507550878591742</v>
+        <v>0.4876</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.59200040923221</v>
+        <v>-0.353</v>
       </c>
       <c r="K28" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="L28" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="M28" t="n">
-        <v>-12.0996</v>
+        <v>0.1346</v>
       </c>
       <c r="N28" t="n">
-        <v>190</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.6689</v>
+        <v>0.132</v>
       </c>
       <c r="C29" t="n">
-        <v>-1.418565</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3961618365107948</v>
+        <v>-0.368</v>
       </c>
       <c r="E29" t="n">
-        <v>-12.323</v>
+        <v>0.132</v>
       </c>
       <c r="F29" t="n">
-        <v>-3.473069254698656</v>
+        <v>0.4963</v>
       </c>
       <c r="G29" t="n">
-        <v>-8.84993937317442</v>
+        <v>-0.3643</v>
       </c>
       <c r="H29" t="n">
-        <v>-3.473069254698656</v>
+        <v>0.4963</v>
       </c>
       <c r="I29" t="n">
-        <v>-2.759345214079961</v>
+        <v>0.4963</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.84993937317442</v>
+        <v>-0.3643</v>
       </c>
       <c r="K29" t="n">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="L29" t="n">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="M29" t="n">
-        <v>-11.6093</v>
+        <v>0.132</v>
       </c>
       <c r="N29" t="n">
-        <v>125</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.0545</v>
+        <v>-0.0693</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.746325</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4929924994430711</v>
+        <v>-0.4494</v>
       </c>
       <c r="E30" t="n">
-        <v>-15.335</v>
+        <v>-0.0693</v>
       </c>
       <c r="F30" t="n">
-        <v>-15.3350228725228</v>
+        <v>-0.0693</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-15.31014108183845</v>
+        <v>-0.0693</v>
       </c>
       <c r="I30" t="n">
-        <v>-17.26969263178668</v>
+        <v>-0.0693</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-17.2697</v>
+        <v>-0.0693</v>
       </c>
       <c r="N30" t="n">
-        <v>115</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.2148</v>
+        <v>-0.1583</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.88258</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5352125393931751</v>
+        <v>-0.4853</v>
       </c>
       <c r="E31" t="n">
-        <v>-16.6483</v>
+        <v>-0.1583</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.676078427474879</v>
+        <v>0.5906</v>
       </c>
       <c r="G31" t="n">
-        <v>-13.97224085228553</v>
+        <v>-0.7489</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.676078427474879</v>
+        <v>0.5906</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.782353312393738</v>
+        <v>0.4787</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.97224085228553</v>
+        <v>-0.7489</v>
       </c>
       <c r="K31" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L31" t="n">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="M31" t="n">
-        <v>-16.7546</v>
+        <v>-0.2702</v>
       </c>
       <c r="N31" t="n">
-        <v>190</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>arrozdoce</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-2.7783</v>
+        <v>-0.8278</v>
       </c>
       <c r="C32" t="n">
-        <v>-2.361555</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6932724289231995</v>
+        <v>-0.7558</v>
       </c>
       <c r="E32" t="n">
-        <v>-21.5649</v>
+        <v>-0.8278</v>
       </c>
       <c r="F32" t="n">
-        <v>-11.84872503966209</v>
+        <v>-0.8278</v>
       </c>
       <c r="G32" t="n">
-        <v>-9.716204581857179</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-11.84872503966209</v>
+        <v>-0.8278</v>
       </c>
       <c r="I32" t="n">
-        <v>-9.413783697779376</v>
+        <v>-0.8278</v>
       </c>
       <c r="J32" t="n">
-        <v>-9.716204581857179</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="L32" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-19.13</v>
+        <v>-0.8278</v>
       </c>
       <c r="N32" t="n">
-        <v>125</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>arrozdoce</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-2.8304</v>
+        <v>-1</v>
       </c>
       <c r="C33" t="n">
-        <v>-2.40584</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7086919545229639</v>
+        <v>-0.8253</v>
       </c>
       <c r="E33" t="n">
-        <v>-22.0446</v>
+        <v>-1</v>
       </c>
       <c r="F33" t="n">
-        <v>-22.04456932805225</v>
+        <v>-1</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-23.06635602617493</v>
+        <v>-1</v>
       </c>
       <c r="I33" t="n">
-        <v>-19.90990730680363</v>
+        <v>-1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-19.9099</v>
+        <v>-1</v>
       </c>
       <c r="N33" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>roman</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-3.2348</v>
+        <v>-1.02</v>
       </c>
       <c r="C34" t="n">
-        <v>-2.74958</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8331836529339119</v>
+        <v>-0.8334</v>
       </c>
       <c r="E34" t="n">
-        <v>-25.917</v>
+        <v>-1.02</v>
       </c>
       <c r="F34" t="n">
-        <v>-25.91700764045613</v>
+        <v>0.75</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-1.77</v>
       </c>
       <c r="H34" t="n">
-        <v>-29.22215231234575</v>
+        <v>0.75</v>
       </c>
       <c r="I34" t="n">
-        <v>-25.2233314696037</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-1.77</v>
       </c>
       <c r="K34" t="n">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="M34" t="n">
-        <v>-25.2233</v>
+        <v>-1.0165</v>
       </c>
       <c r="N34" t="n">
-        <v>88</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-3.6648</v>
+        <v>-1.1592</v>
       </c>
       <c r="C35" t="n">
-        <v>-3.11508</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9755116505615455</v>
+        <v>-0.8897</v>
       </c>
       <c r="E35" t="n">
-        <v>-30.3443</v>
+        <v>-1.1592</v>
       </c>
       <c r="F35" t="n">
-        <v>-13.59745060050582</v>
+        <v>-1.1592</v>
       </c>
       <c r="G35" t="n">
-        <v>-16.74681121011679</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-13.59745060050582</v>
+        <v>-1.1592</v>
       </c>
       <c r="I35" t="n">
-        <v>-14.13744505019098</v>
+        <v>-1.1592</v>
       </c>
       <c r="J35" t="n">
-        <v>-16.74681121011679</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="L35" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-30.8843</v>
+        <v>-1.1592</v>
       </c>
       <c r="N35" t="n">
-        <v>190</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>roman</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-3.6987</v>
+        <v>-1.1787</v>
       </c>
       <c r="C36" t="n">
-        <v>-3.143895</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.987204125289959</v>
+        <v>-0.8975</v>
       </c>
       <c r="E36" t="n">
-        <v>-30.708</v>
+        <v>-1.1787</v>
       </c>
       <c r="F36" t="n">
-        <v>-30.70796788647402</v>
+        <v>-1.1787</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-39.1573401931543</v>
+        <v>-1.1787</v>
       </c>
       <c r="I36" t="n">
-        <v>-33.7989673246174</v>
+        <v>-1.1787</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2105,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-33.799</v>
+        <v>-1.1787</v>
       </c>
       <c r="N36" t="n">
         <v>88</v>
@@ -2114,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-3.7027</v>
+        <v>-1.6466</v>
       </c>
       <c r="C37" t="n">
-        <v>-3.147295</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9886002326524492</v>
+        <v>-1.0866</v>
       </c>
       <c r="E37" t="n">
-        <v>-30.7514</v>
+        <v>-1.6466</v>
       </c>
       <c r="F37" t="n">
-        <v>-30.7513951969513</v>
+        <v>-0.7527</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.8939</v>
       </c>
       <c r="H37" t="n">
-        <v>-39.2613547992422</v>
+        <v>-0.7527</v>
       </c>
       <c r="I37" t="n">
-        <v>-22.33576595995166</v>
+        <v>-0.7527</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.8939</v>
       </c>
       <c r="K37" t="n">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M37" t="n">
-        <v>-22.3358</v>
+        <v>-1.6466</v>
       </c>
       <c r="N37" t="n">
-        <v>58</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38">
@@ -2164,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-3.7182</v>
+        <v>-1.7229</v>
       </c>
       <c r="C38" t="n">
-        <v>-3.16047</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9939704911148673</v>
+        <v>-1.1174</v>
       </c>
       <c r="E38" t="n">
-        <v>-30.9184</v>
+        <v>-1.7229</v>
       </c>
       <c r="F38" t="n">
-        <v>-30.91844243691047</v>
+        <v>-1.7229</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-39.66403875955793</v>
+        <v>-1.7229</v>
       </c>
       <c r="I38" t="n">
-        <v>-34.23632819246053</v>
+        <v>-1.7229</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2197,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-34.2363</v>
+        <v>-1.7229</v>
       </c>
       <c r="N38" t="n">
         <v>88</v>
@@ -2206,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>story</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-3.9134</v>
+        <v>-1.7563</v>
       </c>
       <c r="C39" t="n">
-        <v>-3.32639</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.062796550860407</v>
+        <v>-1.1309</v>
       </c>
       <c r="E39" t="n">
-        <v>-33.0593</v>
+        <v>-1.7563</v>
       </c>
       <c r="F39" t="n">
-        <v>-33.05934559794396</v>
+        <v>-1.7563</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-45.2057489288955</v>
+        <v>-1.7563</v>
       </c>
       <c r="I39" t="n">
-        <v>-50.99165220089529</v>
+        <v>-1.7563</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-50.9917</v>
+        <v>-1.7563</v>
       </c>
       <c r="N39" t="n">
-        <v>115</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-4.759</v>
+        <v>-2</v>
       </c>
       <c r="C40" t="n">
-        <v>-4.04515</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.389628071031172</v>
+        <v>-1.2293</v>
       </c>
       <c r="E40" t="n">
-        <v>-43.2258</v>
+        <v>-2</v>
       </c>
       <c r="F40" t="n">
-        <v>-6.76509102886737</v>
+        <v>-2</v>
       </c>
       <c r="G40" t="n">
-        <v>-36.4606746321446</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-6.76509102886737</v>
+        <v>-2</v>
       </c>
       <c r="I40" t="n">
-        <v>-8.095451035022627</v>
+        <v>-2</v>
       </c>
       <c r="J40" t="n">
-        <v>-36.4606746321446</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="L40" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-44.5561</v>
+        <v>-2</v>
       </c>
       <c r="N40" t="n">
-        <v>249</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41">
@@ -2302,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-5.477</v>
+        <v>-2.6582</v>
       </c>
       <c r="C41" t="n">
-        <v>-4.65545</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.707409790575953</v>
+        <v>-1.4952</v>
       </c>
       <c r="E41" t="n">
-        <v>-53.1107</v>
+        <v>-2.6582</v>
       </c>
       <c r="F41" t="n">
-        <v>-29.13175271165176</v>
+        <v>-1.6582</v>
       </c>
       <c r="G41" t="n">
-        <v>-23.9789299474769</v>
+        <v>-1</v>
       </c>
       <c r="H41" t="n">
-        <v>-35.56290629928137</v>
+        <v>-1.6582</v>
       </c>
       <c r="I41" t="n">
-        <v>-40.46344075583306</v>
+        <v>-1.6659</v>
       </c>
       <c r="J41" t="n">
-        <v>-23.9789299474769</v>
+        <v>-1</v>
       </c>
       <c r="K41" t="n">
         <v>116</v>
@@ -2335,7 +2323,7 @@
         <v>59</v>
       </c>
       <c r="M41" t="n">
-        <v>-64.44240000000001</v>
+        <v>-2.6659</v>
       </c>
       <c r="N41" t="n">
         <v>175</v>
@@ -2348,31 +2336,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-5.5995</v>
+        <v>-2.7875</v>
       </c>
       <c r="C42" t="n">
-        <v>-4.759575</v>
+        <v>-0</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.765747201948977</v>
+        <v>-1.5475</v>
       </c>
       <c r="E42" t="n">
-        <v>-54.9253</v>
+        <v>-2.7875</v>
       </c>
       <c r="F42" t="n">
-        <v>-10.07931696813117</v>
+        <v>-1.352</v>
       </c>
       <c r="G42" t="n">
-        <v>-44.84600899437373</v>
+        <v>-1.4355</v>
       </c>
       <c r="H42" t="n">
-        <v>-10.07931696813117</v>
+        <v>-1.352</v>
       </c>
       <c r="I42" t="n">
-        <v>-9.787547266422111</v>
+        <v>-1.0958</v>
       </c>
       <c r="J42" t="n">
-        <v>-44.84600899437373</v>
+        <v>-1.4355</v>
       </c>
       <c r="K42" t="n">
         <v>99</v>
@@ -2381,7 +2369,7 @@
         <v>148</v>
       </c>
       <c r="M42" t="n">
-        <v>-54.6336</v>
+        <v>-2.5313</v>
       </c>
       <c r="N42" t="n">
         <v>247</v>
@@ -2402,52 +2390,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2487,10 +2475,10 @@
         <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7588767143581208</v>
+        <v>1.1592</v>
       </c>
       <c r="J2" t="n">
-        <v>16.69528771587866</v>
+        <v>25.5024</v>
       </c>
     </row>
     <row r="3">
@@ -2527,10 +2515,10 @@
         <v>1.36</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5451249406340053</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>11.99274869394812</v>
+        <v>19.8814</v>
       </c>
     </row>
     <row r="4">
@@ -2567,10 +2555,10 @@
         <v>1.32</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4739675689582438</v>
+        <v>0.8118</v>
       </c>
       <c r="J4" t="n">
-        <v>10.42728651708136</v>
+        <v>17.8596</v>
       </c>
     </row>
     <row r="5">
@@ -2607,10 +2595,10 @@
         <v>1.25</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3571733569858112</v>
+        <v>0.6314</v>
       </c>
       <c r="J5" t="n">
-        <v>7.857813853687847</v>
+        <v>13.8908</v>
       </c>
     </row>
     <row r="6">
@@ -2647,10 +2635,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3403892191538935</v>
+        <v>-0.6931</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.488562821385656</v>
+        <v>-15.2482</v>
       </c>
     </row>
     <row r="7">
@@ -2687,10 +2675,10 @@
         <v>1.13</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1223061668511099</v>
+        <v>0.3277</v>
       </c>
       <c r="J7" t="n">
-        <v>2.690735670724417</v>
+        <v>7.2094</v>
       </c>
     </row>
     <row r="8">
@@ -2727,10 +2715,10 @@
         <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.007236715252510372</v>
+        <v>0.209</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1592077355552282</v>
+        <v>4.598</v>
       </c>
     </row>
     <row r="9">
@@ -2767,10 +2755,10 @@
         <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2757723418730969</v>
+        <v>-0.1922</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.066991521208132</v>
+        <v>-4.2284</v>
       </c>
     </row>
     <row r="10">
@@ -2807,10 +2795,10 @@
         <v>0.72</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5004902385422043</v>
+        <v>-0.4625</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.0107852479285</v>
+        <v>-10.175</v>
       </c>
     </row>
     <row r="11">
@@ -2847,10 +2835,10 @@
         <v>0.54</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7630807021573713</v>
+        <v>-0.6976</v>
       </c>
       <c r="J11" t="n">
-        <v>-16.78777544746217</v>
+        <v>-15.3472</v>
       </c>
     </row>
     <row r="12">
@@ -2887,10 +2875,10 @@
         <v>1.57</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9762941667297298</v>
+        <v>1.3766</v>
       </c>
       <c r="J12" t="n">
-        <v>21.47847166805406</v>
+        <v>30.2852</v>
       </c>
     </row>
     <row r="13">
@@ -2927,10 +2915,10 @@
         <v>1.4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6800592157877915</v>
+        <v>1.0332</v>
       </c>
       <c r="J13" t="n">
-        <v>14.96130274733141</v>
+        <v>22.7304</v>
       </c>
     </row>
     <row r="14">
@@ -2967,10 +2955,10 @@
         <v>1.31</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5170028737972379</v>
+        <v>0.8345</v>
       </c>
       <c r="J14" t="n">
-        <v>11.37406322353923</v>
+        <v>18.359</v>
       </c>
     </row>
     <row r="15">
@@ -3007,10 +2995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1123506794171401</v>
+        <v>-0.3485</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.471714947177083</v>
+        <v>-7.667</v>
       </c>
     </row>
     <row r="16">
@@ -3047,10 +3035,10 @@
         <v>0.61</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6041467217345464</v>
+        <v>-1.1379</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.29122787816002</v>
+        <v>-25.0338</v>
       </c>
     </row>
     <row r="17">
@@ -3087,10 +3075,10 @@
         <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6176104126599118</v>
+        <v>0.7125</v>
       </c>
       <c r="J17" t="n">
-        <v>13.58742907851806</v>
+        <v>15.675</v>
       </c>
     </row>
     <row r="18">
@@ -3127,10 +3115,10 @@
         <v>1.29</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3490855244069253</v>
+        <v>0.5258</v>
       </c>
       <c r="J18" t="n">
-        <v>7.679881536952356</v>
+        <v>11.5676</v>
       </c>
     </row>
     <row r="19">
@@ -3167,10 +3155,10 @@
         <v>0.76</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4930390072260645</v>
+        <v>-0.4276</v>
       </c>
       <c r="J19" t="n">
-        <v>-10.84685815897342</v>
+        <v>-9.4072</v>
       </c>
     </row>
     <row r="20">
@@ -3207,10 +3195,10 @@
         <v>0.68</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6124658850111533</v>
+        <v>-0.536</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.47424947024537</v>
+        <v>-11.792</v>
       </c>
     </row>
     <row r="21">
@@ -3247,10 +3235,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7858070637663245</v>
+        <v>-0.6863</v>
       </c>
       <c r="J21" t="n">
-        <v>-17.28775540285914</v>
+        <v>-15.0986</v>
       </c>
     </row>
     <row r="22">
@@ -3287,10 +3275,10 @@
         <v>1.1</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.05258393161952844</v>
+        <v>0.3275</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8939268375319835</v>
+        <v>5.5675</v>
       </c>
     </row>
     <row r="23">
@@ -3327,10 +3315,10 @@
         <v>0.99</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2198420109841984</v>
+        <v>0.0822</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.737314186731373</v>
+        <v>1.3974</v>
       </c>
     </row>
     <row r="24">
@@ -3367,10 +3355,10 @@
         <v>0.65</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7108555486000446</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-12.08454432620076</v>
+        <v>-8.902900000000001</v>
       </c>
     </row>
     <row r="25">
@@ -3407,10 +3395,10 @@
         <v>0.53</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8871891772077665</v>
+        <v>-0.6861</v>
       </c>
       <c r="J25" t="n">
-        <v>-15.08221601253203</v>
+        <v>-11.6637</v>
       </c>
     </row>
     <row r="26">
@@ -3447,10 +3435,10 @@
         <v>0.48</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.959519790991055</v>
+        <v>-0.7493</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.31183644684793</v>
+        <v>-12.7381</v>
       </c>
     </row>
     <row r="27">
@@ -3487,10 +3475,10 @@
         <v>1.86</v>
       </c>
       <c r="I27" t="n">
-        <v>1.460393854046149</v>
+        <v>1.032</v>
       </c>
       <c r="J27" t="n">
-        <v>24.82669551878454</v>
+        <v>17.544</v>
       </c>
     </row>
     <row r="28">
@@ -3527,10 +3515,10 @@
         <v>1.52</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8806783469402205</v>
+        <v>0.6687</v>
       </c>
       <c r="J28" t="n">
-        <v>14.97153189798375</v>
+        <v>11.3679</v>
       </c>
     </row>
     <row r="29">
@@ -3567,10 +3555,10 @@
         <v>1.46</v>
       </c>
       <c r="I29" t="n">
-        <v>0.775825759339704</v>
+        <v>0.5956</v>
       </c>
       <c r="J29" t="n">
-        <v>13.18903790877497</v>
+        <v>10.1252</v>
       </c>
     </row>
     <row r="30">
@@ -3607,10 +3595,10 @@
         <v>1.13</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2013818844075259</v>
+        <v>0.1389</v>
       </c>
       <c r="J30" t="n">
-        <v>3.42349203492794</v>
+        <v>2.3613</v>
       </c>
     </row>
     <row r="31">
@@ -3647,10 +3635,10 @@
         <v>1.05</v>
       </c>
       <c r="I31" t="n">
-        <v>0.05581987156997333</v>
+        <v>0.0101</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9489378166895466</v>
+        <v>0.1717</v>
       </c>
     </row>
     <row r="32">
@@ -3687,10 +3675,10 @@
         <v>1.74</v>
       </c>
       <c r="I32" t="n">
-        <v>1.335304211390679</v>
+        <v>1.6673</v>
       </c>
       <c r="J32" t="n">
-        <v>25.37078001642291</v>
+        <v>31.6787</v>
       </c>
     </row>
     <row r="33">
@@ -3727,10 +3715,10 @@
         <v>1.44</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8303495747142109</v>
+        <v>1.0908</v>
       </c>
       <c r="J33" t="n">
-        <v>15.77664191957001</v>
+        <v>20.7252</v>
       </c>
     </row>
     <row r="34">
@@ -3767,10 +3755,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1650754503137148</v>
+        <v>0.108</v>
       </c>
       <c r="J34" t="n">
-        <v>3.136433555960581</v>
+        <v>2.052</v>
       </c>
     </row>
     <row r="35">
@@ -3807,10 +3795,10 @@
         <v>1.06</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1650754503137148</v>
+        <v>0.108</v>
       </c>
       <c r="J35" t="n">
-        <v>3.136433555960581</v>
+        <v>2.052</v>
       </c>
     </row>
     <row r="36">
@@ -3847,10 +3835,10 @@
         <v>0.79</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2663553519152272</v>
+        <v>-0.7577</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.060751686389318</v>
+        <v>-14.3963</v>
       </c>
     </row>
     <row r="37">
@@ -3887,10 +3875,10 @@
         <v>1.38</v>
       </c>
       <c r="I37" t="n">
-        <v>0.450201338935176</v>
+        <v>0.6652</v>
       </c>
       <c r="J37" t="n">
-        <v>8.553825439768344</v>
+        <v>12.6388</v>
       </c>
     </row>
     <row r="38">
@@ -3927,10 +3915,10 @@
         <v>0.78</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.5052657861430466</v>
+        <v>-0.3787</v>
       </c>
       <c r="J38" t="n">
-        <v>-9.600049936717886</v>
+        <v>-7.1953</v>
       </c>
     </row>
     <row r="39">
@@ -3967,10 +3955,10 @@
         <v>0.76</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5350861404675176</v>
+        <v>-0.4085</v>
       </c>
       <c r="J39" t="n">
-        <v>-10.16663666888283</v>
+        <v>-7.7615</v>
       </c>
     </row>
     <row r="40">
@@ -4007,10 +3995,10 @@
         <v>0.75</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5500257107830909</v>
+        <v>-0.4231</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.45048850487873</v>
+        <v>-8.0389</v>
       </c>
     </row>
     <row r="41">
@@ -4047,10 +4035,10 @@
         <v>0.72</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.594848817589039</v>
+        <v>-0.4659</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.30212753419174</v>
+        <v>-8.8521</v>
       </c>
     </row>
     <row r="42">
@@ -4087,10 +4075,10 @@
         <v>1.71</v>
       </c>
       <c r="I42" t="n">
-        <v>0.965088325470751</v>
+        <v>1.539</v>
       </c>
       <c r="J42" t="n">
-        <v>17.37158985847352</v>
+        <v>27.702</v>
       </c>
     </row>
     <row r="43">
@@ -4127,10 +4115,10 @@
         <v>1.61</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8317371914027583</v>
+        <v>1.352</v>
       </c>
       <c r="J43" t="n">
-        <v>14.97126944524965</v>
+        <v>24.336</v>
       </c>
     </row>
     <row r="44">
@@ -4167,10 +4155,10 @@
         <v>1.42</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5735486507427654</v>
+        <v>0.9597</v>
       </c>
       <c r="J44" t="n">
-        <v>10.32387571336978</v>
+        <v>17.2746</v>
       </c>
     </row>
     <row r="45">
@@ -4207,10 +4195,10 @@
         <v>1.13</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1828044537915081</v>
+        <v>0.2482</v>
       </c>
       <c r="J45" t="n">
-        <v>3.290480168247145</v>
+        <v>4.4676</v>
       </c>
     </row>
     <row r="46">
@@ -4247,10 +4235,10 @@
         <v>1.04</v>
       </c>
       <c r="I46" t="n">
-        <v>0.05546253801463945</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9983256842635101</v>
+        <v>-0.1584</v>
       </c>
     </row>
     <row r="47">
@@ -4287,10 +4275,10 @@
         <v>1.24</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2730136291269781</v>
+        <v>0.5768</v>
       </c>
       <c r="J47" t="n">
-        <v>4.914245324285606</v>
+        <v>10.3824</v>
       </c>
     </row>
     <row r="48">
@@ -4327,10 +4315,10 @@
         <v>0.68</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.4480491023630178</v>
+        <v>-0.4203</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.064883842534321</v>
+        <v>-7.5654</v>
       </c>
     </row>
     <row r="49">
@@ -4367,10 +4355,10 @@
         <v>0.68</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4480491023630178</v>
+        <v>-0.4203</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.064883842534321</v>
+        <v>-7.5654</v>
       </c>
     </row>
     <row r="50">
@@ -4407,10 +4395,10 @@
         <v>0.45</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.7103682779271817</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.78662900268927</v>
+        <v>-13.8348</v>
       </c>
     </row>
     <row r="51">
@@ -4447,10 +4435,10 @@
         <v>0.3</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.882432718690499</v>
+        <v>-0.9524</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.88378893642898</v>
+        <v>-17.1432</v>
       </c>
     </row>
     <row r="52">
@@ -4487,10 +4475,10 @@
         <v>1.29</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5250267260507955</v>
+        <v>0.8399</v>
       </c>
       <c r="J52" t="n">
-        <v>11.5505879731175</v>
+        <v>18.4778</v>
       </c>
     </row>
     <row r="53">
@@ -4527,10 +4515,10 @@
         <v>1.13</v>
       </c>
       <c r="I53" t="n">
-        <v>0.294958231747146</v>
+        <v>0.4332</v>
       </c>
       <c r="J53" t="n">
-        <v>6.489081098437211</v>
+        <v>9.5304</v>
       </c>
     </row>
     <row r="54">
@@ -4567,10 +4555,10 @@
         <v>1.08</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2283678056736752</v>
+        <v>0.2733</v>
       </c>
       <c r="J54" t="n">
-        <v>5.024091724820853</v>
+        <v>6.0126</v>
       </c>
     </row>
     <row r="55">
@@ -4607,10 +4595,10 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>0.122784239322629</v>
+        <v>-0.0653</v>
       </c>
       <c r="J55" t="n">
-        <v>2.701253265097837</v>
+        <v>-1.4366</v>
       </c>
     </row>
     <row r="56">
@@ -4647,10 +4635,10 @@
         <v>0.87</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0613853557408508</v>
+        <v>-0.5152</v>
       </c>
       <c r="J56" t="n">
-        <v>-1.350477826298718</v>
+        <v>-11.3344</v>
       </c>
     </row>
     <row r="57">
@@ -4687,10 +4675,10 @@
         <v>1.05</v>
       </c>
       <c r="I57" t="n">
-        <v>0.09432716945266222</v>
+        <v>0.2045</v>
       </c>
       <c r="J57" t="n">
-        <v>2.075197727958569</v>
+        <v>4.499</v>
       </c>
     </row>
     <row r="58">
@@ -4727,10 +4715,10 @@
         <v>0.9</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1112306917628717</v>
+        <v>-0.1354</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.447075218783177</v>
+        <v>-2.9788</v>
       </c>
     </row>
     <row r="59">
@@ -4767,10 +4755,10 @@
         <v>0.88</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1358434955993969</v>
+        <v>-0.1713</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.988556903186731</v>
+        <v>-3.7686</v>
       </c>
     </row>
     <row r="60">
@@ -4807,10 +4795,10 @@
         <v>0.73</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3095706956450585</v>
+        <v>-0.4365</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.810555304191287</v>
+        <v>-9.603</v>
       </c>
     </row>
     <row r="61">
@@ -4847,10 +4835,10 @@
         <v>0.59</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4839369555440003</v>
+        <v>-0.6278</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.64661302196801</v>
+        <v>-13.8116</v>
       </c>
     </row>
     <row r="62">
@@ -4887,10 +4875,10 @@
         <v>1.31</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3421375052645653</v>
+        <v>0.5239</v>
       </c>
       <c r="J62" t="n">
-        <v>8.211300126349567</v>
+        <v>12.5736</v>
       </c>
     </row>
     <row r="63">
@@ -4927,10 +4915,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.08691127765852372</v>
+        <v>0.3143</v>
       </c>
       <c r="J63" t="n">
-        <v>2.085870663804569</v>
+        <v>7.5432</v>
       </c>
     </row>
     <row r="64">
@@ -4967,10 +4955,10 @@
         <v>0.97</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1341297094502205</v>
+        <v>-0.1041</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.219113026805291</v>
+        <v>-2.4984</v>
       </c>
     </row>
     <row r="65">
@@ -5007,10 +4995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1664649297392646</v>
+        <v>-0.1652</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.99515831374235</v>
+        <v>-3.9648</v>
       </c>
     </row>
     <row r="66">
@@ -5047,10 +5035,10 @@
         <v>0.76</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3628873282755547</v>
+        <v>-0.4456</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.709295878613313</v>
+        <v>-10.6944</v>
       </c>
     </row>
     <row r="67">
@@ -5087,10 +5075,10 @@
         <v>1.34</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4222809391487511</v>
+        <v>0.528</v>
       </c>
       <c r="J67" t="n">
-        <v>10.13474253957003</v>
+        <v>12.672</v>
       </c>
     </row>
     <row r="68">
@@ -5127,10 +5115,10 @@
         <v>1.31</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3750684147760738</v>
+        <v>0.4892</v>
       </c>
       <c r="J68" t="n">
-        <v>9.001641954625772</v>
+        <v>11.7408</v>
       </c>
     </row>
     <row r="69">
@@ -5167,10 +5155,10 @@
         <v>1.12</v>
       </c>
       <c r="I69" t="n">
-        <v>0.09038696385803807</v>
+        <v>0.1934</v>
       </c>
       <c r="J69" t="n">
-        <v>2.169287132592914</v>
+        <v>4.6416</v>
       </c>
     </row>
     <row r="70">
@@ -5207,10 +5195,10 @@
         <v>0.99</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.07929195289951921</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.903006869588461</v>
+        <v>-2.1576</v>
       </c>
     </row>
     <row r="71">
@@ -5247,10 +5235,10 @@
         <v>0.92</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1650624709167999</v>
+        <v>-0.2288</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.961499302003197</v>
+        <v>-5.4912</v>
       </c>
     </row>
     <row r="72">
@@ -5287,10 +5275,10 @@
         <v>1.64</v>
       </c>
       <c r="I72" t="n">
-        <v>1.032217348728268</v>
+        <v>1.5206</v>
       </c>
       <c r="J72" t="n">
-        <v>22.70878167202189</v>
+        <v>33.4532</v>
       </c>
     </row>
     <row r="73">
@@ -5327,10 +5315,10 @@
         <v>1.25</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3949003281952206</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>8.687807220294854</v>
+        <v>15.5122</v>
       </c>
     </row>
     <row r="74">
@@ -5367,10 +5355,10 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2323662137932864</v>
+        <v>0.4336</v>
       </c>
       <c r="J74" t="n">
-        <v>5.1120567034523</v>
+        <v>9.539199999999999</v>
       </c>
     </row>
     <row r="75">
@@ -5407,10 +5395,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.006046437272737085</v>
+        <v>-0.1008</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.1330216200002159</v>
+        <v>-2.2176</v>
       </c>
     </row>
     <row r="76">
@@ -5447,10 +5435,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3451220598880136</v>
+        <v>-0.9869</v>
       </c>
       <c r="J76" t="n">
-        <v>-7.592685317536299</v>
+        <v>-21.7118</v>
       </c>
     </row>
     <row r="77">
@@ -5487,10 +5475,10 @@
         <v>1.26</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2343186387980206</v>
+        <v>0.4782</v>
       </c>
       <c r="J77" t="n">
-        <v>5.155010053556453</v>
+        <v>10.5204</v>
       </c>
     </row>
     <row r="78">
@@ -5527,10 +5515,10 @@
         <v>1.02</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1045447318962784</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.299984101718125</v>
+        <v>1.848</v>
       </c>
     </row>
     <row r="79">
@@ -5567,10 +5555,10 @@
         <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1279101789495145</v>
+        <v>0.0221</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.814023936889319</v>
+        <v>0.4862</v>
       </c>
     </row>
     <row r="80">
@@ -5607,10 +5595,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2621289699368256</v>
+        <v>-0.2512</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.766837338610164</v>
+        <v>-5.5264</v>
       </c>
     </row>
     <row r="81">
@@ -5647,10 +5635,10 @@
         <v>0.68</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5051929615361289</v>
+        <v>-0.5403</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.11424515379484</v>
+        <v>-11.8866</v>
       </c>
     </row>
     <row r="82">
@@ -5687,10 +5675,10 @@
         <v>1.75</v>
       </c>
       <c r="I82" t="n">
-        <v>1.162282248579921</v>
+        <v>1.7015</v>
       </c>
       <c r="J82" t="n">
-        <v>25.57020946875826</v>
+        <v>37.433</v>
       </c>
     </row>
     <row r="83">
@@ -5727,10 +5715,10 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3731615856903446</v>
+        <v>0.715</v>
       </c>
       <c r="J83" t="n">
-        <v>8.209554885187581</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="84">
@@ -5767,10 +5755,10 @@
         <v>1.23</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3227404457175278</v>
+        <v>0.6401</v>
       </c>
       <c r="J84" t="n">
-        <v>7.100289805785612</v>
+        <v>14.0822</v>
       </c>
     </row>
     <row r="85">
@@ -5807,10 +5795,10 @@
         <v>0.83</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2112036002452342</v>
+        <v>-0.649</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.646479205395152</v>
+        <v>-14.278</v>
       </c>
     </row>
     <row r="86">
@@ -5847,10 +5835,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2750486904831412</v>
+        <v>-0.7922</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.051071190629107</v>
+        <v>-17.4284</v>
       </c>
     </row>
     <row r="87">
@@ -5887,10 +5875,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.06344563488012446</v>
+        <v>0.3438</v>
       </c>
       <c r="J87" t="n">
-        <v>1.395803967362738</v>
+        <v>7.5636</v>
       </c>
     </row>
     <row r="88">
@@ -5927,10 +5915,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.01927299109792105</v>
+        <v>0.2978</v>
       </c>
       <c r="J88" t="n">
-        <v>0.4240058041542631</v>
+        <v>6.5516</v>
       </c>
     </row>
     <row r="89">
@@ -5967,10 +5955,10 @@
         <v>0.9</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2635917954251079</v>
+        <v>-0.224</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.799019499352373</v>
+        <v>-4.928</v>
       </c>
     </row>
     <row r="90">
@@ -6007,10 +5995,10 @@
         <v>0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3002512845694397</v>
+        <v>-0.274</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.605528260527674</v>
+        <v>-6.028</v>
       </c>
     </row>
     <row r="91">
@@ -6047,10 +6035,10 @@
         <v>0.86</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3125145158665817</v>
+        <v>-0.29</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.875319349064797</v>
+        <v>-6.38</v>
       </c>
     </row>
     <row r="92">
@@ -6087,10 +6075,10 @@
         <v>1.34</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2509481195411716</v>
+        <v>0.5756</v>
       </c>
       <c r="J92" t="n">
-        <v>5.269910510364604</v>
+        <v>12.0876</v>
       </c>
     </row>
     <row r="93">
@@ -6127,10 +6115,10 @@
         <v>1.18</v>
       </c>
       <c r="I93" t="n">
-        <v>0.04366437620491824</v>
+        <v>0.3587</v>
       </c>
       <c r="J93" t="n">
-        <v>0.916951900303283</v>
+        <v>7.5327</v>
       </c>
     </row>
     <row r="94">
@@ -6167,10 +6155,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.184521147732512</v>
+        <v>-0.0607</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.874944102382753</v>
+        <v>-1.2747</v>
       </c>
     </row>
     <row r="95">
@@ -6207,10 +6195,10 @@
         <v>0.86</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.322645774456544</v>
+        <v>-0.29</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.775561263587424</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="96">
@@ -6247,10 +6235,10 @@
         <v>0.58</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6474615054026928</v>
+        <v>-0.6683</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.59669161345655</v>
+        <v>-14.0343</v>
       </c>
     </row>
     <row r="97">
@@ -6287,10 +6275,10 @@
         <v>1.51</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6741447588364279</v>
+        <v>1.2662</v>
       </c>
       <c r="J97" t="n">
-        <v>14.15703993556498</v>
+        <v>26.5902</v>
       </c>
     </row>
     <row r="98">
@@ -6327,10 +6315,10 @@
         <v>1.14</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1890674439270574</v>
+        <v>0.385</v>
       </c>
       <c r="J98" t="n">
-        <v>3.970416322468205</v>
+        <v>8.085000000000001</v>
       </c>
     </row>
     <row r="99">
@@ -6367,10 +6355,10 @@
         <v>1.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1254454882790635</v>
+        <v>0.2325</v>
       </c>
       <c r="J99" t="n">
-        <v>2.634355253860333</v>
+        <v>4.8825</v>
       </c>
     </row>
     <row r="100">
@@ -6407,10 +6395,10 @@
         <v>1.04</v>
       </c>
       <c r="I100" t="n">
-        <v>0.05844177700111152</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J100" t="n">
-        <v>1.227277317023342</v>
+        <v>1.4994</v>
       </c>
     </row>
     <row r="101">
@@ -6447,10 +6435,10 @@
         <v>0.98</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.01623173049440026</v>
+        <v>-0.2055</v>
       </c>
       <c r="J101" t="n">
-        <v>-0.3408663403824054</v>
+        <v>-4.3155</v>
       </c>
     </row>
     <row r="102">
@@ -6487,10 +6475,10 @@
         <v>1.06</v>
       </c>
       <c r="I102" t="n">
-        <v>0.04576816536940426</v>
+        <v>0.2042</v>
       </c>
       <c r="J102" t="n">
-        <v>1.052667803496298</v>
+        <v>4.6966</v>
       </c>
     </row>
     <row r="103">
@@ -6527,10 +6515,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.09019035259073896</v>
+        <v>-0.063</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.074378109586996</v>
+        <v>-1.449</v>
       </c>
     </row>
     <row r="104">
@@ -6567,10 +6555,10 @@
         <v>0.8</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2539678469336707</v>
+        <v>-0.3479</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.841260479474426</v>
+        <v>-8.0017</v>
       </c>
     </row>
     <row r="105">
@@ -6607,10 +6595,10 @@
         <v>0.8</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2539678469336707</v>
+        <v>-0.3479</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.841260479474426</v>
+        <v>-8.0017</v>
       </c>
     </row>
     <row r="106">
@@ -6647,10 +6635,10 @@
         <v>0.78</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.277397288132046</v>
+        <v>-0.3787</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.380137627037058</v>
+        <v>-8.710100000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6687,10 +6675,10 @@
         <v>1.31</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3940421621181368</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="J107" t="n">
-        <v>9.062969728717146</v>
+        <v>19.3476</v>
       </c>
     </row>
     <row r="108">
@@ -6727,10 +6715,10 @@
         <v>1.21</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2603585374506894</v>
+        <v>0.5975</v>
       </c>
       <c r="J108" t="n">
-        <v>5.988246361365856</v>
+        <v>13.7425</v>
       </c>
     </row>
     <row r="109">
@@ -6767,10 +6755,10 @@
         <v>1.17</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2098732644621091</v>
+        <v>0.4863</v>
       </c>
       <c r="J109" t="n">
-        <v>4.827085082628509</v>
+        <v>11.1849</v>
       </c>
     </row>
     <row r="110">
@@ -6807,10 +6795,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.05942647477964697</v>
+        <v>0.1045</v>
       </c>
       <c r="J110" t="n">
-        <v>1.36680891993188</v>
+        <v>2.4035</v>
       </c>
     </row>
     <row r="111">
@@ -6847,10 +6835,10 @@
         <v>1.03</v>
       </c>
       <c r="I111" t="n">
-        <v>0.03206123205922584</v>
+        <v>0.0347</v>
       </c>
       <c r="J111" t="n">
-        <v>0.7374083373621944</v>
+        <v>0.7981</v>
       </c>
     </row>
     <row r="112">
@@ -6887,10 +6875,10 @@
         <v>1.74</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9911016432616164</v>
+        <v>0.8959</v>
       </c>
       <c r="J112" t="n">
-        <v>16.84872793544748</v>
+        <v>15.2303</v>
       </c>
     </row>
     <row r="113">
@@ -6927,10 +6915,10 @@
         <v>1.68</v>
       </c>
       <c r="I113" t="n">
-        <v>0.904675465943065</v>
+        <v>0.8324</v>
       </c>
       <c r="J113" t="n">
-        <v>15.37948292103211</v>
+        <v>14.1508</v>
       </c>
     </row>
     <row r="114">
@@ -6967,10 +6955,10 @@
         <v>1.49</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6295948311616326</v>
+        <v>0.6125</v>
       </c>
       <c r="J114" t="n">
-        <v>10.70311212974775</v>
+        <v>10.4125</v>
       </c>
     </row>
     <row r="115">
@@ -7007,10 +6995,10 @@
         <v>1.39</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4972168281395483</v>
+        <v>0.473</v>
       </c>
       <c r="J115" t="n">
-        <v>8.45268607837232</v>
+        <v>8.041</v>
       </c>
     </row>
     <row r="116">
@@ -7047,10 +7035,10 @@
         <v>1.02</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.03654156598257068</v>
+        <v>-0.0564</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.6212066217037014</v>
+        <v>-0.9588</v>
       </c>
     </row>
     <row r="117">
@@ -7087,10 +7075,10 @@
         <v>1.16</v>
       </c>
       <c r="I117" t="n">
-        <v>0.009487448459982993</v>
+        <v>0.4221</v>
       </c>
       <c r="J117" t="n">
-        <v>0.1612866238197109</v>
+        <v>7.1757</v>
       </c>
     </row>
     <row r="118">
@@ -7127,10 +7115,10 @@
         <v>0.92</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.2257402793911149</v>
+        <v>-0.0625</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.837584749648953</v>
+        <v>-1.0625</v>
       </c>
     </row>
     <row r="119">
@@ -7167,10 +7155,10 @@
         <v>0.64</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4793991569426892</v>
+        <v>-0.538</v>
       </c>
       <c r="J119" t="n">
-        <v>-8.149785668025716</v>
+        <v>-9.146000000000001</v>
       </c>
     </row>
     <row r="120">
@@ -7207,10 +7195,10 @@
         <v>0.55</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.5637513068080654</v>
+        <v>-0.6602</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.583772215737111</v>
+        <v>-11.2234</v>
       </c>
     </row>
     <row r="121">
@@ -7247,10 +7235,10 @@
         <v>0.48</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6284373823123545</v>
+        <v>-0.7493</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.68343549931003</v>
+        <v>-12.7381</v>
       </c>
     </row>
     <row r="122">
@@ -7287,10 +7275,10 @@
         <v>1.62</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7660435360329995</v>
+        <v>0.9112</v>
       </c>
       <c r="J122" t="n">
-        <v>17.61900132875899</v>
+        <v>20.9576</v>
       </c>
     </row>
     <row r="123">
@@ -7327,10 +7315,10 @@
         <v>1.16</v>
       </c>
       <c r="I123" t="n">
-        <v>0.09124224476465548</v>
+        <v>0.3381</v>
       </c>
       <c r="J123" t="n">
-        <v>2.098571629587076</v>
+        <v>7.7763</v>
       </c>
     </row>
     <row r="124">
@@ -7367,10 +7355,10 @@
         <v>0.86</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2162525349297587</v>
+        <v>-0.2821</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.973808303384451</v>
+        <v>-6.4883</v>
       </c>
     </row>
     <row r="125">
@@ -7407,10 +7395,10 @@
         <v>0.59</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4637948030508328</v>
+        <v>-0.6523</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.66728047016916</v>
+        <v>-15.0029</v>
       </c>
     </row>
     <row r="126">
@@ -7447,10 +7435,10 @@
         <v>0.58</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4725609323399281</v>
+        <v>-0.6645</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.86890144381834</v>
+        <v>-15.2835</v>
       </c>
     </row>
     <row r="127">
@@ -7487,10 +7475,10 @@
         <v>1.65</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8306918265862808</v>
+        <v>1.5056</v>
       </c>
       <c r="J127" t="n">
-        <v>19.10591201148446</v>
+        <v>34.6288</v>
       </c>
     </row>
     <row r="128">
@@ -7527,10 +7515,10 @@
         <v>1.38</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4433795375879712</v>
+        <v>0.9661</v>
       </c>
       <c r="J128" t="n">
-        <v>10.19772936452334</v>
+        <v>22.2203</v>
       </c>
     </row>
     <row r="129">
@@ -7567,10 +7555,10 @@
         <v>1.33</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3686671343883373</v>
+        <v>0.8546</v>
       </c>
       <c r="J129" t="n">
-        <v>8.479344090931757</v>
+        <v>19.6558</v>
       </c>
     </row>
     <row r="130">
@@ -7607,10 +7595,10 @@
         <v>0.96</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1096532993811322</v>
+        <v>-0.2996</v>
       </c>
       <c r="J130" t="n">
-        <v>-2.52202588576604</v>
+        <v>-6.8908</v>
       </c>
     </row>
     <row r="131">
@@ -7647,10 +7635,10 @@
         <v>0.74</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3207860449403319</v>
+        <v>-0.8702</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.378079033627633</v>
+        <v>-20.0146</v>
       </c>
     </row>
     <row r="132">
@@ -7687,10 +7675,10 @@
         <v>1.62</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6281939136033584</v>
+        <v>0.9483</v>
       </c>
       <c r="J132" t="n">
-        <v>11.93568435846381</v>
+        <v>18.0177</v>
       </c>
     </row>
     <row r="133">
@@ -7727,10 +7715,10 @@
         <v>0.96</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.20603229299934</v>
+        <v>-0.0371</v>
       </c>
       <c r="J133" t="n">
-        <v>-3.91461356698746</v>
+        <v>-0.7049</v>
       </c>
     </row>
     <row r="134">
@@ -7767,10 +7755,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.4398315169788795</v>
+        <v>-0.5042</v>
       </c>
       <c r="J134" t="n">
-        <v>-8.35679882259871</v>
+        <v>-9.579800000000001</v>
       </c>
     </row>
     <row r="135">
@@ -7807,10 +7795,10 @@
         <v>0.62</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5024998513655843</v>
+        <v>-0.5972</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.547497175946102</v>
+        <v>-11.3468</v>
       </c>
     </row>
     <row r="136">
@@ -7847,10 +7835,10 @@
         <v>0.44</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6573064148397292</v>
+        <v>-0.8166</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.48882188195485</v>
+        <v>-15.5154</v>
       </c>
     </row>
     <row r="137">
@@ -7887,10 +7875,10 @@
         <v>2.61</v>
       </c>
       <c r="I137" t="n">
-        <v>1.913511571720888</v>
+        <v>2.4041</v>
       </c>
       <c r="J137" t="n">
-        <v>36.35671986269688</v>
+        <v>45.6779</v>
       </c>
     </row>
     <row r="138">
@@ -7927,10 +7915,10 @@
         <v>1.72</v>
       </c>
       <c r="I138" t="n">
-        <v>0.8685782166498336</v>
+        <v>1.5384</v>
       </c>
       <c r="J138" t="n">
-        <v>16.50298611634684</v>
+        <v>29.2296</v>
       </c>
     </row>
     <row r="139">
@@ -7967,10 +7955,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.04074100405819024</v>
+        <v>0.0723</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.7740790771056146</v>
+        <v>1.3737</v>
       </c>
     </row>
     <row r="140">
@@ -8007,10 +7995,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2278502074112157</v>
+        <v>-0.607</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.329153940813098</v>
+        <v>-11.533</v>
       </c>
     </row>
     <row r="141">
@@ -8047,10 +8035,10 @@
         <v>0.86</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2358695607535383</v>
+        <v>-0.632</v>
       </c>
       <c r="J141" t="n">
-        <v>-4.481521654317228</v>
+        <v>-12.008</v>
       </c>
     </row>
     <row r="142">
@@ -8087,10 +8075,10 @@
         <v>1.01</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.1219096494735005</v>
+        <v>0.1475</v>
       </c>
       <c r="J142" t="n">
-        <v>-2.072464041049508</v>
+        <v>2.5075</v>
       </c>
     </row>
     <row r="143">
@@ -8127,10 +8115,10 @@
         <v>0.87</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.271226917618433</v>
+        <v>-0.1533</v>
       </c>
       <c r="J143" t="n">
-        <v>-4.610857599513361</v>
+        <v>-2.6061</v>
       </c>
     </row>
     <row r="144">
@@ -8167,10 +8155,10 @@
         <v>0.77</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3718223799018062</v>
+        <v>-0.3237</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.320980458330705</v>
+        <v>-5.5029</v>
       </c>
     </row>
     <row r="145">
@@ -8207,10 +8195,10 @@
         <v>0.63</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5067891981971304</v>
+        <v>-0.5548</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.615416369351218</v>
+        <v>-9.4316</v>
       </c>
     </row>
     <row r="146">
@@ -8247,10 +8235,10 @@
         <v>0.51</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6295579364669663</v>
+        <v>-0.7134</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.70248491993843</v>
+        <v>-12.1278</v>
       </c>
     </row>
     <row r="147">
@@ -8287,10 +8275,10 @@
         <v>2.23</v>
       </c>
       <c r="I147" t="n">
-        <v>1.121499807808762</v>
+        <v>2.0593</v>
       </c>
       <c r="J147" t="n">
-        <v>19.06549673274895</v>
+        <v>35.0081</v>
       </c>
     </row>
     <row r="148">
@@ -8327,10 +8315,10 @@
         <v>1.48</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4745423327687114</v>
+        <v>1.1059</v>
       </c>
       <c r="J148" t="n">
-        <v>8.067219657068094</v>
+        <v>18.8003</v>
       </c>
     </row>
     <row r="149">
@@ -8367,10 +8355,10 @@
         <v>1.21</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2231056167427233</v>
+        <v>0.4575</v>
       </c>
       <c r="J149" t="n">
-        <v>3.792795484626297</v>
+        <v>7.7775</v>
       </c>
     </row>
     <row r="150">
@@ -8407,10 +8395,10 @@
         <v>1.08</v>
       </c>
       <c r="I150" t="n">
-        <v>0.09256110942004817</v>
+        <v>0.1208</v>
       </c>
       <c r="J150" t="n">
-        <v>1.573538860140819</v>
+        <v>2.0536</v>
       </c>
     </row>
     <row r="151">
@@ -8447,10 +8435,10 @@
         <v>0.77</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2427048798459714</v>
+        <v>-0.8303</v>
       </c>
       <c r="J151" t="n">
-        <v>-4.125982957381513</v>
+        <v>-14.1151</v>
       </c>
     </row>
     <row r="152">
@@ -8487,10 +8475,10 @@
         <v>1.17</v>
       </c>
       <c r="I152" t="n">
-        <v>0.1189395435071558</v>
+        <v>0.3445</v>
       </c>
       <c r="J152" t="n">
-        <v>2.854549044171739</v>
+        <v>8.268000000000001</v>
       </c>
     </row>
     <row r="153">
@@ -8527,10 +8515,10 @@
         <v>0.96</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.09648794014370007</v>
+        <v>-0.1079</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.315710563448802</v>
+        <v>-2.5896</v>
       </c>
     </row>
     <row r="154">
@@ -8567,10 +8555,10 @@
         <v>0.95</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1065355097734259</v>
+        <v>-0.1294</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.556852234562222</v>
+        <v>-3.1056</v>
       </c>
     </row>
     <row r="155">
@@ -8607,10 +8595,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1168078339048972</v>
+        <v>-0.1496</v>
       </c>
       <c r="J155" t="n">
-        <v>-2.803388013717532</v>
+        <v>-3.5904</v>
       </c>
     </row>
     <row r="156">
@@ -8647,10 +8635,10 @@
         <v>0.91</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.148451548121387</v>
+        <v>-0.2057</v>
       </c>
       <c r="J156" t="n">
-        <v>-3.562837154913288</v>
+        <v>-4.9368</v>
       </c>
     </row>
     <row r="157">
@@ -8687,10 +8675,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.32243260706563</v>
+        <v>0.947</v>
       </c>
       <c r="J157" t="n">
-        <v>7.738382569575121</v>
+        <v>22.728</v>
       </c>
     </row>
     <row r="158">
@@ -8727,10 +8715,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1098217194369009</v>
+        <v>0.4259</v>
       </c>
       <c r="J158" t="n">
-        <v>2.635721266485621</v>
+        <v>10.2216</v>
       </c>
     </row>
     <row r="159">
@@ -8767,10 +8755,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1098217194369009</v>
+        <v>0.4259</v>
       </c>
       <c r="J159" t="n">
-        <v>2.635721266485621</v>
+        <v>10.2216</v>
       </c>
     </row>
     <row r="160">
@@ -8807,10 +8795,10 @@
         <v>1.06</v>
       </c>
       <c r="I160" t="n">
-        <v>0.0481851301342984</v>
+        <v>0.1822</v>
       </c>
       <c r="J160" t="n">
-        <v>1.156443123223162</v>
+        <v>4.3728</v>
       </c>
     </row>
     <row r="161">
@@ -8847,10 +8835,10 @@
         <v>0.76</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2926303029780314</v>
+        <v>-0.7929</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.023127271472754</v>
+        <v>-19.0296</v>
       </c>
     </row>
     <row r="162">
@@ -8887,10 +8875,10 @@
         <v>1.85</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9056110261620092</v>
+        <v>1.7859</v>
       </c>
       <c r="J162" t="n">
-        <v>15.39538744475416</v>
+        <v>30.3603</v>
       </c>
     </row>
     <row r="163">
@@ -8927,10 +8915,10 @@
         <v>1.62</v>
       </c>
       <c r="I163" t="n">
-        <v>0.66312533191957</v>
+        <v>1.3693</v>
       </c>
       <c r="J163" t="n">
-        <v>11.27313064263269</v>
+        <v>23.2781</v>
       </c>
     </row>
     <row r="164">
@@ -8967,10 +8955,10 @@
         <v>1.28</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2975146291909069</v>
+        <v>0.61</v>
       </c>
       <c r="J164" t="n">
-        <v>5.057748696245417</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="165">
@@ -9007,10 +8995,10 @@
         <v>1.17</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1707186012520996</v>
+        <v>0.3481</v>
       </c>
       <c r="J165" t="n">
-        <v>2.902216221285693</v>
+        <v>5.9177</v>
       </c>
     </row>
     <row r="166">
@@ -9047,10 +9035,10 @@
         <v>1.01</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.01161067568290333</v>
+        <v>-0.121</v>
       </c>
       <c r="J166" t="n">
-        <v>-0.1973814866093565</v>
+        <v>-2.057</v>
       </c>
     </row>
     <row r="167">
@@ -9087,10 +9075,10 @@
         <v>1.5</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3893623649004408</v>
+        <v>0.8421</v>
       </c>
       <c r="J167" t="n">
-        <v>6.619160203307494</v>
+        <v>14.3157</v>
       </c>
     </row>
     <row r="168">
@@ -9127,10 +9115,10 @@
         <v>0.85</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2896794402682875</v>
+        <v>-0.2073</v>
       </c>
       <c r="J168" t="n">
-        <v>-4.924550484560887</v>
+        <v>-3.5241</v>
       </c>
     </row>
     <row r="169">
@@ -9167,10 +9155,10 @@
         <v>0.64</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4686194022934405</v>
+        <v>-0.5536</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.966529838988489</v>
+        <v>-9.411199999999999</v>
       </c>
     </row>
     <row r="170">
@@ -9207,10 +9195,10 @@
         <v>0.58</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5224404881001544</v>
+        <v>-0.6333</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.881488297702624</v>
+        <v>-10.7661</v>
       </c>
     </row>
     <row r="171">
@@ -9247,10 +9235,10 @@
         <v>0.42</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6615195844763178</v>
+        <v>-0.8304</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.2458329360974</v>
+        <v>-14.1168</v>
       </c>
     </row>
     <row r="172">
@@ -9287,10 +9275,10 @@
         <v>1.39</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3245901525635637</v>
+        <v>0.6418</v>
       </c>
       <c r="J172" t="n">
-        <v>7.140983356398401</v>
+        <v>14.1196</v>
       </c>
     </row>
     <row r="173">
@@ -9327,10 +9315,10 @@
         <v>1.03</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.07669805412574994</v>
+        <v>0.1037</v>
       </c>
       <c r="J173" t="n">
-        <v>-1.687357190766499</v>
+        <v>2.2814</v>
       </c>
     </row>
     <row r="174">
@@ -9367,10 +9355,10 @@
         <v>0.91</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1898171930523156</v>
+        <v>-0.2021</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.175978247150942</v>
+        <v>-4.4462</v>
       </c>
     </row>
     <row r="175">
@@ -9407,10 +9395,10 @@
         <v>0.87</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2311500318513205</v>
+        <v>-0.2703</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.085300700729052</v>
+        <v>-5.9466</v>
       </c>
     </row>
     <row r="176">
@@ -9447,10 +9435,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4274835606332152</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.404638333930734</v>
+        <v>-11.9196</v>
       </c>
     </row>
     <row r="177">
@@ -9487,10 +9475,10 @@
         <v>1.67</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8149304008143097</v>
+        <v>0.9131</v>
       </c>
       <c r="J177" t="n">
-        <v>17.92846881791481</v>
+        <v>20.0882</v>
       </c>
     </row>
     <row r="178">
@@ -9527,10 +9515,10 @@
         <v>1.31</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3869454083895062</v>
+        <v>0.4943</v>
       </c>
       <c r="J178" t="n">
-        <v>8.512798984569136</v>
+        <v>10.8746</v>
       </c>
     </row>
     <row r="179">
@@ -9567,10 +9555,10 @@
         <v>1.02</v>
       </c>
       <c r="I179" t="n">
-        <v>0.03633554381597327</v>
+        <v>0.0074</v>
       </c>
       <c r="J179" t="n">
-        <v>0.7993819639514118</v>
+        <v>0.1628</v>
       </c>
     </row>
     <row r="180">
@@ -9607,10 +9595,10 @@
         <v>0.9</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0822530233755536</v>
+        <v>-0.2586</v>
       </c>
       <c r="J180" t="n">
-        <v>-1.809566514262179</v>
+        <v>-5.6892</v>
       </c>
     </row>
     <row r="181">
@@ -9647,10 +9635,10 @@
         <v>0.7</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2681146308358645</v>
+        <v>-0.5391</v>
       </c>
       <c r="J181" t="n">
-        <v>-5.898521878389018</v>
+        <v>-11.8602</v>
       </c>
     </row>
     <row r="182">
@@ -9687,10 +9675,10 @@
         <v>1.49</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5635385158616218</v>
+        <v>1.1542</v>
       </c>
       <c r="J182" t="n">
-        <v>10.14369328550919</v>
+        <v>20.7756</v>
       </c>
     </row>
     <row r="183">
@@ -9727,10 +9715,10 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4734959341482347</v>
+        <v>0.9859</v>
       </c>
       <c r="J183" t="n">
-        <v>8.522926814668224</v>
+        <v>17.7462</v>
       </c>
     </row>
     <row r="184">
@@ -9767,10 +9755,10 @@
         <v>1.32</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3748920076744197</v>
+        <v>0.7769</v>
       </c>
       <c r="J184" t="n">
-        <v>6.748056138139554</v>
+        <v>13.9842</v>
       </c>
     </row>
     <row r="185">
@@ -9807,10 +9795,10 @@
         <v>1.26</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3167223110821509</v>
+        <v>0.6078</v>
       </c>
       <c r="J185" t="n">
-        <v>5.701001599478715</v>
+        <v>10.9404</v>
       </c>
     </row>
     <row r="186">
@@ -9847,10 +9835,10 @@
         <v>1.01</v>
       </c>
       <c r="I186" t="n">
-        <v>0.02816259221034198</v>
+        <v>-0.0974</v>
       </c>
       <c r="J186" t="n">
-        <v>0.5069266597861557</v>
+        <v>-1.7532</v>
       </c>
     </row>
     <row r="187">
@@ -9887,10 +9875,10 @@
         <v>1.08</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.04159545809578458</v>
+        <v>0.2668</v>
       </c>
       <c r="J187" t="n">
-        <v>-0.7487182457241224</v>
+        <v>4.8024</v>
       </c>
     </row>
     <row r="188">
@@ -9927,10 +9915,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.04159545809578458</v>
+        <v>0.2668</v>
       </c>
       <c r="J188" t="n">
-        <v>-0.7487182457241224</v>
+        <v>4.8024</v>
       </c>
     </row>
     <row r="189">
@@ -9967,10 +9955,10 @@
         <v>0.73</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3559782079241722</v>
+        <v>-0.4298</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.407607742635099</v>
+        <v>-7.7364</v>
       </c>
     </row>
     <row r="190">
@@ -10007,10 +9995,10 @@
         <v>0.71</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3741037134886299</v>
+        <v>-0.4594</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.733866842795338</v>
+        <v>-8.2692</v>
       </c>
     </row>
     <row r="191">
@@ -10047,10 +10035,10 @@
         <v>0.46</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5978622825722908</v>
+        <v>-0.7851</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.76152108630123</v>
+        <v>-14.1318</v>
       </c>
     </row>
     <row r="192">
@@ -10087,10 +10075,10 @@
         <v>1.19</v>
       </c>
       <c r="I192" t="n">
-        <v>0.05125319291818695</v>
+        <v>0.4438</v>
       </c>
       <c r="J192" t="n">
-        <v>0.9225574725273652</v>
+        <v>7.9884</v>
       </c>
     </row>
     <row r="193">
@@ -10127,10 +10115,10 @@
         <v>0.84</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.3295234229984716</v>
+        <v>-0.2269</v>
       </c>
       <c r="J193" t="n">
-        <v>-5.931421613972489</v>
+        <v>-4.0842</v>
       </c>
     </row>
     <row r="194">
@@ -10167,10 +10155,10 @@
         <v>0.77</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3941078630101368</v>
+        <v>-0.3621</v>
       </c>
       <c r="J194" t="n">
-        <v>-7.093941534182462</v>
+        <v>-6.5178</v>
       </c>
     </row>
     <row r="195">
@@ -10207,10 +10195,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4773701087596342</v>
+        <v>-0.4849</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.592661957673416</v>
+        <v>-8.728199999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10247,10 +10235,10 @@
         <v>0.52</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6565487879846188</v>
+        <v>-0.7103</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.81787818372314</v>
+        <v>-12.7854</v>
       </c>
     </row>
     <row r="197">
@@ -10287,10 +10275,10 @@
         <v>1.94</v>
       </c>
       <c r="I197" t="n">
-        <v>1.012921952089319</v>
+        <v>1.9271</v>
       </c>
       <c r="J197" t="n">
-        <v>18.23259513760774</v>
+        <v>34.6878</v>
       </c>
     </row>
     <row r="198">
@@ -10327,10 +10315,10 @@
         <v>1.53</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5658823715352086</v>
+        <v>1.1966</v>
       </c>
       <c r="J198" t="n">
-        <v>10.18588268763375</v>
+        <v>21.5388</v>
       </c>
     </row>
     <row r="199">
@@ -10367,10 +10355,10 @@
         <v>1.21</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2060788853339029</v>
+        <v>0.4483</v>
       </c>
       <c r="J199" t="n">
-        <v>3.709419936010252</v>
+        <v>8.0694</v>
       </c>
     </row>
     <row r="200">
@@ -10407,10 +10395,10 @@
         <v>1.14</v>
       </c>
       <c r="I200" t="n">
-        <v>0.1218887967385406</v>
+        <v>0.2753</v>
       </c>
       <c r="J200" t="n">
-        <v>2.193998341293732</v>
+        <v>4.9554</v>
       </c>
     </row>
     <row r="201">
@@ -10447,10 +10435,10 @@
         <v>1.07</v>
       </c>
       <c r="I201" t="n">
-        <v>0.03803776332106802</v>
+        <v>0.0849</v>
       </c>
       <c r="J201" t="n">
-        <v>0.6846797397792244</v>
+        <v>1.5282</v>
       </c>
     </row>
     <row r="202">
@@ -10487,10 +10475,10 @@
         <v>1.53</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5505612027536793</v>
+        <v>0.7516</v>
       </c>
       <c r="J202" t="n">
-        <v>12.11234646058094</v>
+        <v>16.5352</v>
       </c>
     </row>
     <row r="203">
@@ -10527,10 +10515,10 @@
         <v>1.43</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4463412377097701</v>
+        <v>0.6354</v>
       </c>
       <c r="J203" t="n">
-        <v>9.819507229614942</v>
+        <v>13.9788</v>
       </c>
     </row>
     <row r="204">
@@ -10567,10 +10555,10 @@
         <v>1.2</v>
       </c>
       <c r="I204" t="n">
-        <v>0.197257122098575</v>
+        <v>0.3306</v>
       </c>
       <c r="J204" t="n">
-        <v>4.33965668616865</v>
+        <v>7.2732</v>
       </c>
     </row>
     <row r="205">
@@ -10607,10 +10595,10 @@
         <v>1.04</v>
       </c>
       <c r="I205" t="n">
-        <v>0.03480554369773534</v>
+        <v>0.0421</v>
       </c>
       <c r="J205" t="n">
-        <v>0.7657219613501773</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="206">
@@ -10647,10 +10635,10 @@
         <v>0.54</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4968591629634856</v>
+        <v>-0.7331</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.93090158519668</v>
+        <v>-16.1282</v>
       </c>
     </row>
     <row r="207">
@@ -10687,10 +10675,10 @@
         <v>1.21</v>
       </c>
       <c r="I207" t="n">
-        <v>0.1209589849207151</v>
+        <v>0.4098</v>
       </c>
       <c r="J207" t="n">
-        <v>2.661097668255733</v>
+        <v>9.015599999999999</v>
       </c>
     </row>
     <row r="208">
@@ -10727,10 +10715,10 @@
         <v>1.2</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1089891804082614</v>
+        <v>0.3956</v>
       </c>
       <c r="J208" t="n">
-        <v>2.397761968981751</v>
+        <v>8.703200000000001</v>
       </c>
     </row>
     <row r="209">
@@ -10767,10 +10755,10 @@
         <v>0.95</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1460740441393941</v>
+        <v>-0.119</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.213628971066671</v>
+        <v>-2.618</v>
       </c>
     </row>
     <row r="210">
@@ -10807,10 +10795,10 @@
         <v>0.82</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2723812075422992</v>
+        <v>-0.3456</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.992386565930583</v>
+        <v>-7.6032</v>
       </c>
     </row>
     <row r="211">
@@ -10847,10 +10835,10 @@
         <v>0.65</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.43888411245779</v>
+        <v>-0.5784</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.65545047407138</v>
+        <v>-12.7248</v>
       </c>
     </row>
     <row r="212">
@@ -10887,10 +10875,10 @@
         <v>1.24</v>
       </c>
       <c r="I212" t="n">
-        <v>0.218109509677599</v>
+        <v>0.4845</v>
       </c>
       <c r="J212" t="n">
-        <v>5.016518722584776</v>
+        <v>11.1435</v>
       </c>
     </row>
     <row r="213">
@@ -10927,10 +10915,10 @@
         <v>0.98</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.06147630294245741</v>
+        <v>0.0029</v>
       </c>
       <c r="J213" t="n">
-        <v>-1.413954967676521</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="214">
@@ -10967,10 +10955,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2361617965137889</v>
+        <v>-0.3313</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.431721319817144</v>
+        <v>-7.6199</v>
       </c>
     </row>
     <row r="215">
@@ -11007,10 +10995,10 @@
         <v>0.72</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3344520495446903</v>
+        <v>-0.4654</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.692397139527877</v>
+        <v>-10.7042</v>
       </c>
     </row>
     <row r="216">
@@ -11047,10 +11035,10 @@
         <v>0.63</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4322842233776377</v>
+        <v>-0.5864</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.942537137685667</v>
+        <v>-13.4872</v>
       </c>
     </row>
     <row r="217">
@@ -11087,10 +11075,10 @@
         <v>1.54</v>
       </c>
       <c r="I217" t="n">
-        <v>0.590034526947214</v>
+        <v>1.3063</v>
       </c>
       <c r="J217" t="n">
-        <v>13.57079411978592</v>
+        <v>30.0449</v>
       </c>
     </row>
     <row r="218">
@@ -11127,10 +11115,10 @@
         <v>1.39</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4163260667290786</v>
+        <v>0.9993</v>
       </c>
       <c r="J218" t="n">
-        <v>9.575499534768808</v>
+        <v>22.9839</v>
       </c>
     </row>
     <row r="219">
@@ -11167,10 +11155,10 @@
         <v>1.15</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1429473282880285</v>
+        <v>0.3844</v>
       </c>
       <c r="J219" t="n">
-        <v>3.287788550624656</v>
+        <v>8.841200000000001</v>
       </c>
     </row>
     <row r="220">
@@ -11207,10 +11195,10 @@
         <v>1.05</v>
       </c>
       <c r="I220" t="n">
-        <v>0.02297036870566348</v>
+        <v>0.0877</v>
       </c>
       <c r="J220" t="n">
-        <v>0.52831848023026</v>
+        <v>2.0171</v>
       </c>
     </row>
     <row r="221">
@@ -11247,10 +11235,10 @@
         <v>0.82</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2042361933879805</v>
+        <v>-0.6794</v>
       </c>
       <c r="J221" t="n">
-        <v>-4.697432447923552</v>
+        <v>-15.6262</v>
       </c>
     </row>
     <row r="222">
@@ -11287,10 +11275,10 @@
         <v>1.06</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.1236188538264138</v>
+        <v>0.1884</v>
       </c>
       <c r="J222" t="n">
-        <v>-2.348758222701863</v>
+        <v>3.5796</v>
       </c>
     </row>
     <row r="223">
@@ -11327,10 +11315,10 @@
         <v>0.95</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2473882201694239</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="J223" t="n">
-        <v>-4.700376183219054</v>
+        <v>-1.5694</v>
       </c>
     </row>
     <row r="224">
@@ -11367,10 +11355,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2577996148241655</v>
+        <v>-0.1037</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.898192681659144</v>
+        <v>-1.9703</v>
       </c>
     </row>
     <row r="225">
@@ -11407,10 +11395,10 @@
         <v>0.89</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3052145884637985</v>
+        <v>-0.2131</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.799077180812172</v>
+        <v>-4.0489</v>
       </c>
     </row>
     <row r="226">
@@ -11447,10 +11435,10 @@
         <v>0.75</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4600565721102715</v>
+        <v>-0.4346</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.741074870095158</v>
+        <v>-8.257400000000001</v>
       </c>
     </row>
     <row r="227">
@@ -11487,10 +11475,10 @@
         <v>1.53</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3989085302116037</v>
+        <v>1.2508</v>
       </c>
       <c r="J227" t="n">
-        <v>7.57926207402047</v>
+        <v>23.7652</v>
       </c>
     </row>
     <row r="228">
@@ -11527,10 +11515,10 @@
         <v>1.35</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2583165290903932</v>
+        <v>0.8709</v>
       </c>
       <c r="J228" t="n">
-        <v>4.90801405271747</v>
+        <v>16.5471</v>
       </c>
     </row>
     <row r="229">
@@ -11567,10 +11555,10 @@
         <v>1.24</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1794192011652563</v>
+        <v>0.5793</v>
       </c>
       <c r="J229" t="n">
-        <v>3.408964822139869</v>
+        <v>11.0067</v>
       </c>
     </row>
     <row r="230">
@@ -11607,10 +11595,10 @@
         <v>1.16</v>
       </c>
       <c r="I230" t="n">
-        <v>0.1173778035459237</v>
+        <v>0.3705</v>
       </c>
       <c r="J230" t="n">
-        <v>2.23017826737255</v>
+        <v>7.0395</v>
       </c>
     </row>
     <row r="231">
@@ -11647,10 +11635,10 @@
         <v>1.04</v>
       </c>
       <c r="I231" t="n">
-        <v>0.02032231246708889</v>
+        <v>0.0262</v>
       </c>
       <c r="J231" t="n">
-        <v>0.3861239368746889</v>
+        <v>0.4978</v>
       </c>
     </row>
     <row r="232">
@@ -11687,10 +11675,10 @@
         <v>0.87</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.2782818747095714</v>
+        <v>-0.1044</v>
       </c>
       <c r="J232" t="n">
-        <v>-4.452509995353143</v>
+        <v>-1.6704</v>
       </c>
     </row>
     <row r="233">
@@ -11727,10 +11715,10 @@
         <v>0.71</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.4516663758798447</v>
+        <v>-0.3602</v>
       </c>
       <c r="J233" t="n">
-        <v>-7.226662014077515</v>
+        <v>-5.7632</v>
       </c>
     </row>
     <row r="234">
@@ -11767,10 +11755,10 @@
         <v>0.63</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.5260148889687244</v>
+        <v>-0.5098</v>
       </c>
       <c r="J234" t="n">
-        <v>-8.41623822349959</v>
+        <v>-8.1568</v>
       </c>
     </row>
     <row r="235">
@@ -11807,10 +11795,10 @@
         <v>0.61</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5459881604179794</v>
+        <v>-0.5421</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.73581056668767</v>
+        <v>-8.6736</v>
       </c>
     </row>
     <row r="236">
@@ -11847,10 +11835,10 @@
         <v>0.47</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6934990633873115</v>
+        <v>-0.7395</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.09598501419698</v>
+        <v>-11.832</v>
       </c>
     </row>
     <row r="237">
@@ -11887,10 +11875,10 @@
         <v>1.8</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5583883559008066</v>
+        <v>1.6459</v>
       </c>
       <c r="J237" t="n">
-        <v>8.934213694412906</v>
+        <v>26.3344</v>
       </c>
     </row>
     <row r="238">
@@ -11927,10 +11915,10 @@
         <v>1.73</v>
       </c>
       <c r="I238" t="n">
-        <v>0.507244370598204</v>
+        <v>1.5197</v>
       </c>
       <c r="J238" t="n">
-        <v>8.115909929571265</v>
+        <v>24.3152</v>
       </c>
     </row>
     <row r="239">
@@ -11967,10 +11955,10 @@
         <v>1.66</v>
       </c>
       <c r="I239" t="n">
-        <v>0.4552806620349448</v>
+        <v>1.3886</v>
       </c>
       <c r="J239" t="n">
-        <v>7.284490592559117</v>
+        <v>22.2176</v>
       </c>
     </row>
     <row r="240">
@@ -12007,10 +11995,10 @@
         <v>1.32</v>
       </c>
       <c r="I240" t="n">
-        <v>0.2091079367530132</v>
+        <v>0.651</v>
       </c>
       <c r="J240" t="n">
-        <v>3.345726988048211</v>
+        <v>10.416</v>
       </c>
     </row>
     <row r="241">
@@ -12047,10 +12035,10 @@
         <v>1.06</v>
       </c>
       <c r="I241" t="n">
-        <v>0.01092910898430378</v>
+        <v>0.0229</v>
       </c>
       <c r="J241" t="n">
-        <v>0.1748657437488605</v>
+        <v>0.3664</v>
       </c>
     </row>
     <row r="242">
@@ -12087,10 +12075,10 @@
         <v>1.09</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.0007154829081022155</v>
+        <v>0.2537</v>
       </c>
       <c r="J242" t="n">
-        <v>-0.01502514107014653</v>
+        <v>5.3277</v>
       </c>
     </row>
     <row r="243">
@@ -12127,10 +12115,10 @@
         <v>1.03</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.06384813000814492</v>
+        <v>0.1404</v>
       </c>
       <c r="J243" t="n">
-        <v>-1.340810730171043</v>
+        <v>2.9484</v>
       </c>
     </row>
     <row r="244">
@@ -12167,10 +12155,10 @@
         <v>0.89</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2037078597304131</v>
+        <v>-0.189</v>
       </c>
       <c r="J244" t="n">
-        <v>-4.277865054338676</v>
+        <v>-3.969</v>
       </c>
     </row>
     <row r="245">
@@ -12207,10 +12195,10 @@
         <v>0.72</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3708792323479087</v>
+        <v>-0.4687</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.788463879306083</v>
+        <v>-9.842700000000001</v>
       </c>
     </row>
     <row r="246">
@@ -12247,10 +12235,10 @@
         <v>0.71</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3810913455433852</v>
+        <v>-0.4825</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.002918256411089</v>
+        <v>-10.1325</v>
       </c>
     </row>
     <row r="247">
@@ -12287,10 +12275,10 @@
         <v>2.06</v>
       </c>
       <c r="I247" t="n">
-        <v>1.06986545104631</v>
+        <v>1.2738</v>
       </c>
       <c r="J247" t="n">
-        <v>22.46717447197251</v>
+        <v>26.7498</v>
       </c>
     </row>
     <row r="248">
@@ -12327,10 +12315,10 @@
         <v>1.51</v>
       </c>
       <c r="I248" t="n">
-        <v>0.5418032597487816</v>
+        <v>0.71</v>
       </c>
       <c r="J248" t="n">
-        <v>11.37786845472441</v>
+        <v>14.91</v>
       </c>
     </row>
     <row r="249">
@@ -12367,10 +12355,10 @@
         <v>1.19</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1998842242815447</v>
+        <v>0.2759</v>
       </c>
       <c r="J249" t="n">
-        <v>4.197568709912439</v>
+        <v>5.7939</v>
       </c>
     </row>
     <row r="250">
@@ -12407,10 +12395,10 @@
         <v>0.7</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3213790185096527</v>
+        <v>-0.5507</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.748959388702706</v>
+        <v>-11.5647</v>
       </c>
     </row>
     <row r="251">
@@ -12447,10 +12435,10 @@
         <v>0.61</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.410920287621458</v>
+        <v>-0.6587</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.62932604005062</v>
+        <v>-13.8327</v>
       </c>
     </row>
     <row r="252">
@@ -12487,10 +12475,10 @@
         <v>1.62</v>
       </c>
       <c r="I252" t="n">
-        <v>0.6218575893258823</v>
+        <v>1.3792</v>
       </c>
       <c r="J252" t="n">
-        <v>12.43715178651765</v>
+        <v>27.584</v>
       </c>
     </row>
     <row r="253">
@@ -12527,10 +12515,10 @@
         <v>1.49</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4783877352250316</v>
+        <v>1.1217</v>
       </c>
       <c r="J253" t="n">
-        <v>9.567754704500633</v>
+        <v>22.434</v>
       </c>
     </row>
     <row r="254">
@@ -12567,10 +12555,10 @@
         <v>1.32</v>
       </c>
       <c r="I254" t="n">
-        <v>0.3020856277543176</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="J254" t="n">
-        <v>6.041712555086352</v>
+        <v>14.304</v>
       </c>
     </row>
     <row r="255">
@@ -12607,10 +12595,10 @@
         <v>1.24</v>
       </c>
       <c r="I255" t="n">
-        <v>0.2126666269817592</v>
+        <v>0.5254</v>
       </c>
       <c r="J255" t="n">
-        <v>4.253332539635184</v>
+        <v>10.508</v>
       </c>
     </row>
     <row r="256">
@@ -12647,10 +12635,10 @@
         <v>1.15</v>
       </c>
       <c r="I256" t="n">
-        <v>0.1090202534711427</v>
+        <v>0.3053</v>
       </c>
       <c r="J256" t="n">
-        <v>2.180405069422854</v>
+        <v>6.106</v>
       </c>
     </row>
     <row r="257">
@@ -12687,10 +12675,10 @@
         <v>0.99</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.0773511574585604</v>
+        <v>0.0804</v>
       </c>
       <c r="J257" t="n">
-        <v>-1.547023149171208</v>
+        <v>1.608</v>
       </c>
     </row>
     <row r="258">
@@ -12727,10 +12715,10 @@
         <v>0.8</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2774188582687375</v>
+        <v>-0.2684</v>
       </c>
       <c r="J258" t="n">
-        <v>-5.548377165374751</v>
+        <v>-5.368</v>
       </c>
     </row>
     <row r="259">
@@ -12767,10 +12755,10 @@
         <v>0.75</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3223898620073354</v>
+        <v>-0.3647</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.447797240146709</v>
+        <v>-7.294</v>
       </c>
     </row>
     <row r="260">
@@ -12807,10 +12795,10 @@
         <v>0.64</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4301409391004872</v>
+        <v>-0.5394</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.602818782009745</v>
+        <v>-10.788</v>
       </c>
     </row>
     <row r="261">
@@ -12847,10 +12835,10 @@
         <v>0.59</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4815421686743863</v>
+        <v>-0.6083</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.630843373487725</v>
+        <v>-12.166</v>
       </c>
     </row>
     <row r="262">
@@ -12887,10 +12875,10 @@
         <v>1.99</v>
       </c>
       <c r="I262" t="n">
-        <v>0.9926491116168967</v>
+        <v>1.9536</v>
       </c>
       <c r="J262" t="n">
-        <v>16.87503489748724</v>
+        <v>33.2112</v>
       </c>
     </row>
     <row r="263">
@@ -12927,10 +12915,10 @@
         <v>1.89</v>
       </c>
       <c r="I263" t="n">
-        <v>0.8932016548047601</v>
+        <v>1.8121</v>
       </c>
       <c r="J263" t="n">
-        <v>15.18442813168092</v>
+        <v>30.8057</v>
       </c>
     </row>
     <row r="264">
@@ -12967,10 +12955,10 @@
         <v>1.34</v>
       </c>
       <c r="I264" t="n">
-        <v>0.3133390056021101</v>
+        <v>0.7028</v>
       </c>
       <c r="J264" t="n">
-        <v>5.326763095235872</v>
+        <v>11.9476</v>
       </c>
     </row>
     <row r="265">
@@ -13007,10 +12995,10 @@
         <v>1.32</v>
       </c>
       <c r="I265" t="n">
-        <v>0.2908055394366562</v>
+        <v>0.6592</v>
       </c>
       <c r="J265" t="n">
-        <v>4.943694170423155</v>
+        <v>11.2064</v>
       </c>
     </row>
     <row r="266">
@@ -13047,10 +13035,10 @@
         <v>0.91</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.1455748463845873</v>
+        <v>-0.5142</v>
       </c>
       <c r="J266" t="n">
-        <v>-2.474772388537984</v>
+        <v>-8.741400000000001</v>
       </c>
     </row>
     <row r="267">
@@ -13087,10 +13075,10 @@
         <v>0.86</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.2689732917312015</v>
+        <v>-0.137</v>
       </c>
       <c r="J267" t="n">
-        <v>-4.572545959430426</v>
+        <v>-2.329</v>
       </c>
     </row>
     <row r="268">
@@ -13127,10 +13115,10 @@
         <v>0.83</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.3002130081112528</v>
+        <v>-0.186</v>
       </c>
       <c r="J268" t="n">
-        <v>-5.103621137891297</v>
+        <v>-3.162</v>
       </c>
     </row>
     <row r="269">
@@ -13167,10 +13155,10 @@
         <v>0.78</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3517526739821379</v>
+        <v>-0.2661</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.979795457696345</v>
+        <v>-4.5237</v>
       </c>
     </row>
     <row r="270">
@@ -13207,10 +13195,10 @@
         <v>0.58</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5410687766649368</v>
+        <v>-0.6008</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.198169203303925</v>
+        <v>-10.2136</v>
       </c>
     </row>
     <row r="271">
@@ -13247,10 +13235,10 @@
         <v>0.4</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.7207861358619413</v>
+        <v>-0.8357</v>
       </c>
       <c r="J271" t="n">
-        <v>-12.253364309653</v>
+        <v>-14.2069</v>
       </c>
     </row>
     <row r="272">
@@ -13287,10 +13275,10 @@
         <v>1.69</v>
       </c>
       <c r="I272" t="n">
-        <v>0.711088749914351</v>
+        <v>0.8985</v>
       </c>
       <c r="J272" t="n">
-        <v>12.79959749845832</v>
+        <v>16.173</v>
       </c>
     </row>
     <row r="273">
@@ -13327,10 +13315,10 @@
         <v>1.43</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4655366295437245</v>
+        <v>0.6067</v>
       </c>
       <c r="J273" t="n">
-        <v>8.379659331787042</v>
+        <v>10.9206</v>
       </c>
     </row>
     <row r="274">
@@ -13367,10 +13355,10 @@
         <v>1.26</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3010668798492162</v>
+        <v>0.3798</v>
       </c>
       <c r="J274" t="n">
-        <v>5.419203837285892</v>
+        <v>6.8364</v>
       </c>
     </row>
     <row r="275">
@@ -13407,10 +13395,10 @@
         <v>0.96</v>
       </c>
       <c r="I275" t="n">
-        <v>0.00680915231422401</v>
+        <v>-0.1783</v>
       </c>
       <c r="J275" t="n">
-        <v>0.1225647416560322</v>
+        <v>-3.2094</v>
       </c>
     </row>
     <row r="276">
@@ -13447,10 +13435,10 @@
         <v>0.89</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.07402272525513851</v>
+        <v>-0.2967</v>
       </c>
       <c r="J276" t="n">
-        <v>-1.332409054592493</v>
+        <v>-5.3406</v>
       </c>
     </row>
     <row r="277">
@@ -13487,10 +13475,10 @@
         <v>0.96</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.1486262677624119</v>
+        <v>-0.0187</v>
       </c>
       <c r="J277" t="n">
-        <v>-2.675272819723415</v>
+        <v>-0.3366</v>
       </c>
     </row>
     <row r="278">
@@ -13527,10 +13515,10 @@
         <v>0.92</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.1863132824576093</v>
+        <v>-0.0961</v>
       </c>
       <c r="J278" t="n">
-        <v>-3.353639084236968</v>
+        <v>-1.7298</v>
       </c>
     </row>
     <row r="279">
@@ -13567,10 +13555,10 @@
         <v>0.79</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2969286422976616</v>
+        <v>-0.3402</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.344715561357908</v>
+        <v>-6.1236</v>
       </c>
     </row>
     <row r="280">
@@ -13607,10 +13595,10 @@
         <v>0.79</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2969286422976616</v>
+        <v>-0.3402</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.344715561357908</v>
+        <v>-6.1236</v>
       </c>
     </row>
     <row r="281">
@@ -13647,10 +13635,10 @@
         <v>0.66</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4149330491775767</v>
+        <v>-0.5337</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.46879488519638</v>
+        <v>-9.6066</v>
       </c>
     </row>
     <row r="282">
@@ -13687,10 +13675,10 @@
         <v>1.32</v>
       </c>
       <c r="I282" t="n">
-        <v>0.2519358784187807</v>
+        <v>0.5712</v>
       </c>
       <c r="J282" t="n">
-        <v>6.046461082050737</v>
+        <v>13.7088</v>
       </c>
     </row>
     <row r="283">
@@ -13727,10 +13715,10 @@
         <v>1.17</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1074460447127616</v>
+        <v>0.3654</v>
       </c>
       <c r="J283" t="n">
-        <v>2.578705073106278</v>
+        <v>8.769600000000001</v>
       </c>
     </row>
     <row r="284">
@@ -13767,10 +13755,10 @@
         <v>0.91</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.173198907327537</v>
+        <v>-0.1801</v>
       </c>
       <c r="J284" t="n">
-        <v>-4.156773775860889</v>
+        <v>-4.3224</v>
       </c>
     </row>
     <row r="285">
@@ -13807,10 +13795,10 @@
         <v>0.71</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4046780869737701</v>
+        <v>-0.4923</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.712274087370483</v>
+        <v>-11.8152</v>
       </c>
     </row>
     <row r="286">
@@ -13847,10 +13835,10 @@
         <v>0.53</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6077490738227018</v>
+        <v>-0.7195</v>
       </c>
       <c r="J286" t="n">
-        <v>-14.58597777174484</v>
+        <v>-17.268</v>
       </c>
     </row>
     <row r="287">
@@ -13887,10 +13875,10 @@
         <v>1.52</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5089775217971851</v>
+        <v>1.2445</v>
       </c>
       <c r="J287" t="n">
-        <v>12.21546052313244</v>
+        <v>29.868</v>
       </c>
     </row>
     <row r="288">
@@ -13927,10 +13915,10 @@
         <v>1.45</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4236228542982632</v>
+        <v>1.1025</v>
       </c>
       <c r="J288" t="n">
-        <v>10.16694850315832</v>
+        <v>26.46</v>
       </c>
     </row>
     <row r="289">
@@ -13967,10 +13955,10 @@
         <v>1.22</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1488154404805028</v>
+        <v>0.5468</v>
       </c>
       <c r="J289" t="n">
-        <v>3.571570571532066</v>
+        <v>13.1232</v>
       </c>
     </row>
     <row r="290">
@@ -14007,10 +13995,10 @@
         <v>1.15</v>
       </c>
       <c r="I290" t="n">
-        <v>0.06444665505139668</v>
+        <v>0.3576</v>
       </c>
       <c r="J290" t="n">
-        <v>1.54671972123352</v>
+        <v>8.5824</v>
       </c>
     </row>
     <row r="291">
@@ -14047,10 +14035,10 @@
         <v>0.84</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2381013637915703</v>
+        <v>-0.642</v>
       </c>
       <c r="J291" t="n">
-        <v>-5.714432730997689</v>
+        <v>-15.408</v>
       </c>
     </row>
     <row r="292">
@@ -14087,10 +14075,10 @@
         <v>1.49</v>
       </c>
       <c r="I292" t="n">
-        <v>0.3955804694335163</v>
+        <v>0.7661</v>
       </c>
       <c r="J292" t="n">
-        <v>9.098350796970875</v>
+        <v>17.6203</v>
       </c>
     </row>
     <row r="293">
@@ -14127,10 +14115,10 @@
         <v>0.99</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.1124556989640538</v>
+        <v>-0.0098</v>
       </c>
       <c r="J293" t="n">
-        <v>-2.586481076173238</v>
+        <v>-0.2254</v>
       </c>
     </row>
     <row r="294">
@@ -14167,10 +14155,10 @@
         <v>0.97</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1338136911068689</v>
+        <v>-0.062</v>
       </c>
       <c r="J294" t="n">
-        <v>-3.077714895457986</v>
+        <v>-1.426</v>
       </c>
     </row>
     <row r="295">
@@ -14207,10 +14195,10 @@
         <v>0.96</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1430793015195054</v>
+        <v>-0.0891</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.290823934948625</v>
+        <v>-2.0493</v>
       </c>
     </row>
     <row r="296">
@@ -14247,10 +14235,10 @@
         <v>0.39</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.7836336952781496</v>
+        <v>-0.8834</v>
       </c>
       <c r="J296" t="n">
-        <v>-18.02357499139744</v>
+        <v>-20.3182</v>
       </c>
     </row>
     <row r="297">
@@ -14287,10 +14275,10 @@
         <v>1.76</v>
       </c>
       <c r="I297" t="n">
-        <v>0.8579938736108577</v>
+        <v>1.7297</v>
       </c>
       <c r="J297" t="n">
-        <v>19.73385909304973</v>
+        <v>39.7831</v>
       </c>
     </row>
     <row r="298">
@@ -14327,10 +14315,10 @@
         <v>1.17</v>
       </c>
       <c r="I298" t="n">
-        <v>0.1571455153472537</v>
+        <v>0.4758</v>
       </c>
       <c r="J298" t="n">
-        <v>3.614346852986836</v>
+        <v>10.9434</v>
       </c>
     </row>
     <row r="299">
@@ -14367,10 +14355,10 @@
         <v>1.12</v>
       </c>
       <c r="I299" t="n">
-        <v>0.1023825505614866</v>
+        <v>0.3149</v>
       </c>
       <c r="J299" t="n">
-        <v>2.354798662914192</v>
+        <v>7.2427</v>
       </c>
     </row>
     <row r="300">
@@ -14407,10 +14395,10 @@
         <v>0.99</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.04505481567318062</v>
+        <v>-0.1681</v>
       </c>
       <c r="J300" t="n">
-        <v>-1.036260760483154</v>
+        <v>-3.8663</v>
       </c>
     </row>
     <row r="301">
@@ -14447,10 +14435,10 @@
         <v>0.78</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.2375477024043283</v>
+        <v>-0.768</v>
       </c>
       <c r="J301" t="n">
-        <v>-5.463597155299551</v>
+        <v>-17.664</v>
       </c>
     </row>
     <row r="302">
@@ -14487,10 +14475,10 @@
         <v>1.32</v>
       </c>
       <c r="I302" t="n">
-        <v>0.2462379440251628</v>
+        <v>0.8629</v>
       </c>
       <c r="J302" t="n">
-        <v>5.909710656603908</v>
+        <v>20.7096</v>
       </c>
     </row>
     <row r="303">
@@ -14527,10 +14515,10 @@
         <v>1.31</v>
       </c>
       <c r="I303" t="n">
-        <v>0.2355283367189073</v>
+        <v>0.8401</v>
       </c>
       <c r="J303" t="n">
-        <v>5.652680081253775</v>
+        <v>20.1624</v>
       </c>
     </row>
     <row r="304">
@@ -14567,10 +14555,10 @@
         <v>1.29</v>
       </c>
       <c r="I304" t="n">
-        <v>0.2140955859456772</v>
+        <v>0.7937</v>
       </c>
       <c r="J304" t="n">
-        <v>5.138294062696252</v>
+        <v>19.0488</v>
       </c>
     </row>
     <row r="305">
@@ -14607,10 +14595,10 @@
         <v>0.96</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.12812649651373</v>
+        <v>-0.2799</v>
       </c>
       <c r="J305" t="n">
-        <v>-3.075035916329521</v>
+        <v>-6.7176</v>
       </c>
     </row>
     <row r="306">
@@ -14647,10 +14635,10 @@
         <v>0.9</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1969009644271345</v>
+        <v>-0.4624</v>
       </c>
       <c r="J306" t="n">
-        <v>-4.725623146251227</v>
+        <v>-11.0976</v>
       </c>
     </row>
     <row r="307">
@@ -14687,10 +14675,10 @@
         <v>1.32</v>
       </c>
       <c r="I307" t="n">
-        <v>0.2148427919359087</v>
+        <v>0.5329</v>
       </c>
       <c r="J307" t="n">
-        <v>5.156227006461808</v>
+        <v>12.7896</v>
       </c>
     </row>
     <row r="308">
@@ -14727,10 +14715,10 @@
         <v>1.1</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.02107858829218318</v>
+        <v>0.2118</v>
       </c>
       <c r="J308" t="n">
-        <v>-0.5058861190123962</v>
+        <v>5.0832</v>
       </c>
     </row>
     <row r="309">
@@ -14767,10 +14755,10 @@
         <v>1.08</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.04228505180897354</v>
+        <v>0.1756</v>
       </c>
       <c r="J309" t="n">
-        <v>-1.014841243415365</v>
+        <v>4.2144</v>
       </c>
     </row>
     <row r="310">
@@ -14807,10 +14795,10 @@
         <v>1.05</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.07249919916745579</v>
+        <v>0.1147</v>
       </c>
       <c r="J310" t="n">
-        <v>-1.739980780018939</v>
+        <v>2.7528</v>
       </c>
     </row>
     <row r="311">
@@ -14847,10 +14835,10 @@
         <v>0.65</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5030171490061012</v>
+        <v>-0.5903</v>
       </c>
       <c r="J311" t="n">
-        <v>-12.07241157614643</v>
+        <v>-14.1672</v>
       </c>
     </row>
     <row r="312">
@@ -14887,10 +14875,10 @@
         <v>1.77</v>
       </c>
       <c r="I312" t="n">
-        <v>0.7829916256184146</v>
+        <v>1.765</v>
       </c>
       <c r="J312" t="n">
-        <v>17.22581576360512</v>
+        <v>38.83</v>
       </c>
     </row>
     <row r="313">
@@ -14927,10 +14915,10 @@
         <v>1.44</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4676249431046516</v>
+        <v>1.1357</v>
       </c>
       <c r="J313" t="n">
-        <v>10.28774874830234</v>
+        <v>24.9854</v>
       </c>
     </row>
     <row r="314">
@@ -14967,10 +14955,10 @@
         <v>1.1</v>
       </c>
       <c r="I314" t="n">
-        <v>0.1201520155134828</v>
+        <v>0.2782</v>
       </c>
       <c r="J314" t="n">
-        <v>2.643344341296622</v>
+        <v>6.1204</v>
       </c>
     </row>
     <row r="315">
@@ -15007,10 +14995,10 @@
         <v>0.79</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2171185044404005</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="J315" t="n">
-        <v>-4.776607097688811</v>
+        <v>-16.1788</v>
       </c>
     </row>
     <row r="316">
@@ -15047,10 +15035,10 @@
         <v>0.55</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4762822900904629</v>
+        <v>-1.2527</v>
       </c>
       <c r="J316" t="n">
-        <v>-10.47821038199018</v>
+        <v>-27.5594</v>
       </c>
     </row>
     <row r="317">
@@ -15087,10 +15075,10 @@
         <v>1.37</v>
       </c>
       <c r="I317" t="n">
-        <v>0.311917271010376</v>
+        <v>0.6327</v>
       </c>
       <c r="J317" t="n">
-        <v>6.862179962228272</v>
+        <v>13.9194</v>
       </c>
     </row>
     <row r="318">
@@ -15127,10 +15115,10 @@
         <v>1.02</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.06286646224779824</v>
+        <v>0.0997</v>
       </c>
       <c r="J318" t="n">
-        <v>-1.383062169451561</v>
+        <v>2.1934</v>
       </c>
     </row>
     <row r="319">
@@ -15167,10 +15155,10 @@
         <v>0.93</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1556712190390568</v>
+        <v>-0.1394</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.424766818859249</v>
+        <v>-3.0668</v>
       </c>
     </row>
     <row r="320">
@@ -15207,10 +15195,10 @@
         <v>0.75</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3494300144807618</v>
+        <v>-0.4382</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.68746031857676</v>
+        <v>-9.6404</v>
       </c>
     </row>
     <row r="321">
@@ -15247,10 +15235,10 @@
         <v>0.59</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5227001266559318</v>
+        <v>-0.6475</v>
       </c>
       <c r="J321" t="n">
-        <v>-11.4994027864305</v>
+        <v>-14.245</v>
       </c>
     </row>
     <row r="322">
@@ -15287,10 +15275,10 @@
         <v>1.51</v>
       </c>
       <c r="I322" t="n">
-        <v>0.3864711896947464</v>
+        <v>1.2827</v>
       </c>
       <c r="J322" t="n">
-        <v>13.52649163931613</v>
+        <v>44.8945</v>
       </c>
     </row>
     <row r="323">
@@ -15327,10 +15315,10 @@
         <v>1.17</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1193289427670773</v>
+        <v>0.5135</v>
       </c>
       <c r="J323" t="n">
-        <v>4.176512996847704</v>
+        <v>17.9725</v>
       </c>
     </row>
     <row r="324">
@@ -15367,10 +15355,10 @@
         <v>1.13</v>
       </c>
       <c r="I324" t="n">
-        <v>0.08975146668261605</v>
+        <v>0.3948</v>
       </c>
       <c r="J324" t="n">
-        <v>3.141301333891562</v>
+        <v>13.818</v>
       </c>
     </row>
     <row r="325">
@@ -15407,10 +15395,10 @@
         <v>1.09</v>
       </c>
       <c r="I325" t="n">
-        <v>0.06293771651478797</v>
+        <v>0.2541</v>
       </c>
       <c r="J325" t="n">
-        <v>2.202820078017579</v>
+        <v>8.8935</v>
       </c>
     </row>
     <row r="326">
@@ -15447,10 +15435,10 @@
         <v>0.7</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4244581473112336</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="J326" t="n">
-        <v>-14.85603515589318</v>
+        <v>-32.83</v>
       </c>
     </row>
     <row r="327">
@@ -15487,10 +15475,10 @@
         <v>1.17</v>
       </c>
       <c r="I327" t="n">
-        <v>0.1057049797831659</v>
+        <v>0.3509</v>
       </c>
       <c r="J327" t="n">
-        <v>3.699674292410808</v>
+        <v>12.2815</v>
       </c>
     </row>
     <row r="328">
@@ -15527,10 +15515,10 @@
         <v>1.1</v>
       </c>
       <c r="I328" t="n">
-        <v>0.0249520437996923</v>
+        <v>0.2402</v>
       </c>
       <c r="J328" t="n">
-        <v>0.8733215329892304</v>
+        <v>8.407</v>
       </c>
     </row>
     <row r="329">
@@ -15567,10 +15555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1275259906513952</v>
+        <v>-0.1414</v>
       </c>
       <c r="J329" t="n">
-        <v>-4.463409672798833</v>
+        <v>-4.949</v>
       </c>
     </row>
     <row r="330">
@@ -15607,10 +15595,10 @@
         <v>0.88</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1854646829994361</v>
+        <v>-0.2512</v>
       </c>
       <c r="J330" t="n">
-        <v>-6.491263904980265</v>
+        <v>-8.792</v>
       </c>
     </row>
     <row r="331">
@@ -15647,10 +15635,10 @@
         <v>0.75</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3149322212748769</v>
+        <v>-0.4468</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.02262774462069</v>
+        <v>-15.638</v>
       </c>
     </row>
     <row r="332">
@@ -15687,10 +15675,10 @@
         <v>1.62</v>
       </c>
       <c r="I332" t="n">
-        <v>0.449088269552687</v>
+        <v>1.3684</v>
       </c>
       <c r="J332" t="n">
-        <v>8.083588851948367</v>
+        <v>24.6312</v>
       </c>
     </row>
     <row r="333">
@@ -15727,10 +15715,10 @@
         <v>1.45</v>
       </c>
       <c r="I333" t="n">
-        <v>0.3205418425171356</v>
+        <v>1.0236</v>
       </c>
       <c r="J333" t="n">
-        <v>5.769753165308441</v>
+        <v>18.4248</v>
       </c>
     </row>
     <row r="334">
@@ -15767,10 +15755,10 @@
         <v>1.39</v>
       </c>
       <c r="I334" t="n">
-        <v>0.2788825933608904</v>
+        <v>0.8793</v>
       </c>
       <c r="J334" t="n">
-        <v>5.019886680496028</v>
+        <v>15.8274</v>
       </c>
     </row>
     <row r="335">
@@ -15807,10 +15795,10 @@
         <v>1.34</v>
       </c>
       <c r="I335" t="n">
-        <v>0.2453115716996626</v>
+        <v>0.7488</v>
       </c>
       <c r="J335" t="n">
-        <v>4.415608290593926</v>
+        <v>13.4784</v>
       </c>
     </row>
     <row r="336">
@@ -15847,10 +15835,10 @@
         <v>1.14</v>
       </c>
       <c r="I336" t="n">
-        <v>0.08936417124767174</v>
+        <v>0.2721</v>
       </c>
       <c r="J336" t="n">
-        <v>1.608555082458091</v>
+        <v>4.8978</v>
       </c>
     </row>
     <row r="337">
@@ -15887,10 +15875,10 @@
         <v>1.35</v>
       </c>
       <c r="I337" t="n">
-        <v>0.2821935623081818</v>
+        <v>0.6871</v>
       </c>
       <c r="J337" t="n">
-        <v>5.079484121547273</v>
+        <v>12.3678</v>
       </c>
     </row>
     <row r="338">
@@ -15927,10 +15915,10 @@
         <v>0.66</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.4150357519636109</v>
+        <v>-0.5051</v>
       </c>
       <c r="J338" t="n">
-        <v>-7.470643535344997</v>
+        <v>-9.091799999999999</v>
       </c>
     </row>
     <row r="339">
@@ -15967,10 +15955,10 @@
         <v>0.59</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.4810207857809</v>
+        <v>-0.6041</v>
       </c>
       <c r="J339" t="n">
-        <v>-8.6583741440562</v>
+        <v>-10.8738</v>
       </c>
     </row>
     <row r="340">
@@ -16007,10 +15995,10 @@
         <v>0.57</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4999102801960043</v>
+        <v>-0.631</v>
       </c>
       <c r="J340" t="n">
-        <v>-8.998385043528078</v>
+        <v>-11.358</v>
       </c>
     </row>
     <row r="341">
@@ -16047,10 +16035,10 @@
         <v>0.53</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.5375196115230744</v>
+        <v>-0.6836</v>
       </c>
       <c r="J341" t="n">
-        <v>-9.675353007415339</v>
+        <v>-12.3048</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7485/event_7485_evp_summary.xlsx
+++ b/database/event/7485/event_7485_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>9.3149</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3.7654</v>
       </c>
       <c r="D2" t="n">
         <v>3.3417</v>
@@ -545,7 +545,7 @@
         <v>7.8432</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3.1705</v>
       </c>
       <c r="D3" t="n">
         <v>2.7471</v>
@@ -591,7 +591,7 @@
         <v>7.4704</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.0198</v>
       </c>
       <c r="D4" t="n">
         <v>2.5965</v>
@@ -637,7 +637,7 @@
         <v>7.1465</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.8889</v>
       </c>
       <c r="D5" t="n">
         <v>2.4657</v>
@@ -683,7 +683,7 @@
         <v>5.7396</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.3201</v>
       </c>
       <c r="D6" t="n">
         <v>1.8973</v>
@@ -729,7 +729,7 @@
         <v>4.4034</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="D7" t="n">
         <v>1.3575</v>
@@ -775,7 +775,7 @@
         <v>4.0678</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1.6443</v>
       </c>
       <c r="D8" t="n">
         <v>1.2219</v>
@@ -821,7 +821,7 @@
         <v>3.3438</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1.3517</v>
       </c>
       <c r="D9" t="n">
         <v>0.9295</v>
@@ -867,7 +867,7 @@
         <v>2.6901</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.0874</v>
       </c>
       <c r="D10" t="n">
         <v>0.6654</v>
@@ -913,7 +913,7 @@
         <v>2.6347</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.065</v>
       </c>
       <c r="D11" t="n">
         <v>0.643</v>
@@ -959,7 +959,7 @@
         <v>2.5777</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.042</v>
       </c>
       <c r="D12" t="n">
         <v>0.62</v>
@@ -1005,7 +1005,7 @@
         <v>2.2769</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.9204</v>
       </c>
       <c r="D13" t="n">
         <v>0.4985</v>
@@ -1051,7 +1051,7 @@
         <v>2.0329</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.8218</v>
       </c>
       <c r="D14" t="n">
         <v>0.3999</v>
@@ -1097,7 +1097,7 @@
         <v>1.7207</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.6956</v>
       </c>
       <c r="D15" t="n">
         <v>0.2738</v>
@@ -1143,7 +1143,7 @@
         <v>1.7192</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.695</v>
       </c>
       <c r="D16" t="n">
         <v>0.2732</v>
@@ -1189,7 +1189,7 @@
         <v>1.5389</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.6221</v>
       </c>
       <c r="D17" t="n">
         <v>0.2003</v>
@@ -1235,7 +1235,7 @@
         <v>1.4297</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.5779</v>
       </c>
       <c r="D18" t="n">
         <v>0.1562</v>
@@ -1281,7 +1281,7 @@
         <v>1.2014</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.4856</v>
       </c>
       <c r="D19" t="n">
         <v>0.064</v>
@@ -1327,7 +1327,7 @@
         <v>1.0696</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.4324</v>
       </c>
       <c r="D20" t="n">
         <v>0.0107</v>
@@ -1373,7 +1373,7 @@
         <v>1.0464</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.423</v>
       </c>
       <c r="D21" t="n">
         <v>0.0014</v>
@@ -1419,7 +1419,7 @@
         <v>0.851</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="D22" t="n">
         <v>-0.0776</v>
@@ -1465,7 +1465,7 @@
         <v>0.7231</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.2923</v>
       </c>
       <c r="D23" t="n">
         <v>-0.1292</v>
@@ -1511,7 +1511,7 @@
         <v>0.6754</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1485</v>
@@ -1557,7 +1557,7 @@
         <v>0.4246</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.1716</v>
       </c>
       <c r="D25" t="n">
         <v>-0.2498</v>
@@ -1603,7 +1603,7 @@
         <v>0.3098</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.1252</v>
       </c>
       <c r="D26" t="n">
         <v>-0.2962</v>
@@ -1649,7 +1649,7 @@
         <v>0.2814</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.1138</v>
       </c>
       <c r="D27" t="n">
         <v>-0.3077</v>
@@ -1695,7 +1695,7 @@
         <v>0.1346</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.0544</v>
       </c>
       <c r="D28" t="n">
         <v>-0.367</v>
@@ -1741,7 +1741,7 @@
         <v>0.132</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.0534</v>
       </c>
       <c r="D29" t="n">
         <v>-0.368</v>
@@ -1787,7 +1787,7 @@
         <v>-0.0693</v>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>-0.028</v>
       </c>
       <c r="D30" t="n">
         <v>-0.4494</v>
@@ -1833,7 +1833,7 @@
         <v>-0.1583</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.064</v>
       </c>
       <c r="D31" t="n">
         <v>-0.4853</v>
@@ -1879,7 +1879,7 @@
         <v>-0.8278</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.3346</v>
       </c>
       <c r="D32" t="n">
         <v>-0.7558</v>
@@ -1925,7 +1925,7 @@
         <v>-1</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.4042</v>
       </c>
       <c r="D33" t="n">
         <v>-0.8253</v>
@@ -1971,7 +1971,7 @@
         <v>-1.02</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.4123</v>
       </c>
       <c r="D34" t="n">
         <v>-0.8334</v>
@@ -2017,7 +2017,7 @@
         <v>-1.1592</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.4686</v>
       </c>
       <c r="D35" t="n">
         <v>-0.8897</v>
@@ -2063,7 +2063,7 @@
         <v>-1.1787</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.4765</v>
       </c>
       <c r="D36" t="n">
         <v>-0.8975</v>
@@ -2109,7 +2109,7 @@
         <v>-1.6466</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.6656</v>
       </c>
       <c r="D37" t="n">
         <v>-1.0866</v>
@@ -2155,7 +2155,7 @@
         <v>-1.7229</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-0.6965</v>
       </c>
       <c r="D38" t="n">
         <v>-1.1174</v>
@@ -2201,7 +2201,7 @@
         <v>-1.7563</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-0.71</v>
       </c>
       <c r="D39" t="n">
         <v>-1.1309</v>
@@ -2247,7 +2247,7 @@
         <v>-2</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-0.8085</v>
       </c>
       <c r="D40" t="n">
         <v>-1.2293</v>
@@ -2293,7 +2293,7 @@
         <v>-2.6582</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-1.0745</v>
       </c>
       <c r="D41" t="n">
         <v>-1.4952</v>
@@ -2339,7 +2339,7 @@
         <v>-2.7875</v>
       </c>
       <c r="C42" t="n">
-        <v>-0</v>
+        <v>-1.1268</v>
       </c>
       <c r="D42" t="n">
         <v>-1.5475</v>

--- a/database/event/7485/event_7485_evp_summary.xlsx
+++ b/database/event/7485/event_7485_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.7654</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3417</v>
+        <v>3.2671</v>
       </c>
       <c r="E2" t="n">
         <v>9.3149</v>
@@ -548,7 +548,7 @@
         <v>3.1705</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7471</v>
+        <v>2.6808</v>
       </c>
       <c r="E3" t="n">
         <v>7.8432</v>
@@ -594,7 +594,7 @@
         <v>3.0198</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5965</v>
+        <v>2.5323</v>
       </c>
       <c r="E4" t="n">
         <v>7.4704</v>
@@ -640,7 +640,7 @@
         <v>2.8889</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4657</v>
+        <v>2.4033</v>
       </c>
       <c r="E5" t="n">
         <v>7.1465</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7396</v>
+        <v>5.7277</v>
       </c>
       <c r="C6" t="n">
-        <v>2.3201</v>
+        <v>2.3153</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8973</v>
+        <v>1.838</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7396</v>
+        <v>5.7277</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1848</v>
+        <v>3.1729</v>
       </c>
       <c r="G6" t="n">
         <v>2.5548</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1848</v>
+        <v>3.1729</v>
       </c>
       <c r="I6" t="n">
         <v>3.1996</v>
@@ -732,7 +732,7 @@
         <v>1.78</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3575</v>
+        <v>1.3104</v>
       </c>
       <c r="E7" t="n">
         <v>4.4034</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0678</v>
+        <v>4.0647</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6443</v>
+        <v>1.6431</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2219</v>
+        <v>1.1755</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0678</v>
+        <v>4.0647</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8304</v>
+        <v>0.8273</v>
       </c>
       <c r="G8" t="n">
         <v>3.2373</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8304</v>
+        <v>0.8273</v>
       </c>
       <c r="I8" t="n">
         <v>0.8343</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3438</v>
+        <v>3.3355</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3517</v>
+        <v>1.3483</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9295</v>
+        <v>0.885</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3438</v>
+        <v>3.3355</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2154</v>
+        <v>2.2071</v>
       </c>
       <c r="G9" t="n">
         <v>1.1284</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2154</v>
+        <v>2.2071</v>
       </c>
       <c r="I9" t="n">
         <v>2.2257</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6901</v>
+        <v>2.6822</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0874</v>
+        <v>1.0842</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6654</v>
+        <v>0.6247</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6901</v>
+        <v>2.6822</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1134</v>
+        <v>2.1055</v>
       </c>
       <c r="G10" t="n">
         <v>0.5767</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1134</v>
+        <v>2.1055</v>
       </c>
       <c r="I10" t="n">
         <v>2.1232</v>
@@ -916,7 +916,7 @@
         <v>1.065</v>
       </c>
       <c r="D11" t="n">
-        <v>0.643</v>
+        <v>0.6058</v>
       </c>
       <c r="E11" t="n">
         <v>2.6347</v>
@@ -962,7 +962,7 @@
         <v>1.042</v>
       </c>
       <c r="D12" t="n">
-        <v>0.62</v>
+        <v>0.583</v>
       </c>
       <c r="E12" t="n">
         <v>2.5777</v>
@@ -1008,7 +1008,7 @@
         <v>0.9204</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4985</v>
+        <v>0.4632</v>
       </c>
       <c r="E13" t="n">
         <v>2.2769</v>
@@ -1054,7 +1054,7 @@
         <v>0.8218</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3999</v>
+        <v>0.366</v>
       </c>
       <c r="E14" t="n">
         <v>2.0329</v>
@@ -1100,7 +1100,7 @@
         <v>0.6956</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2738</v>
+        <v>0.2416</v>
       </c>
       <c r="E15" t="n">
         <v>1.7207</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7192</v>
+        <v>1.7157</v>
       </c>
       <c r="C16" t="n">
-        <v>0.695</v>
+        <v>0.6935</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2732</v>
+        <v>0.2396</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7192</v>
+        <v>1.7157</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9322</v>
+        <v>0.9287</v>
       </c>
       <c r="G16" t="n">
         <v>0.787</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9322</v>
+        <v>0.9287</v>
       </c>
       <c r="I16" t="n">
         <v>0.9365</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5389</v>
+        <v>1.531</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6221</v>
+        <v>0.6189</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2003</v>
+        <v>0.166</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5389</v>
+        <v>1.531</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1215</v>
+        <v>2.1136</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5826</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1215</v>
+        <v>2.1136</v>
       </c>
       <c r="I17" t="n">
         <v>2.1314</v>
@@ -1238,7 +1238,7 @@
         <v>0.5779</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1562</v>
+        <v>0.1257</v>
       </c>
       <c r="E18" t="n">
         <v>1.4297</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2014</v>
+        <v>1.1986</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4856</v>
+        <v>0.4845</v>
       </c>
       <c r="D19" t="n">
-        <v>0.064</v>
+        <v>0.0336</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2014</v>
+        <v>1.1986</v>
       </c>
       <c r="F19" t="n">
-        <v>0.755</v>
+        <v>0.7522</v>
       </c>
       <c r="G19" t="n">
         <v>0.4464</v>
       </c>
       <c r="H19" t="n">
-        <v>0.755</v>
+        <v>0.7522</v>
       </c>
       <c r="I19" t="n">
         <v>0.7585</v>
@@ -1330,7 +1330,7 @@
         <v>0.4324</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0107</v>
+        <v>-0.0178</v>
       </c>
       <c r="E20" t="n">
         <v>1.0696</v>
@@ -1376,7 +1376,7 @@
         <v>0.423</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0014</v>
+        <v>-0.027</v>
       </c>
       <c r="E21" t="n">
         <v>1.0464</v>
@@ -1422,7 +1422,7 @@
         <v>0.344</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0776</v>
+        <v>-0.1049</v>
       </c>
       <c r="E22" t="n">
         <v>0.851</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7231</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2923</v>
+        <v>0.2932</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1292</v>
+        <v>-0.155</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7231</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.59</v>
       </c>
       <c r="G23" t="n">
         <v>1.3153</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.59</v>
       </c>
       <c r="I23" t="n">
         <v>-0.595</v>
@@ -1514,7 +1514,7 @@
         <v>0.273</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1485</v>
+        <v>-0.1748</v>
       </c>
       <c r="E24" t="n">
         <v>0.6754</v>
@@ -1560,7 +1560,7 @@
         <v>0.1716</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2498</v>
+        <v>-0.2747</v>
       </c>
       <c r="E25" t="n">
         <v>0.4246</v>
@@ -1606,7 +1606,7 @@
         <v>0.1252</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2962</v>
+        <v>-0.3205</v>
       </c>
       <c r="E26" t="n">
         <v>0.3098</v>
@@ -1652,7 +1652,7 @@
         <v>0.1138</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3077</v>
+        <v>-0.3318</v>
       </c>
       <c r="E27" t="n">
         <v>0.2814</v>
@@ -1698,7 +1698,7 @@
         <v>0.0544</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.367</v>
+        <v>-0.3903</v>
       </c>
       <c r="E28" t="n">
         <v>0.1346</v>
@@ -1744,7 +1744,7 @@
         <v>0.0534</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.368</v>
+        <v>-0.3913</v>
       </c>
       <c r="E29" t="n">
         <v>0.132</v>
@@ -1790,7 +1790,7 @@
         <v>-0.028</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4494</v>
+        <v>-0.4715</v>
       </c>
       <c r="E30" t="n">
         <v>-0.0693</v>
@@ -1836,7 +1836,7 @@
         <v>-0.064</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4853</v>
+        <v>-0.507</v>
       </c>
       <c r="E31" t="n">
         <v>-0.1583</v>
@@ -1882,7 +1882,7 @@
         <v>-0.3346</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7558</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="E32" t="n">
         <v>-0.8278</v>
@@ -1928,7 +1928,7 @@
         <v>-0.4042</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E33" t="n">
         <v>-1</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.02</v>
+        <v>-1.0228</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4123</v>
+        <v>-0.4135</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8334</v>
+        <v>-0.8514</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.02</v>
+        <v>-1.0228</v>
       </c>
       <c r="F34" t="n">
-        <v>0.75</v>
+        <v>0.7472</v>
       </c>
       <c r="G34" t="n">
         <v>-1.77</v>
       </c>
       <c r="H34" t="n">
-        <v>0.75</v>
+        <v>0.7472</v>
       </c>
       <c r="I34" t="n">
         <v>0.7534999999999999</v>
@@ -2020,7 +2020,7 @@
         <v>-0.4686</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8897</v>
+        <v>-0.9056999999999999</v>
       </c>
       <c r="E35" t="n">
         <v>-1.1592</v>
@@ -2066,7 +2066,7 @@
         <v>-0.4765</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8975</v>
+        <v>-0.9135</v>
       </c>
       <c r="E36" t="n">
         <v>-1.1787</v>
@@ -2112,7 +2112,7 @@
         <v>-0.6656</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0866</v>
+        <v>-1.0999</v>
       </c>
       <c r="E37" t="n">
         <v>-1.6466</v>
@@ -2158,7 +2158,7 @@
         <v>-0.6965</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1174</v>
+        <v>-1.1303</v>
       </c>
       <c r="E38" t="n">
         <v>-1.7229</v>
@@ -2204,7 +2204,7 @@
         <v>-0.71</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1309</v>
+        <v>-1.1436</v>
       </c>
       <c r="E39" t="n">
         <v>-1.7563</v>
@@ -2250,7 +2250,7 @@
         <v>-0.8085</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E40" t="n">
         <v>-2</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.6582</v>
+        <v>-2.652</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.0745</v>
+        <v>-1.072</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4952</v>
+        <v>-1.5005</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.6582</v>
+        <v>-2.652</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.6582</v>
+        <v>-1.652</v>
       </c>
       <c r="G41" t="n">
         <v>-1</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.6582</v>
+        <v>-1.652</v>
       </c>
       <c r="I41" t="n">
         <v>-1.6659</v>
@@ -2342,7 +2342,7 @@
         <v>-1.1268</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.5475</v>
+        <v>-1.5545</v>
       </c>
       <c r="E42" t="n">
         <v>-2.7875</v>

--- a/database/event/7485/event_7485_evp_summary.xlsx
+++ b/database/event/7485/event_7485_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.3149</v>
+        <v>8.7875</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7654</v>
+        <v>3.5522</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2671</v>
+        <v>3.3291</v>
       </c>
       <c r="E2" t="n">
-        <v>9.3149</v>
+        <v>8.7875</v>
       </c>
       <c r="F2" t="n">
-        <v>4.454</v>
+        <v>4.2854</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8609</v>
+        <v>4.5021</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3591</v>
+        <v>9.6128</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3437</v>
+        <v>4.9982</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8609</v>
+        <v>4.5021</v>
       </c>
       <c r="K2" t="n">
         <v>99</v>
@@ -529,7 +529,7 @@
         <v>148</v>
       </c>
       <c r="M2" t="n">
-        <v>9.204599999999999</v>
+        <v>9.500299999999999</v>
       </c>
       <c r="N2" t="n">
         <v>247</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.8432</v>
+        <v>7.3361</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1705</v>
+        <v>2.9655</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6808</v>
+        <v>2.6739</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8432</v>
+        <v>7.3361</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4401</v>
+        <v>3.3113</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4032</v>
+        <v>4.0248</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4401</v>
+        <v>6.1805</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7883</v>
+        <v>3.2136</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4032</v>
+        <v>4.0248</v>
       </c>
       <c r="K3" t="n">
         <v>99</v>
@@ -575,7 +575,7 @@
         <v>148</v>
       </c>
       <c r="M3" t="n">
-        <v>7.1915</v>
+        <v>7.2384</v>
       </c>
       <c r="N3" t="n">
         <v>247</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.4704</v>
+        <v>7.1017</v>
       </c>
       <c r="C4" t="n">
-        <v>3.0198</v>
+        <v>2.8708</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5323</v>
+        <v>2.568</v>
       </c>
       <c r="E4" t="n">
-        <v>7.4704</v>
+        <v>7.1017</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0782</v>
+        <v>3.0748</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3922</v>
+        <v>4.0269</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0782</v>
+        <v>5.3472</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4949</v>
+        <v>2.7803</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3922</v>
+        <v>4.0269</v>
       </c>
       <c r="K4" t="n">
         <v>99</v>
@@ -621,7 +621,7 @@
         <v>148</v>
       </c>
       <c r="M4" t="n">
-        <v>6.8871</v>
+        <v>6.8072</v>
       </c>
       <c r="N4" t="n">
         <v>247</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.1465</v>
+        <v>6.7215</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8889</v>
+        <v>2.7171</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4033</v>
+        <v>2.3964</v>
       </c>
       <c r="E5" t="n">
-        <v>7.1465</v>
+        <v>6.7215</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8563</v>
+        <v>2.83</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2902</v>
+        <v>3.8915</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8563</v>
+        <v>4.485</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3151</v>
+        <v>2.332</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2902</v>
+        <v>3.8915</v>
       </c>
       <c r="K5" t="n">
         <v>109</v>
@@ -667,7 +667,7 @@
         <v>120</v>
       </c>
       <c r="M5" t="n">
-        <v>6.6053</v>
+        <v>6.2235</v>
       </c>
       <c r="N5" t="n">
         <v>229</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7277</v>
+        <v>5.1859</v>
       </c>
       <c r="C6" t="n">
-        <v>2.3153</v>
+        <v>2.0963</v>
       </c>
       <c r="D6" t="n">
-        <v>1.838</v>
+        <v>1.7032</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7277</v>
+        <v>5.1859</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1729</v>
+        <v>3.189</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5548</v>
+        <v>1.9969</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1729</v>
+        <v>3.6428</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1996</v>
+        <v>3.7926</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5548</v>
+        <v>1.9969</v>
       </c>
       <c r="K6" t="n">
         <v>122</v>
@@ -713,7 +713,7 @@
         <v>127</v>
       </c>
       <c r="M6" t="n">
-        <v>5.7544</v>
+        <v>5.7895</v>
       </c>
       <c r="N6" t="n">
         <v>249</v>
@@ -722,461 +722,461 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.4034</v>
+        <v>4.1688</v>
       </c>
       <c r="C7" t="n">
-        <v>1.78</v>
+        <v>1.6852</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3104</v>
+        <v>1.244</v>
       </c>
       <c r="E7" t="n">
-        <v>4.4034</v>
+        <v>4.1688</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7781</v>
+        <v>1.2264</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6253</v>
+        <v>2.9425</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7781</v>
+        <v>1.2264</v>
       </c>
       <c r="I7" t="n">
-        <v>3.0623</v>
+        <v>1.2768</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6253</v>
+        <v>2.9425</v>
       </c>
       <c r="K7" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="L7" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6876</v>
+        <v>4.2193</v>
       </c>
       <c r="N7" t="n">
-        <v>229</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0647</v>
+        <v>3.6421</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6431</v>
+        <v>1.4723</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1755</v>
+        <v>1.0062</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0647</v>
+        <v>3.6421</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8273</v>
+        <v>3.2753</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2373</v>
+        <v>0.3668</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8273</v>
+        <v>6.0538</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8343</v>
+        <v>3.1477</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2373</v>
+        <v>0.3668</v>
       </c>
       <c r="K8" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="L8" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="M8" t="n">
-        <v>4.0716</v>
+        <v>3.5145</v>
       </c>
       <c r="N8" t="n">
-        <v>249</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3355</v>
+        <v>3.4457</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3483</v>
+        <v>1.3929</v>
       </c>
       <c r="D9" t="n">
-        <v>0.885</v>
+        <v>0.9175</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3355</v>
+        <v>3.4457</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2071</v>
+        <v>2.7042</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1284</v>
+        <v>0.7415</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2071</v>
+        <v>2.7042</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2257</v>
+        <v>2.7042</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1284</v>
+        <v>0.7415</v>
       </c>
       <c r="K9" t="n">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="L9" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3541</v>
+        <v>3.4457</v>
       </c>
       <c r="N9" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6822</v>
+        <v>3.3868</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0842</v>
+        <v>1.3691</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6247</v>
+        <v>0.891</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6822</v>
+        <v>3.3868</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1055</v>
+        <v>2.0402</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5767</v>
+        <v>1.3466</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1055</v>
+        <v>2.0402</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1232</v>
+        <v>1.0608</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5767</v>
+        <v>1.3466</v>
       </c>
       <c r="K10" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L10" t="n">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6999</v>
+        <v>2.4074</v>
       </c>
       <c r="N10" t="n">
-        <v>175</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6347</v>
+        <v>3.2197</v>
       </c>
       <c r="C11" t="n">
-        <v>1.065</v>
+        <v>1.3015</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6058</v>
+        <v>0.8155</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6347</v>
+        <v>3.2197</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2955</v>
+        <v>2.1988</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3392</v>
+        <v>1.0209</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2955</v>
+        <v>2.1988</v>
       </c>
       <c r="I11" t="n">
-        <v>1.05</v>
+        <v>2.2892</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3392</v>
+        <v>1.0209</v>
       </c>
       <c r="K11" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="L11" t="n">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="M11" t="n">
-        <v>2.3892</v>
+        <v>3.3101</v>
       </c>
       <c r="N11" t="n">
-        <v>229</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5777</v>
+        <v>3.0545</v>
       </c>
       <c r="C12" t="n">
-        <v>1.042</v>
+        <v>1.2347</v>
       </c>
       <c r="D12" t="n">
-        <v>0.583</v>
+        <v>0.7409</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5777</v>
+        <v>3.0545</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7979</v>
+        <v>2.4908</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7798</v>
+        <v>0.5637</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7979</v>
+        <v>3.2897</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7979</v>
+        <v>1.7105</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7798</v>
+        <v>0.5637</v>
       </c>
       <c r="K12" t="n">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="L12" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5777</v>
+        <v>2.2742</v>
       </c>
       <c r="N12" t="n">
-        <v>125</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2769</v>
+        <v>2.6167</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9204</v>
+        <v>1.0578</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4632</v>
+        <v>0.5433</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2769</v>
+        <v>2.6167</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4648</v>
+        <v>2.4845</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8121</v>
+        <v>0.1322</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4648</v>
+        <v>2.4845</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4648</v>
+        <v>2.4845</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8121</v>
+        <v>0.1322</v>
       </c>
       <c r="K13" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="L13" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2769</v>
+        <v>2.6167</v>
       </c>
       <c r="N13" t="n">
-        <v>190</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0329</v>
+        <v>2.5328</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8218</v>
+        <v>1.0238</v>
       </c>
       <c r="D14" t="n">
-        <v>0.366</v>
+        <v>0.5054</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0329</v>
+        <v>2.5328</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0529</v>
+        <v>2.132</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.02</v>
+        <v>0.4008</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0529</v>
+        <v>2.132</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0529</v>
+        <v>2.2197</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.02</v>
+        <v>0.4008</v>
       </c>
       <c r="K14" t="n">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="L14" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0329</v>
+        <v>2.6205</v>
       </c>
       <c r="N14" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7207</v>
+        <v>2.2345</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6956</v>
+        <v>0.9033</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2416</v>
+        <v>0.3708</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7207</v>
+        <v>2.2345</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6362</v>
+        <v>1.7287</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.5058</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6362</v>
+        <v>1.7287</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3262</v>
+        <v>1.7998</v>
       </c>
       <c r="J15" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.5058</v>
       </c>
       <c r="K15" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="L15" t="n">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4107</v>
+        <v>2.3056</v>
       </c>
       <c r="N15" t="n">
-        <v>229</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7157</v>
+        <v>2.2185</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6935</v>
+        <v>0.8968</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2396</v>
+        <v>0.3635</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7157</v>
+        <v>2.2185</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9287</v>
+        <v>2.6127</v>
       </c>
       <c r="G16" t="n">
-        <v>0.787</v>
+        <v>-0.3942</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9287</v>
+        <v>3.7192</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9365</v>
+        <v>1.9338</v>
       </c>
       <c r="J16" t="n">
-        <v>0.787</v>
+        <v>-0.3942</v>
       </c>
       <c r="K16" t="n">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="L16" t="n">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7235</v>
+        <v>1.5396</v>
       </c>
       <c r="N16" t="n">
-        <v>175</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.531</v>
+        <v>2.2003</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6189</v>
+        <v>0.8894</v>
       </c>
       <c r="D17" t="n">
-        <v>0.166</v>
+        <v>0.3553</v>
       </c>
       <c r="E17" t="n">
-        <v>1.531</v>
+        <v>2.2003</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1136</v>
+        <v>2.6503</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5826</v>
+        <v>-0.45</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1136</v>
+        <v>2.6503</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1314</v>
+        <v>2.7593</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5826</v>
+        <v>-0.45</v>
       </c>
       <c r="K17" t="n">
         <v>122</v>
@@ -1219,7 +1219,7 @@
         <v>127</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5488</v>
+        <v>2.3093</v>
       </c>
       <c r="N17" t="n">
         <v>249</v>
@@ -1228,875 +1228,875 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4297</v>
+        <v>2.0754</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5779</v>
+        <v>0.8389</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1257</v>
+        <v>0.2989</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4297</v>
+        <v>2.0754</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9566</v>
+        <v>1.2282</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5269</v>
+        <v>0.8472</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9566</v>
+        <v>1.2282</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5859</v>
+        <v>1.2787</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5269</v>
+        <v>0.8472</v>
       </c>
       <c r="K18" t="n">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="L18" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="M18" t="n">
-        <v>1.059</v>
+        <v>2.1259</v>
       </c>
       <c r="N18" t="n">
-        <v>247</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1986</v>
+        <v>1.9615</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4845</v>
+        <v>0.7929</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0336</v>
+        <v>0.2475</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1986</v>
+        <v>1.9615</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7522</v>
+        <v>0.4613</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4464</v>
+        <v>1.5002</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7522</v>
+        <v>0.4613</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7585</v>
+        <v>0.4613</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4464</v>
+        <v>1.5002</v>
       </c>
       <c r="K19" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="L19" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2049</v>
+        <v>1.9615</v>
       </c>
       <c r="N19" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0696</v>
+        <v>1.4393</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4324</v>
+        <v>0.5818</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0178</v>
+        <v>0.0118</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0696</v>
+        <v>1.4393</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0696</v>
+        <v>0.8998</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.5395</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0696</v>
+        <v>0.8998</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0696</v>
+        <v>0.8998</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.5395</v>
       </c>
       <c r="K20" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0696</v>
+        <v>1.4393</v>
       </c>
       <c r="N20" t="n">
-        <v>115</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0464</v>
+        <v>1.3516</v>
       </c>
       <c r="C21" t="n">
-        <v>0.423</v>
+        <v>0.5464</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.027</v>
+        <v>-0.0278</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0464</v>
+        <v>1.3516</v>
       </c>
       <c r="F21" t="n">
-        <v>0.628</v>
+        <v>1.3516</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4184</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.628</v>
+        <v>1.3516</v>
       </c>
       <c r="I21" t="n">
-        <v>0.628</v>
+        <v>1.3516</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4184</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="L21" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0464</v>
+        <v>1.3516</v>
       </c>
       <c r="N21" t="n">
-        <v>190</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ewjerkz</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.851</v>
+        <v>1.1793</v>
       </c>
       <c r="C22" t="n">
-        <v>0.344</v>
+        <v>0.4767</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1049</v>
+        <v>-0.1056</v>
       </c>
       <c r="E22" t="n">
-        <v>0.851</v>
+        <v>1.1793</v>
       </c>
       <c r="F22" t="n">
-        <v>0.851</v>
+        <v>1.2186</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.0393</v>
       </c>
       <c r="H22" t="n">
-        <v>0.851</v>
+        <v>1.2186</v>
       </c>
       <c r="I22" t="n">
-        <v>0.851</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.0393</v>
       </c>
       <c r="K22" t="n">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M22" t="n">
-        <v>0.851</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>88</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7252999999999999</v>
+        <v>1.1136</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2932</v>
+        <v>0.4502</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.155</v>
+        <v>-0.1353</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7252999999999999</v>
+        <v>1.1136</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.59</v>
+        <v>1.7839</v>
       </c>
       <c r="G23" t="n">
-        <v>1.3153</v>
+        <v>-0.6703</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.59</v>
+        <v>1.7839</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.595</v>
+        <v>1.7839</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3153</v>
+        <v>-0.6703</v>
       </c>
       <c r="K23" t="n">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="L23" t="n">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7202999999999999</v>
+        <v>1.1136</v>
       </c>
       <c r="N23" t="n">
-        <v>249</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>ewjerkz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6754</v>
+        <v>1.0802</v>
       </c>
       <c r="C24" t="n">
-        <v>0.273</v>
+        <v>0.4367</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1748</v>
+        <v>-0.1504</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6754</v>
+        <v>1.0802</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6754</v>
+        <v>1.0802</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6754</v>
+        <v>1.0802</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6754</v>
+        <v>1.0802</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6754</v>
+        <v>1.0802</v>
       </c>
       <c r="N24" t="n">
-        <v>115</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4246</v>
+        <v>1.0754</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1716</v>
+        <v>0.4347</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2747</v>
+        <v>-0.1525</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4246</v>
+        <v>1.0754</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4246</v>
+        <v>-0.1849</v>
       </c>
       <c r="G25" t="n">
-        <v>-1</v>
+        <v>1.2603</v>
       </c>
       <c r="H25" t="n">
-        <v>1.4246</v>
+        <v>-0.1849</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4246</v>
+        <v>-0.1925</v>
       </c>
       <c r="J25" t="n">
-        <v>-1</v>
+        <v>1.2603</v>
       </c>
       <c r="K25" t="n">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="L25" t="n">
-        <v>44</v>
+        <v>127</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4246000000000001</v>
+        <v>1.0678</v>
       </c>
       <c r="N25" t="n">
-        <v>125</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3098</v>
+        <v>0.8794</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1252</v>
+        <v>0.3555</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3205</v>
+        <v>-0.241</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3098</v>
+        <v>0.8794</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1826</v>
+        <v>1.1386</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1272</v>
+        <v>-0.2592</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1826</v>
+        <v>1.1386</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1826</v>
+        <v>1.1386</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1272</v>
+        <v>-0.2592</v>
       </c>
       <c r="K26" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="L26" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3098</v>
+        <v>0.8794000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>190</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2814</v>
+        <v>0.8739</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1138</v>
+        <v>0.3533</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3318</v>
+        <v>-0.2435</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2814</v>
+        <v>0.8739</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8739</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4086</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8739</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8739</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4086</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="L27" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2813999999999999</v>
+        <v>0.8739</v>
       </c>
       <c r="N27" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1346</v>
+        <v>0.7726</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0544</v>
+        <v>0.3123</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3903</v>
+        <v>-0.2892</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1346</v>
+        <v>0.7726</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4876</v>
+        <v>0.5093</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.353</v>
+        <v>0.2633</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4876</v>
+        <v>0.5093</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4876</v>
+        <v>0.5093</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.353</v>
+        <v>0.2633</v>
       </c>
       <c r="K28" t="n">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="L28" t="n">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1346</v>
+        <v>0.7726</v>
       </c>
       <c r="N28" t="n">
-        <v>125</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.132</v>
+        <v>0.7247</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0534</v>
+        <v>0.2929</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3913</v>
+        <v>-0.3108</v>
       </c>
       <c r="E29" t="n">
-        <v>0.132</v>
+        <v>0.7247</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4963</v>
+        <v>0.9647</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3643</v>
+        <v>-0.24</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4963</v>
+        <v>0.9647</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4963</v>
+        <v>0.9647</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3643</v>
+        <v>-0.24</v>
       </c>
       <c r="K29" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="L29" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="M29" t="n">
-        <v>0.132</v>
+        <v>0.7247</v>
       </c>
       <c r="N29" t="n">
-        <v>190</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0693</v>
+        <v>0.3534</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.028</v>
+        <v>0.1429</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4715</v>
+        <v>-0.4785</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0693</v>
+        <v>0.3534</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0693</v>
+        <v>0.8109</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.4575</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0693</v>
+        <v>0.8109</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0693</v>
+        <v>0.8109</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.4575</v>
       </c>
       <c r="K30" t="n">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0693</v>
+        <v>0.3533999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>57</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1583</v>
+        <v>0.193</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.064</v>
+        <v>0.078</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.507</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1583</v>
+        <v>0.193</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5906</v>
+        <v>1.6478</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.7489</v>
+        <v>-1.4548</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5906</v>
+        <v>1.6478</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4787</v>
+        <v>1.7156</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.7489</v>
+        <v>-1.4548</v>
       </c>
       <c r="K31" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="L31" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2702</v>
+        <v>0.2607999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>229</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>arrozdoce</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8278</v>
+        <v>0.1249</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3346</v>
+        <v>0.0505</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7737000000000001</v>
+        <v>-0.5816</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8278</v>
+        <v>0.1249</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8278</v>
+        <v>0.1249</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8278</v>
+        <v>0.1249</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8278</v>
+        <v>0.1249</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8278</v>
+        <v>0.1249</v>
       </c>
       <c r="N32" t="n">
-        <v>88</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>arrozdoce</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1</v>
+        <v>-0.5134</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4042</v>
+        <v>-0.2075</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8423</v>
+        <v>-0.8698</v>
       </c>
       <c r="E33" t="n">
-        <v>-1</v>
+        <v>-0.5134</v>
       </c>
       <c r="F33" t="n">
-        <v>-1</v>
+        <v>-0.5134</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1</v>
+        <v>-0.5134</v>
       </c>
       <c r="I33" t="n">
-        <v>-1</v>
+        <v>-0.5134</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1</v>
+        <v>-0.5134</v>
       </c>
       <c r="N33" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0228</v>
+        <v>-0.6204</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4135</v>
+        <v>-0.2508</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8514</v>
+        <v>-0.9181</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0228</v>
+        <v>-0.6204</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7472</v>
+        <v>-0.6204</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.77</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7472</v>
+        <v>-0.6204</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7534999999999999</v>
+        <v>-0.6204</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.77</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="L34" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0165</v>
+        <v>-0.6204</v>
       </c>
       <c r="N34" t="n">
-        <v>249</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>roman</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1592</v>
+        <v>-0.7357</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4686</v>
+        <v>-0.2974</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9056999999999999</v>
+        <v>-0.9701</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1592</v>
+        <v>-0.7357</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1592</v>
+        <v>-0.7357</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1592</v>
+        <v>-0.7357</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.1592</v>
+        <v>-0.7357</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1592</v>
+        <v>-0.7357</v>
       </c>
       <c r="N35" t="n">
-        <v>115</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>roman</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1787</v>
+        <v>-0.9649</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4765</v>
+        <v>-0.39</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9135</v>
+        <v>-1.0736</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1787</v>
+        <v>-0.9649</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1787</v>
+        <v>-0.9649</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1787</v>
+        <v>-0.9649</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1787</v>
+        <v>-0.9649</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1787</v>
+        <v>-0.9649</v>
       </c>
       <c r="N36" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.6466</v>
+        <v>-0.988</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6656</v>
+        <v>-0.3994</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0999</v>
+        <v>-1.084</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.6466</v>
+        <v>-0.988</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7527</v>
+        <v>-0.4849</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.8939</v>
+        <v>-0.5031</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7527</v>
+        <v>-0.4849</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7527</v>
+        <v>-0.4849</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.8939</v>
+        <v>-0.5031</v>
       </c>
       <c r="K37" t="n">
         <v>106</v>
@@ -2139,7 +2139,7 @@
         <v>84</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.6466</v>
+        <v>-0.988</v>
       </c>
       <c r="N37" t="n">
         <v>190</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.7229</v>
+        <v>-1.1994</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.6965</v>
+        <v>-0.4848</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1303</v>
+        <v>-1.1795</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.7229</v>
+        <v>-1.1994</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.7229</v>
+        <v>-1.1994</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.7229</v>
+        <v>-1.1994</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.7229</v>
+        <v>-1.1994</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.7229</v>
+        <v>-1.1994</v>
       </c>
       <c r="N38" t="n">
         <v>88</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7563</v>
+        <v>-1.2743</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.71</v>
+        <v>-0.5151</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1436</v>
+        <v>-1.2133</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7563</v>
+        <v>-1.2743</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.7563</v>
+        <v>-1.2743</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.7563</v>
+        <v>-1.2743</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.7563</v>
+        <v>-1.2743</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.7563</v>
+        <v>-1.2743</v>
       </c>
       <c r="N39" t="n">
         <v>88</v>
@@ -2250,7 +2250,7 @@
         <v>-0.8085</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2407</v>
+        <v>-1.5409</v>
       </c>
       <c r="E40" t="n">
         <v>-2</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.652</v>
+        <v>-2.4763</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.072</v>
+        <v>-1.001</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5005</v>
+        <v>-1.7559</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.652</v>
+        <v>-2.4763</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.652</v>
+        <v>-1.4763</v>
       </c>
       <c r="G41" t="n">
         <v>-1</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.652</v>
+        <v>-1.4763</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.6659</v>
+        <v>-1.537</v>
       </c>
       <c r="J41" t="n">
         <v>-1</v>
@@ -2323,7 +2323,7 @@
         <v>59</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.6659</v>
+        <v>-2.537</v>
       </c>
       <c r="N41" t="n">
         <v>175</v>
@@ -2336,31 +2336,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.7875</v>
+        <v>-2.7474</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.1268</v>
+        <v>-1.1106</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.5545</v>
+        <v>-1.8783</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.7875</v>
+        <v>-2.7474</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.352</v>
+        <v>-1.3969</v>
       </c>
       <c r="G42" t="n">
-        <v>-1.4355</v>
+        <v>-1.3505</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.352</v>
+        <v>-1.3969</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.0958</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.4355</v>
+        <v>-1.3505</v>
       </c>
       <c r="K42" t="n">
         <v>99</v>
@@ -2369,7 +2369,7 @@
         <v>148</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.5313</v>
+        <v>-2.0768</v>
       </c>
       <c r="N42" t="n">
         <v>247</v>
@@ -2475,10 +2475,10 @@
         <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1592</v>
+        <v>1.1054</v>
       </c>
       <c r="J2" t="n">
-        <v>25.5024</v>
+        <v>24.3188</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>1.36</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>19.8814</v>
+        <v>20.1476</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>1.32</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8118</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>17.8596</v>
+        <v>18.1962</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>1.25</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6314</v>
+        <v>0.6691</v>
       </c>
       <c r="J5" t="n">
-        <v>13.8908</v>
+        <v>14.7202</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6931</v>
+        <v>-0.6338</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.2482</v>
+        <v>-13.9436</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.13</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3277</v>
+        <v>0.3537</v>
       </c>
       <c r="J7" t="n">
-        <v>7.2094</v>
+        <v>7.7814</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.209</v>
+        <v>0.2017</v>
       </c>
       <c r="J8" t="n">
-        <v>4.598</v>
+        <v>4.4374</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1922</v>
+        <v>-0.1427</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.2284</v>
+        <v>-3.1394</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>0.72</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4625</v>
+        <v>-0.3006</v>
       </c>
       <c r="J10" t="n">
-        <v>-10.175</v>
+        <v>-6.6132</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>0.54</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6976</v>
+        <v>-0.4691</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.3472</v>
+        <v>-10.3202</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.57</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3766</v>
+        <v>1.2399</v>
       </c>
       <c r="J12" t="n">
-        <v>30.2852</v>
+        <v>27.2778</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>1.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0332</v>
+        <v>1.0144</v>
       </c>
       <c r="J13" t="n">
-        <v>22.7304</v>
+        <v>22.3168</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>1.31</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8345</v>
+        <v>0.8269</v>
       </c>
       <c r="J14" t="n">
-        <v>18.359</v>
+        <v>18.1918</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3485</v>
+        <v>-0.274</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.667</v>
+        <v>-6.028</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.61</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1379</v>
+        <v>-1.1312</v>
       </c>
       <c r="J16" t="n">
-        <v>-25.0338</v>
+        <v>-24.8864</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7125</v>
+        <v>0.8817</v>
       </c>
       <c r="J17" t="n">
-        <v>15.675</v>
+        <v>19.3974</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.29</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5258</v>
+        <v>0.6219</v>
       </c>
       <c r="J18" t="n">
-        <v>11.5676</v>
+        <v>13.6818</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>0.76</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4276</v>
+        <v>-0.2721</v>
       </c>
       <c r="J19" t="n">
-        <v>-9.4072</v>
+        <v>-5.9862</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>0.68</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.536</v>
+        <v>-0.3489</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.792</v>
+        <v>-7.6758</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6863</v>
+        <v>-0.46</v>
       </c>
       <c r="J21" t="n">
-        <v>-15.0986</v>
+        <v>-10.12</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3275</v>
+        <v>0.2689</v>
       </c>
       <c r="J22" t="n">
-        <v>5.5675</v>
+        <v>4.5713</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>0.99</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0822</v>
+        <v>0.031</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3974</v>
+        <v>0.527</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>0.65</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.3504</v>
       </c>
       <c r="J24" t="n">
-        <v>-8.902900000000001</v>
+        <v>-5.9568</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>0.53</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6861</v>
+        <v>-0.4626</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.6637</v>
+        <v>-7.8642</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.48</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7493</v>
+        <v>-0.509</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.7381</v>
+        <v>-8.653</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.86</v>
       </c>
       <c r="I27" t="n">
-        <v>1.032</v>
+        <v>0.95</v>
       </c>
       <c r="J27" t="n">
-        <v>17.544</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>1.52</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6687</v>
+        <v>0.6118</v>
       </c>
       <c r="J28" t="n">
-        <v>11.3679</v>
+        <v>10.4006</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>1.46</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5956</v>
+        <v>0.55</v>
       </c>
       <c r="J29" t="n">
-        <v>10.1252</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>1.13</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1389</v>
+        <v>0.1704</v>
       </c>
       <c r="J30" t="n">
-        <v>2.3613</v>
+        <v>2.8968</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>1.05</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0101</v>
+        <v>0.0528</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1717</v>
+        <v>0.8976</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.74</v>
       </c>
       <c r="I32" t="n">
-        <v>1.6673</v>
+        <v>1.4359</v>
       </c>
       <c r="J32" t="n">
-        <v>31.6787</v>
+        <v>27.2821</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.44</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0908</v>
+        <v>1.0599</v>
       </c>
       <c r="J33" t="n">
-        <v>20.7252</v>
+        <v>20.1381</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.108</v>
+        <v>0.1797</v>
       </c>
       <c r="J34" t="n">
-        <v>2.052</v>
+        <v>3.4143</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>1.06</v>
       </c>
       <c r="I35" t="n">
-        <v>0.108</v>
+        <v>0.1797</v>
       </c>
       <c r="J35" t="n">
-        <v>2.052</v>
+        <v>3.4143</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.79</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7577</v>
+        <v>-0.705</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.3963</v>
+        <v>-13.395</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.38</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6652</v>
+        <v>0.8172</v>
       </c>
       <c r="J37" t="n">
-        <v>12.6388</v>
+        <v>15.5268</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>0.78</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3787</v>
+        <v>-0.2439</v>
       </c>
       <c r="J38" t="n">
-        <v>-7.1953</v>
+        <v>-4.6341</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>0.76</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4085</v>
+        <v>-0.2635</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.7615</v>
+        <v>-5.0065</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.75</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4231</v>
+        <v>-0.2732</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.0389</v>
+        <v>-5.1908</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.72</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4659</v>
+        <v>-0.3022</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.8521</v>
+        <v>-5.7418</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.71</v>
       </c>
       <c r="I42" t="n">
-        <v>1.539</v>
+        <v>1.084</v>
       </c>
       <c r="J42" t="n">
-        <v>27.702</v>
+        <v>19.512</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.61</v>
       </c>
       <c r="I43" t="n">
-        <v>1.352</v>
+        <v>0.9654</v>
       </c>
       <c r="J43" t="n">
-        <v>24.336</v>
+        <v>17.3772</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.42</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9597</v>
+        <v>0.7351</v>
       </c>
       <c r="J44" t="n">
-        <v>17.2746</v>
+        <v>13.2318</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>1.13</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2482</v>
+        <v>0.3379</v>
       </c>
       <c r="J45" t="n">
-        <v>4.4676</v>
+        <v>6.0822</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>1.04</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0767</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.1584</v>
+        <v>1.3806</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.24</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5768</v>
+        <v>0.5596</v>
       </c>
       <c r="J47" t="n">
-        <v>10.3824</v>
+        <v>10.0728</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>0.68</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.4203</v>
+        <v>-0.3121</v>
       </c>
       <c r="J48" t="n">
-        <v>-7.5654</v>
+        <v>-5.6178</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.68</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4203</v>
+        <v>-0.3121</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.5654</v>
+        <v>-5.6178</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.45</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.8348</v>
+        <v>-9.444599999999999</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.3</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9524</v>
+        <v>-0.6657</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.1432</v>
+        <v>-11.9826</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.29</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8399</v>
+        <v>0.6167</v>
       </c>
       <c r="J52" t="n">
-        <v>18.4778</v>
+        <v>13.5674</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>1.13</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4332</v>
+        <v>0.3785</v>
       </c>
       <c r="J53" t="n">
-        <v>9.5304</v>
+        <v>8.327</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>1.08</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2733</v>
+        <v>0.2713</v>
       </c>
       <c r="J54" t="n">
-        <v>6.0126</v>
+        <v>5.9686</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0653</v>
+        <v>-0.0162</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.4366</v>
+        <v>-0.3564</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.87</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5152</v>
+        <v>-0.4551</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.3344</v>
+        <v>-10.0122</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.05</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2045</v>
+        <v>0.1927</v>
       </c>
       <c r="J57" t="n">
-        <v>4.499</v>
+        <v>4.2394</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>0.9</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1354</v>
+        <v>-0.1163</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.9788</v>
+        <v>-2.5586</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>0.88</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1713</v>
+        <v>-0.1384</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.7686</v>
+        <v>-3.0448</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>0.73</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4365</v>
+        <v>-0.2861</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.603</v>
+        <v>-6.2942</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.59</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6278</v>
+        <v>-0.4182</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.8116</v>
+        <v>-9.2004</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.31</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5239</v>
+        <v>0.4186</v>
       </c>
       <c r="J62" t="n">
-        <v>12.5736</v>
+        <v>10.0464</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3143</v>
+        <v>0.2726</v>
       </c>
       <c r="J63" t="n">
-        <v>7.5432</v>
+        <v>6.5424</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>0.97</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1041</v>
+        <v>-0.0527</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.4984</v>
+        <v>-1.2648</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1652</v>
+        <v>-0.091</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.9648</v>
+        <v>-2.184</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.76</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4456</v>
+        <v>-0.2817</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.6944</v>
+        <v>-6.7608</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.34</v>
       </c>
       <c r="I67" t="n">
-        <v>0.528</v>
+        <v>0.406</v>
       </c>
       <c r="J67" t="n">
-        <v>12.672</v>
+        <v>9.744</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.31</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4892</v>
+        <v>0.3853</v>
       </c>
       <c r="J68" t="n">
-        <v>11.7408</v>
+        <v>9.247199999999999</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>1.12</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1934</v>
+        <v>0.1866</v>
       </c>
       <c r="J69" t="n">
-        <v>4.6416</v>
+        <v>4.4784</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>0.99</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.0335</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.1576</v>
+        <v>-0.804</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.92</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2288</v>
+        <v>-0.1262</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.4912</v>
+        <v>-3.0288</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>1.64</v>
       </c>
       <c r="I72" t="n">
-        <v>1.5206</v>
+        <v>1.0621</v>
       </c>
       <c r="J72" t="n">
-        <v>33.4532</v>
+        <v>23.3662</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>1.25</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.5451</v>
       </c>
       <c r="J73" t="n">
-        <v>15.5122</v>
+        <v>11.9922</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4336</v>
+        <v>0.4003</v>
       </c>
       <c r="J74" t="n">
-        <v>9.539199999999999</v>
+        <v>8.8066</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1008</v>
+        <v>-0.0343</v>
       </c>
       <c r="J75" t="n">
-        <v>-2.2176</v>
+        <v>-0.7546</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.9869</v>
+        <v>-0.9602000000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>-21.7118</v>
+        <v>-21.1244</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>1.26</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4782</v>
+        <v>0.4666</v>
       </c>
       <c r="J77" t="n">
-        <v>10.5204</v>
+        <v>10.2652</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>1.02</v>
       </c>
       <c r="I78" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>1.848</v>
+        <v>1.584</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0221</v>
+        <v>0.0046</v>
       </c>
       <c r="J79" t="n">
-        <v>0.4862</v>
+        <v>0.1012</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2512</v>
+        <v>-0.1525</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.5264</v>
+        <v>-3.355</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.68</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5403</v>
+        <v>-0.3515</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.8866</v>
+        <v>-7.733</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.75</v>
       </c>
       <c r="I82" t="n">
-        <v>1.7015</v>
+        <v>1.1913</v>
       </c>
       <c r="J82" t="n">
-        <v>37.433</v>
+        <v>26.2086</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>0.715</v>
+        <v>0.555</v>
       </c>
       <c r="J83" t="n">
-        <v>15.73</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>1.23</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6401</v>
+        <v>0.5129</v>
       </c>
       <c r="J84" t="n">
-        <v>14.0822</v>
+        <v>11.2838</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>0.83</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.649</v>
+        <v>-0.5888</v>
       </c>
       <c r="J85" t="n">
-        <v>-14.278</v>
+        <v>-12.9536</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7922</v>
+        <v>-0.744</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.4284</v>
+        <v>-16.368</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3438</v>
+        <v>0.3651</v>
       </c>
       <c r="J87" t="n">
-        <v>7.5636</v>
+        <v>8.0322</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2978</v>
+        <v>0.3267</v>
       </c>
       <c r="J88" t="n">
-        <v>6.5516</v>
+        <v>7.1874</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>0.9</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.224</v>
+        <v>-0.1329</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.928</v>
+        <v>-2.9238</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.274</v>
+        <v>-0.1655</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.028</v>
+        <v>-3.641</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.86</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.29</v>
+        <v>-0.1761</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.38</v>
+        <v>-3.8742</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.34</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5756</v>
+        <v>0.5444</v>
       </c>
       <c r="J92" t="n">
-        <v>12.0876</v>
+        <v>11.4324</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>1.18</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3587</v>
+        <v>0.3761</v>
       </c>
       <c r="J93" t="n">
-        <v>7.5327</v>
+        <v>7.8981</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0607</v>
+        <v>-0.0351</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.2747</v>
+        <v>-0.7371</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>0.86</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.29</v>
+        <v>-0.1761</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.09</v>
+        <v>-3.6981</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>0.58</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6683</v>
+        <v>-0.4462</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.0343</v>
+        <v>-9.370200000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.51</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2662</v>
+        <v>0.8932</v>
       </c>
       <c r="J97" t="n">
-        <v>26.5902</v>
+        <v>18.7572</v>
       </c>
     </row>
     <row r="98">
@@ -6355,10 +6355,10 @@
         <v>1.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2325</v>
+        <v>0.2852</v>
       </c>
       <c r="J99" t="n">
-        <v>4.8825</v>
+        <v>5.9892</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>1.04</v>
       </c>
       <c r="I100" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.1312</v>
       </c>
       <c r="J100" t="n">
-        <v>1.4994</v>
+        <v>2.7552</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.98</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2055</v>
+        <v>-0.1324</v>
       </c>
       <c r="J101" t="n">
-        <v>-4.3155</v>
+        <v>-2.7804</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.06</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2042</v>
+        <v>0.1971</v>
       </c>
       <c r="J102" t="n">
-        <v>4.6966</v>
+        <v>4.5333</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.063</v>
+        <v>-0.0639</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.449</v>
+        <v>-1.4697</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>0.8</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3479</v>
+        <v>-0.2241</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.0017</v>
+        <v>-5.1543</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>0.8</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3479</v>
+        <v>-0.2241</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.0017</v>
+        <v>-5.1543</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.78</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3787</v>
+        <v>-0.2439</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.710100000000001</v>
+        <v>-5.6097</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.31</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.6267</v>
       </c>
       <c r="J107" t="n">
-        <v>19.3476</v>
+        <v>14.4141</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>1.21</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5975</v>
+        <v>0.4865</v>
       </c>
       <c r="J108" t="n">
-        <v>13.7425</v>
+        <v>11.1895</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>1.17</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4863</v>
+        <v>0.4286</v>
       </c>
       <c r="J109" t="n">
-        <v>11.1849</v>
+        <v>9.857799999999999</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1045</v>
+        <v>0.1637</v>
       </c>
       <c r="J110" t="n">
-        <v>2.4035</v>
+        <v>3.7651</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>1.03</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0347</v>
+        <v>0.096</v>
       </c>
       <c r="J111" t="n">
-        <v>0.7981</v>
+        <v>2.208</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.74</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8959</v>
+        <v>0.623</v>
       </c>
       <c r="J112" t="n">
-        <v>15.2303</v>
+        <v>10.591</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.68</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8324</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="J113" t="n">
-        <v>14.1508</v>
+        <v>9.9994</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>1.49</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6125</v>
+        <v>0.4762</v>
       </c>
       <c r="J114" t="n">
-        <v>10.4125</v>
+        <v>8.0954</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>1.39</v>
       </c>
       <c r="I115" t="n">
-        <v>0.473</v>
+        <v>0.416</v>
       </c>
       <c r="J115" t="n">
-        <v>8.041</v>
+        <v>7.072</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>1.02</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0564</v>
+        <v>-0.0047</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.9588</v>
+        <v>-0.0799</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.16</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4221</v>
+        <v>0.3542</v>
       </c>
       <c r="J117" t="n">
-        <v>7.1757</v>
+        <v>6.0214</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>0.92</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0625</v>
+        <v>-0.0767</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.0625</v>
+        <v>-1.3039</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.64</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.538</v>
+        <v>-0.3597</v>
       </c>
       <c r="J119" t="n">
-        <v>-9.146000000000001</v>
+        <v>-6.1149</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>0.55</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.6602</v>
+        <v>-0.4439</v>
       </c>
       <c r="J120" t="n">
-        <v>-11.2234</v>
+        <v>-7.5463</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.48</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7493</v>
+        <v>-0.509</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.7381</v>
+        <v>-8.653</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.62</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9112</v>
+        <v>0.8263</v>
       </c>
       <c r="J122" t="n">
-        <v>20.9576</v>
+        <v>19.0049</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.16</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3381</v>
+        <v>0.3588</v>
       </c>
       <c r="J123" t="n">
-        <v>7.7763</v>
+        <v>8.2524</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>0.86</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2821</v>
+        <v>-0.1731</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.4883</v>
+        <v>-3.9813</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>0.59</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.6523</v>
+        <v>-0.4343</v>
       </c>
       <c r="J125" t="n">
-        <v>-15.0029</v>
+        <v>-9.988899999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.58</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6645</v>
+        <v>-0.4435</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.2835</v>
+        <v>-10.2005</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.65</v>
       </c>
       <c r="I127" t="n">
-        <v>1.5056</v>
+        <v>1.0534</v>
       </c>
       <c r="J127" t="n">
-        <v>34.6288</v>
+        <v>24.2282</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.38</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9661</v>
+        <v>0.7094</v>
       </c>
       <c r="J128" t="n">
-        <v>22.2203</v>
+        <v>16.3162</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>1.33</v>
       </c>
       <c r="I129" t="n">
-        <v>0.8546</v>
+        <v>0.6431</v>
       </c>
       <c r="J129" t="n">
-        <v>19.6558</v>
+        <v>14.7913</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>0.96</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2996</v>
+        <v>-0.22</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.8908</v>
+        <v>-5.06</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.74</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8702</v>
+        <v>-0.8293</v>
       </c>
       <c r="J131" t="n">
-        <v>-20.0146</v>
+        <v>-19.0739</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.62</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9483</v>
+        <v>0.867</v>
       </c>
       <c r="J132" t="n">
-        <v>18.0177</v>
+        <v>16.473</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>0.96</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0371</v>
+        <v>-0.0491</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.7049</v>
+        <v>-0.9329</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.5042</v>
+        <v>-0.3292</v>
       </c>
       <c r="J134" t="n">
-        <v>-9.579800000000001</v>
+        <v>-6.2548</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>0.62</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5972</v>
+        <v>-0.3951</v>
       </c>
       <c r="J135" t="n">
-        <v>-11.3468</v>
+        <v>-7.5069</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.44</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8166</v>
+        <v>-0.5599</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.5154</v>
+        <v>-10.6381</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>2.61</v>
       </c>
       <c r="I137" t="n">
-        <v>2.4041</v>
+        <v>2.0761</v>
       </c>
       <c r="J137" t="n">
-        <v>45.6779</v>
+        <v>39.4459</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.72</v>
       </c>
       <c r="I138" t="n">
-        <v>1.5384</v>
+        <v>1.087</v>
       </c>
       <c r="J138" t="n">
-        <v>29.2296</v>
+        <v>20.653</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0723</v>
+        <v>0.1631</v>
       </c>
       <c r="J139" t="n">
-        <v>1.3737</v>
+        <v>3.0989</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.607</v>
+        <v>-0.5375</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.533</v>
+        <v>-10.2125</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.86</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.632</v>
+        <v>-0.5648</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.008</v>
+        <v>-10.7312</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.01</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1475</v>
+        <v>0.1176</v>
       </c>
       <c r="J142" t="n">
-        <v>2.5075</v>
+        <v>1.9992</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>0.87</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1533</v>
+        <v>-0.137</v>
       </c>
       <c r="J143" t="n">
-        <v>-2.6061</v>
+        <v>-2.329</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>0.77</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3237</v>
+        <v>-0.2399</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.5029</v>
+        <v>-4.0783</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.63</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5548</v>
+        <v>-0.3703</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.4316</v>
+        <v>-6.2951</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.51</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7134</v>
+        <v>-0.4823</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.1278</v>
+        <v>-8.1991</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>2.23</v>
       </c>
       <c r="I147" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J147" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.48</v>
       </c>
       <c r="I148" t="n">
-        <v>1.1059</v>
+        <v>1.0862</v>
       </c>
       <c r="J148" t="n">
-        <v>18.8003</v>
+        <v>18.4654</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.21</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4575</v>
+        <v>0.5545</v>
       </c>
       <c r="J149" t="n">
-        <v>7.7775</v>
+        <v>9.426500000000001</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>1.08</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1208</v>
+        <v>0.2088</v>
       </c>
       <c r="J150" t="n">
-        <v>2.0536</v>
+        <v>3.5496</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.77</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8303</v>
+        <v>-0.7842</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.1151</v>
+        <v>-13.3314</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.17</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3445</v>
+        <v>0.3873</v>
       </c>
       <c r="J152" t="n">
-        <v>8.268000000000001</v>
+        <v>9.295199999999999</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>0.96</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1079</v>
+        <v>-0.062</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.5896</v>
+        <v>-1.488</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>0.95</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1294</v>
+        <v>-0.0745</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.1056</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1496</v>
+        <v>-0.0867</v>
       </c>
       <c r="J155" t="n">
-        <v>-3.5904</v>
+        <v>-2.0808</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>0.91</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2057</v>
+        <v>-0.1215</v>
       </c>
       <c r="J156" t="n">
-        <v>-4.9368</v>
+        <v>-2.916</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.947</v>
+        <v>0.9275</v>
       </c>
       <c r="J157" t="n">
-        <v>22.728</v>
+        <v>22.26</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4259</v>
+        <v>0.4068</v>
       </c>
       <c r="J158" t="n">
-        <v>10.2216</v>
+        <v>9.763199999999999</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4259</v>
+        <v>0.4068</v>
       </c>
       <c r="J159" t="n">
-        <v>10.2216</v>
+        <v>9.763199999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>1.06</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1822</v>
+        <v>0.2114</v>
       </c>
       <c r="J160" t="n">
-        <v>4.3728</v>
+        <v>5.0736</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>0.76</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7929</v>
+        <v>-0.7478</v>
       </c>
       <c r="J161" t="n">
-        <v>-19.0296</v>
+        <v>-17.9472</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.85</v>
       </c>
       <c r="I162" t="n">
-        <v>1.7859</v>
+        <v>1.5201</v>
       </c>
       <c r="J162" t="n">
-        <v>30.3603</v>
+        <v>25.8417</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>1.62</v>
       </c>
       <c r="I163" t="n">
-        <v>1.3693</v>
+        <v>1.2504</v>
       </c>
       <c r="J163" t="n">
-        <v>23.2781</v>
+        <v>21.2568</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>1.28</v>
       </c>
       <c r="I164" t="n">
-        <v>0.61</v>
+        <v>0.7133</v>
       </c>
       <c r="J164" t="n">
-        <v>10.37</v>
+        <v>12.1261</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>1.17</v>
       </c>
       <c r="I165" t="n">
-        <v>0.3481</v>
+        <v>0.4476</v>
       </c>
       <c r="J165" t="n">
-        <v>5.9177</v>
+        <v>7.6092</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>1.01</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.121</v>
+        <v>-0.0371</v>
       </c>
       <c r="J166" t="n">
-        <v>-2.057</v>
+        <v>-0.6307</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.5</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8421</v>
+        <v>1.0525</v>
       </c>
       <c r="J167" t="n">
-        <v>14.3157</v>
+        <v>17.8925</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>0.85</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2073</v>
+        <v>-0.1657</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.5241</v>
+        <v>-2.8169</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.64</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.5536</v>
+        <v>-0.3669</v>
       </c>
       <c r="J169" t="n">
-        <v>-9.411199999999999</v>
+        <v>-6.2373</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.58</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6333</v>
+        <v>-0.4231</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.7661</v>
+        <v>-7.1927</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.42</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.8304</v>
+        <v>-0.5704</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.1168</v>
+        <v>-9.6968</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.39</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6418</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="J172" t="n">
-        <v>14.1196</v>
+        <v>13.1626</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.03</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1037</v>
+        <v>0.0738</v>
       </c>
       <c r="J173" t="n">
-        <v>2.2814</v>
+        <v>1.6236</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>0.91</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2021</v>
+        <v>-0.1204</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.4462</v>
+        <v>-2.6488</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>0.87</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2703</v>
+        <v>-0.1641</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.9466</v>
+        <v>-3.6102</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.3524</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.9196</v>
+        <v>-7.7528</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>1.67</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9131</v>
+        <v>0.8292</v>
       </c>
       <c r="J177" t="n">
-        <v>20.0882</v>
+        <v>18.2424</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>1.31</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4943</v>
+        <v>0.424</v>
       </c>
       <c r="J178" t="n">
-        <v>10.8746</v>
+        <v>9.327999999999999</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>1.02</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0074</v>
+        <v>0.034</v>
       </c>
       <c r="J179" t="n">
-        <v>0.1628</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>0.9</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2586</v>
+        <v>-0.1473</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.6892</v>
+        <v>-3.2406</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.7</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5391</v>
+        <v>-0.3486</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.8602</v>
+        <v>-7.6692</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.49</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1542</v>
+        <v>1.1079</v>
       </c>
       <c r="J182" t="n">
-        <v>20.7756</v>
+        <v>19.9422</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9859</v>
+        <v>0.9992</v>
       </c>
       <c r="J183" t="n">
-        <v>17.7462</v>
+        <v>17.9856</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.32</v>
       </c>
       <c r="I184" t="n">
-        <v>0.7769</v>
+        <v>0.8164</v>
       </c>
       <c r="J184" t="n">
-        <v>13.9842</v>
+        <v>14.6952</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>1.26</v>
       </c>
       <c r="I185" t="n">
-        <v>0.6078</v>
+        <v>0.6843</v>
       </c>
       <c r="J185" t="n">
-        <v>10.9404</v>
+        <v>12.3174</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>1.01</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.0974</v>
+        <v>-0.0174</v>
       </c>
       <c r="J186" t="n">
-        <v>-1.7532</v>
+        <v>-0.3132</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.08</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2668</v>
+        <v>0.2713</v>
       </c>
       <c r="J187" t="n">
-        <v>4.8024</v>
+        <v>4.8834</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2668</v>
+        <v>0.2713</v>
       </c>
       <c r="J188" t="n">
-        <v>4.8024</v>
+        <v>4.8834</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>0.73</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.4298</v>
+        <v>-0.2836</v>
       </c>
       <c r="J189" t="n">
-        <v>-7.7364</v>
+        <v>-5.1048</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.71</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4594</v>
+        <v>-0.3027</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.2692</v>
+        <v>-5.4486</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.46</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.7851</v>
+        <v>-0.5356</v>
       </c>
       <c r="J191" t="n">
-        <v>-14.1318</v>
+        <v>-9.6408</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.19</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4438</v>
+        <v>0.5087</v>
       </c>
       <c r="J192" t="n">
-        <v>7.9884</v>
+        <v>9.156599999999999</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>0.84</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2269</v>
+        <v>-0.1766</v>
       </c>
       <c r="J193" t="n">
-        <v>-4.0842</v>
+        <v>-3.1788</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>0.77</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3621</v>
+        <v>-0.244</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.5178</v>
+        <v>-4.392</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4849</v>
+        <v>-0.3203</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.728199999999999</v>
+        <v>-5.7654</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>0.52</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7103</v>
+        <v>-0.4793</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.7854</v>
+        <v>-8.6274</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.94</v>
       </c>
       <c r="I197" t="n">
-        <v>1.9271</v>
+        <v>1.6256</v>
       </c>
       <c r="J197" t="n">
-        <v>34.6878</v>
+        <v>29.2608</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.53</v>
       </c>
       <c r="I198" t="n">
-        <v>1.1966</v>
+        <v>1.1436</v>
       </c>
       <c r="J198" t="n">
-        <v>21.5388</v>
+        <v>20.5848</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>1.21</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4483</v>
+        <v>0.5493</v>
       </c>
       <c r="J199" t="n">
-        <v>8.0694</v>
+        <v>9.8874</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>1.14</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2753</v>
+        <v>0.3712</v>
       </c>
       <c r="J200" t="n">
-        <v>4.9554</v>
+        <v>6.6816</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>1.07</v>
       </c>
       <c r="I201" t="n">
-        <v>0.0849</v>
+        <v>0.1734</v>
       </c>
       <c r="J201" t="n">
-        <v>1.5282</v>
+        <v>3.1212</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>1.53</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7516</v>
+        <v>0.6685</v>
       </c>
       <c r="J202" t="n">
-        <v>16.5352</v>
+        <v>14.707</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>1.43</v>
       </c>
       <c r="I203" t="n">
-        <v>0.6354</v>
+        <v>0.5569</v>
       </c>
       <c r="J203" t="n">
-        <v>13.9788</v>
+        <v>12.2518</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>1.2</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3306</v>
+        <v>0.2866</v>
       </c>
       <c r="J204" t="n">
-        <v>7.2732</v>
+        <v>6.3052</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>1.04</v>
       </c>
       <c r="I205" t="n">
-        <v>0.0421</v>
+        <v>0.0665</v>
       </c>
       <c r="J205" t="n">
-        <v>0.9262</v>
+        <v>1.463</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.54</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7331</v>
+        <v>-0.4962</v>
       </c>
       <c r="J206" t="n">
-        <v>-16.1282</v>
+        <v>-10.9164</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.21</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4098</v>
+        <v>0.3587</v>
       </c>
       <c r="J207" t="n">
-        <v>9.015599999999999</v>
+        <v>7.8914</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.2</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3956</v>
+        <v>0.3445</v>
       </c>
       <c r="J208" t="n">
-        <v>8.703200000000001</v>
+        <v>7.579</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>0.95</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.119</v>
+        <v>-0.0728</v>
       </c>
       <c r="J209" t="n">
-        <v>-2.618</v>
+        <v>-1.6016</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>0.82</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3456</v>
+        <v>-0.2148</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.6032</v>
+        <v>-4.7256</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.65</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5784</v>
+        <v>-0.3794</v>
       </c>
       <c r="J211" t="n">
-        <v>-12.7248</v>
+        <v>-8.3468</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>1.24</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4845</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J212" t="n">
-        <v>11.1435</v>
+        <v>12.972</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>0.98</v>
       </c>
       <c r="I213" t="n">
-        <v>0.0029</v>
+        <v>-0.0224</v>
       </c>
       <c r="J213" t="n">
-        <v>0.0667</v>
+        <v>-0.5152</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3313</v>
+        <v>-0.2139</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.6199</v>
+        <v>-4.9197</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.72</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4654</v>
+        <v>-0.3019</v>
       </c>
       <c r="J215" t="n">
-        <v>-10.7042</v>
+        <v>-6.9437</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.63</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5864</v>
+        <v>-0.3871</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.4872</v>
+        <v>-8.9033</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.54</v>
       </c>
       <c r="I217" t="n">
-        <v>1.3063</v>
+        <v>1.1951</v>
       </c>
       <c r="J217" t="n">
-        <v>30.0449</v>
+        <v>27.4873</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.39</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9993</v>
+        <v>0.9907</v>
       </c>
       <c r="J218" t="n">
-        <v>22.9839</v>
+        <v>22.7861</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>1.15</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3844</v>
+        <v>0.4391</v>
       </c>
       <c r="J219" t="n">
-        <v>8.841200000000001</v>
+        <v>10.0993</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>1.05</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0877</v>
+        <v>0.1548</v>
       </c>
       <c r="J220" t="n">
-        <v>2.0171</v>
+        <v>3.5604</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>0.82</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6794</v>
+        <v>-0.6206</v>
       </c>
       <c r="J221" t="n">
-        <v>-15.6262</v>
+        <v>-14.2738</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.06</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1884</v>
+        <v>0.1834</v>
       </c>
       <c r="J222" t="n">
-        <v>3.5796</v>
+        <v>3.4846</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>0.95</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.5694</v>
+        <v>-1.311</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1037</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J224" t="n">
-        <v>-1.9703</v>
+        <v>-1.5428</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>0.89</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2131</v>
+        <v>-0.1364</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.0489</v>
+        <v>-2.5916</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.75</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4346</v>
+        <v>-0.2784</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.257400000000001</v>
+        <v>-5.2896</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>1.53</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2508</v>
+        <v>1.1647</v>
       </c>
       <c r="J227" t="n">
-        <v>23.7652</v>
+        <v>22.1293</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>1.35</v>
       </c>
       <c r="I228" t="n">
-        <v>0.8709</v>
+        <v>0.8895</v>
       </c>
       <c r="J228" t="n">
-        <v>16.5471</v>
+        <v>16.9005</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>1.24</v>
       </c>
       <c r="I229" t="n">
-        <v>0.5793</v>
+        <v>0.6442</v>
       </c>
       <c r="J229" t="n">
-        <v>11.0067</v>
+        <v>12.2398</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>1.16</v>
       </c>
       <c r="I230" t="n">
-        <v>0.3705</v>
+        <v>0.449</v>
       </c>
       <c r="J230" t="n">
-        <v>7.0395</v>
+        <v>8.531000000000001</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>1.04</v>
       </c>
       <c r="I231" t="n">
-        <v>0.0262</v>
+        <v>0.1036</v>
       </c>
       <c r="J231" t="n">
-        <v>0.4978</v>
+        <v>1.9684</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>0.87</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.1044</v>
+        <v>-0.1107</v>
       </c>
       <c r="J232" t="n">
-        <v>-1.6704</v>
+        <v>-1.7712</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>0.71</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.3602</v>
+        <v>-0.2821</v>
       </c>
       <c r="J233" t="n">
-        <v>-5.7632</v>
+        <v>-4.5136</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>0.63</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.5098</v>
+        <v>-0.3548</v>
       </c>
       <c r="J234" t="n">
-        <v>-8.1568</v>
+        <v>-5.6768</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>0.61</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5421</v>
+        <v>-0.373</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.6736</v>
+        <v>-5.968</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.47</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7395</v>
+        <v>-0.5039</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.832</v>
+        <v>-8.0624</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.8</v>
       </c>
       <c r="I237" t="n">
-        <v>1.6459</v>
+        <v>1.4365</v>
       </c>
       <c r="J237" t="n">
-        <v>26.3344</v>
+        <v>22.984</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>1.73</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5197</v>
+        <v>1.3571</v>
       </c>
       <c r="J238" t="n">
-        <v>24.3152</v>
+        <v>21.7136</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>1.66</v>
       </c>
       <c r="I239" t="n">
-        <v>1.3886</v>
+        <v>1.2771</v>
       </c>
       <c r="J239" t="n">
-        <v>22.2176</v>
+        <v>20.4336</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>1.32</v>
       </c>
       <c r="I240" t="n">
-        <v>0.651</v>
+        <v>0.7785</v>
       </c>
       <c r="J240" t="n">
-        <v>10.416</v>
+        <v>12.456</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>1.06</v>
       </c>
       <c r="I241" t="n">
-        <v>0.0229</v>
+        <v>0.1146</v>
       </c>
       <c r="J241" t="n">
-        <v>0.3664</v>
+        <v>1.8336</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.09</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2537</v>
+        <v>0.1992</v>
       </c>
       <c r="J242" t="n">
-        <v>5.3277</v>
+        <v>4.1832</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.03</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1404</v>
+        <v>0.0921</v>
       </c>
       <c r="J243" t="n">
-        <v>2.9484</v>
+        <v>1.9341</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>0.89</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.189</v>
+        <v>-0.134</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.969</v>
+        <v>-2.814</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>0.72</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4687</v>
+        <v>-0.3035</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.842700000000001</v>
+        <v>-6.3735</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.71</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4825</v>
+        <v>-0.3131</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.1325</v>
+        <v>-6.5751</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>2.06</v>
       </c>
       <c r="I247" t="n">
-        <v>1.2738</v>
+        <v>1.1199</v>
       </c>
       <c r="J247" t="n">
-        <v>26.7498</v>
+        <v>23.5179</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>1.51</v>
       </c>
       <c r="I248" t="n">
-        <v>0.71</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="J248" t="n">
-        <v>14.91</v>
+        <v>13.2636</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>1.19</v>
       </c>
       <c r="I249" t="n">
-        <v>0.2759</v>
+        <v>0.2687</v>
       </c>
       <c r="J249" t="n">
-        <v>5.7939</v>
+        <v>5.6427</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>0.7</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5507</v>
+        <v>-0.3569</v>
       </c>
       <c r="J250" t="n">
-        <v>-11.5647</v>
+        <v>-7.4949</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.61</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6587</v>
+        <v>-0.439</v>
       </c>
       <c r="J251" t="n">
-        <v>-13.8327</v>
+        <v>-9.218999999999999</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.62</v>
       </c>
       <c r="I252" t="n">
-        <v>1.3792</v>
+        <v>1.2545</v>
       </c>
       <c r="J252" t="n">
-        <v>27.584</v>
+        <v>25.09</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1.49</v>
       </c>
       <c r="I253" t="n">
-        <v>1.1217</v>
+        <v>1.097</v>
       </c>
       <c r="J253" t="n">
-        <v>22.434</v>
+        <v>21.94</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>1.32</v>
       </c>
       <c r="I254" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.8073</v>
       </c>
       <c r="J254" t="n">
-        <v>14.304</v>
+        <v>16.146</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>1.24</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5254</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="J255" t="n">
-        <v>10.508</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>1.15</v>
       </c>
       <c r="I256" t="n">
-        <v>0.3053</v>
+        <v>0.4007</v>
       </c>
       <c r="J256" t="n">
-        <v>6.106</v>
+        <v>8.013999999999999</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>0.99</v>
       </c>
       <c r="I257" t="n">
-        <v>0.0804</v>
+        <v>0.0384</v>
       </c>
       <c r="J257" t="n">
-        <v>1.608</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>0.8</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2684</v>
+        <v>-0.2102</v>
       </c>
       <c r="J258" t="n">
-        <v>-5.368</v>
+        <v>-4.204</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>0.75</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3647</v>
+        <v>-0.2576</v>
       </c>
       <c r="J259" t="n">
-        <v>-7.294</v>
+        <v>-5.152</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>0.64</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.5394</v>
+        <v>-0.3603</v>
       </c>
       <c r="J260" t="n">
-        <v>-10.788</v>
+        <v>-7.206</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.59</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6083</v>
+        <v>-0.4072</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.166</v>
+        <v>-8.144</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.99</v>
       </c>
       <c r="I262" t="n">
-        <v>1.9536</v>
+        <v>1.6542</v>
       </c>
       <c r="J262" t="n">
-        <v>33.2112</v>
+        <v>28.1214</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>1.89</v>
       </c>
       <c r="I263" t="n">
-        <v>1.8121</v>
+        <v>1.5425</v>
       </c>
       <c r="J263" t="n">
-        <v>30.8057</v>
+        <v>26.2225</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>1.34</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7028</v>
+        <v>0.8277</v>
       </c>
       <c r="J264" t="n">
-        <v>11.9476</v>
+        <v>14.0709</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>1.32</v>
       </c>
       <c r="I265" t="n">
-        <v>0.6592</v>
+        <v>0.7832</v>
       </c>
       <c r="J265" t="n">
-        <v>11.2064</v>
+        <v>13.3144</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.91</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5142</v>
+        <v>-0.4365</v>
       </c>
       <c r="J266" t="n">
-        <v>-8.741400000000001</v>
+        <v>-7.4205</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>0.86</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.137</v>
+        <v>-0.132</v>
       </c>
       <c r="J267" t="n">
-        <v>-2.329</v>
+        <v>-2.244</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>0.83</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.186</v>
+        <v>-0.1656</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.162</v>
+        <v>-2.8152</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>0.78</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2661</v>
+        <v>-0.2187</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.5237</v>
+        <v>-3.7179</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.58</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.6008</v>
+        <v>-0.4062</v>
       </c>
       <c r="J270" t="n">
-        <v>-10.2136</v>
+        <v>-6.9054</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.4</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.8357</v>
+        <v>-0.5747</v>
       </c>
       <c r="J271" t="n">
-        <v>-14.2069</v>
+        <v>-9.7699</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>1.69</v>
       </c>
       <c r="I272" t="n">
-        <v>0.8985</v>
+        <v>0.8159</v>
       </c>
       <c r="J272" t="n">
-        <v>16.173</v>
+        <v>14.6862</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>1.43</v>
       </c>
       <c r="I273" t="n">
-        <v>0.6067</v>
+        <v>0.5384</v>
       </c>
       <c r="J273" t="n">
-        <v>10.9206</v>
+        <v>9.6912</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>1.26</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3798</v>
+        <v>0.3478</v>
       </c>
       <c r="J274" t="n">
-        <v>6.8364</v>
+        <v>6.2604</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>0.96</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1783</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="J275" t="n">
-        <v>-3.2094</v>
+        <v>-1.5822</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.89</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2967</v>
+        <v>-0.1706</v>
       </c>
       <c r="J276" t="n">
-        <v>-5.3406</v>
+        <v>-3.0708</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>0.96</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.0187</v>
+        <v>-0.0416</v>
       </c>
       <c r="J277" t="n">
-        <v>-0.3366</v>
+        <v>-0.7488</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>0.92</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0961</v>
+        <v>-0.0921</v>
       </c>
       <c r="J278" t="n">
-        <v>-1.7298</v>
+        <v>-1.6578</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>0.79</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3402</v>
+        <v>-0.2274</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.1236</v>
+        <v>-4.0932</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>0.79</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3402</v>
+        <v>-0.2274</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.1236</v>
+        <v>-4.0932</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>0.66</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5337</v>
+        <v>-0.3518</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.6066</v>
+        <v>-6.3324</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>1.32</v>
       </c>
       <c r="I282" t="n">
-        <v>0.5712</v>
+        <v>0.6835</v>
       </c>
       <c r="J282" t="n">
-        <v>13.7088</v>
+        <v>16.404</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>1.17</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3654</v>
+        <v>0.4076</v>
       </c>
       <c r="J283" t="n">
-        <v>8.769600000000001</v>
+        <v>9.782400000000001</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>0.91</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1801</v>
+        <v>-0.1156</v>
       </c>
       <c r="J284" t="n">
-        <v>-4.3224</v>
+        <v>-2.7744</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>0.71</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4923</v>
+        <v>-0.3182</v>
       </c>
       <c r="J285" t="n">
-        <v>-11.8152</v>
+        <v>-7.6368</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.53</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.7195</v>
+        <v>-0.4853</v>
       </c>
       <c r="J286" t="n">
-        <v>-17.268</v>
+        <v>-11.6472</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1.52</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2445</v>
+        <v>1.1584</v>
       </c>
       <c r="J287" t="n">
-        <v>29.868</v>
+        <v>27.8016</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>1.45</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1025</v>
+        <v>1.0693</v>
       </c>
       <c r="J288" t="n">
-        <v>26.46</v>
+        <v>25.6632</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>1.22</v>
       </c>
       <c r="I289" t="n">
-        <v>0.5468</v>
+        <v>0.6022</v>
       </c>
       <c r="J289" t="n">
-        <v>13.1232</v>
+        <v>14.4528</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>1.15</v>
       </c>
       <c r="I290" t="n">
-        <v>0.3576</v>
+        <v>0.4293</v>
       </c>
       <c r="J290" t="n">
-        <v>8.5824</v>
+        <v>10.3032</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>0.84</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.642</v>
+        <v>-0.5786</v>
       </c>
       <c r="J291" t="n">
-        <v>-15.408</v>
+        <v>-13.8864</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.49</v>
       </c>
       <c r="I292" t="n">
-        <v>0.7661</v>
+        <v>0.9543</v>
       </c>
       <c r="J292" t="n">
-        <v>17.6203</v>
+        <v>21.9489</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>0.99</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.0098</v>
+        <v>-0.0176</v>
       </c>
       <c r="J293" t="n">
-        <v>-0.2254</v>
+        <v>-0.4048</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>0.97</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.062</v>
+        <v>-0.0472</v>
       </c>
       <c r="J294" t="n">
-        <v>-1.426</v>
+        <v>-1.0856</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.96</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.0891</v>
+        <v>-0.0601</v>
       </c>
       <c r="J295" t="n">
-        <v>-2.0493</v>
+        <v>-1.3823</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.39</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.8834</v>
+        <v>-0.6131</v>
       </c>
       <c r="J296" t="n">
-        <v>-20.3182</v>
+        <v>-14.1013</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>1.76</v>
       </c>
       <c r="I297" t="n">
-        <v>1.7297</v>
+        <v>1.4788</v>
       </c>
       <c r="J297" t="n">
-        <v>39.7831</v>
+        <v>34.0124</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.17</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4758</v>
+        <v>0.493</v>
       </c>
       <c r="J298" t="n">
-        <v>10.9434</v>
+        <v>11.339</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.12</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3149</v>
+        <v>0.3657</v>
       </c>
       <c r="J299" t="n">
-        <v>7.2427</v>
+        <v>8.411099999999999</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>0.99</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1681</v>
+        <v>-0.0944</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.8663</v>
+        <v>-2.1712</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>0.78</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.768</v>
+        <v>-0.7177</v>
       </c>
       <c r="J301" t="n">
-        <v>-17.664</v>
+        <v>-16.5071</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>1.32</v>
       </c>
       <c r="I302" t="n">
-        <v>0.8629</v>
+        <v>0.8534</v>
       </c>
       <c r="J302" t="n">
-        <v>20.7096</v>
+        <v>20.4816</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>1.31</v>
       </c>
       <c r="I303" t="n">
-        <v>0.8401</v>
+        <v>0.8302</v>
       </c>
       <c r="J303" t="n">
-        <v>20.1624</v>
+        <v>19.9248</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>1.29</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7937</v>
+        <v>0.7834</v>
       </c>
       <c r="J304" t="n">
-        <v>19.0488</v>
+        <v>18.8016</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>0.96</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2799</v>
+        <v>-0.2057</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.7176</v>
+        <v>-4.9368</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>0.9</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4624</v>
+        <v>-0.3922</v>
       </c>
       <c r="J306" t="n">
-        <v>-11.0976</v>
+        <v>-9.412800000000001</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>1.32</v>
       </c>
       <c r="I307" t="n">
-        <v>0.5329</v>
+        <v>0.6369</v>
       </c>
       <c r="J307" t="n">
-        <v>12.7896</v>
+        <v>15.2856</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>1.1</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2118</v>
+        <v>0.2374</v>
       </c>
       <c r="J308" t="n">
-        <v>5.0832</v>
+        <v>5.6976</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>1.08</v>
       </c>
       <c r="I309" t="n">
-        <v>0.1756</v>
+        <v>0.1967</v>
       </c>
       <c r="J309" t="n">
-        <v>4.2144</v>
+        <v>4.7208</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>1.05</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1147</v>
+        <v>0.1326</v>
       </c>
       <c r="J310" t="n">
-        <v>2.7528</v>
+        <v>3.1824</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.65</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5903</v>
+        <v>-0.3874</v>
       </c>
       <c r="J311" t="n">
-        <v>-14.1672</v>
+        <v>-9.297599999999999</v>
       </c>
     </row>
     <row r="312">
@@ -14875,10 +14875,10 @@
         <v>1.77</v>
       </c>
       <c r="I312" t="n">
-        <v>1.765</v>
+        <v>1.5041</v>
       </c>
       <c r="J312" t="n">
-        <v>38.83</v>
+        <v>33.0902</v>
       </c>
     </row>
     <row r="313">
@@ -14915,10 +14915,10 @@
         <v>1.44</v>
       </c>
       <c r="I313" t="n">
-        <v>1.1357</v>
+        <v>1.0813</v>
       </c>
       <c r="J313" t="n">
-        <v>24.9854</v>
+        <v>23.7886</v>
       </c>
     </row>
     <row r="314">
@@ -14955,10 +14955,10 @@
         <v>1.1</v>
       </c>
       <c r="I314" t="n">
-        <v>0.2782</v>
+        <v>0.3181</v>
       </c>
       <c r="J314" t="n">
-        <v>6.1204</v>
+        <v>6.9982</v>
       </c>
     </row>
     <row r="315">
@@ -14995,10 +14995,10 @@
         <v>0.79</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.6835</v>
       </c>
       <c r="J315" t="n">
-        <v>-16.1788</v>
+        <v>-15.037</v>
       </c>
     </row>
     <row r="316">
@@ -15035,10 +15035,10 @@
         <v>0.55</v>
       </c>
       <c r="I316" t="n">
-        <v>-1.2527</v>
+        <v>-1.2629</v>
       </c>
       <c r="J316" t="n">
-        <v>-27.5594</v>
+        <v>-27.7838</v>
       </c>
     </row>
     <row r="317">
@@ -15075,10 +15075,10 @@
         <v>1.37</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6327</v>
+        <v>0.7692</v>
       </c>
       <c r="J317" t="n">
-        <v>13.9194</v>
+        <v>16.9224</v>
       </c>
     </row>
     <row r="318">
@@ -15115,10 +15115,10 @@
         <v>1.02</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0997</v>
+        <v>0.0805</v>
       </c>
       <c r="J318" t="n">
-        <v>2.1934</v>
+        <v>1.771</v>
       </c>
     </row>
     <row r="319">
@@ -15155,10 +15155,10 @@
         <v>0.93</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1394</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.0668</v>
+        <v>-2.0614</v>
       </c>
     </row>
     <row r="320">
@@ -15195,10 +15195,10 @@
         <v>0.75</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4382</v>
+        <v>-0.2801</v>
       </c>
       <c r="J320" t="n">
-        <v>-9.6404</v>
+        <v>-6.1622</v>
       </c>
     </row>
     <row r="321">
@@ -15235,10 +15235,10 @@
         <v>0.59</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.6475</v>
+        <v>-0.431</v>
       </c>
       <c r="J321" t="n">
-        <v>-14.245</v>
+        <v>-9.481999999999999</v>
       </c>
     </row>
     <row r="322">
@@ -15275,10 +15275,10 @@
         <v>1.51</v>
       </c>
       <c r="I322" t="n">
-        <v>1.2827</v>
+        <v>1.1764</v>
       </c>
       <c r="J322" t="n">
-        <v>44.8945</v>
+        <v>41.174</v>
       </c>
     </row>
     <row r="323">
@@ -15315,10 +15315,10 @@
         <v>1.17</v>
       </c>
       <c r="I323" t="n">
-        <v>0.5135</v>
+        <v>0.5018</v>
       </c>
       <c r="J323" t="n">
-        <v>17.9725</v>
+        <v>17.563</v>
       </c>
     </row>
     <row r="324">
@@ -15355,10 +15355,10 @@
         <v>1.13</v>
       </c>
       <c r="I324" t="n">
-        <v>0.3948</v>
+        <v>0.3992</v>
       </c>
       <c r="J324" t="n">
-        <v>13.818</v>
+        <v>13.972</v>
       </c>
     </row>
     <row r="325">
@@ -15395,10 +15395,10 @@
         <v>1.09</v>
       </c>
       <c r="I325" t="n">
-        <v>0.2541</v>
+        <v>0.2921</v>
       </c>
       <c r="J325" t="n">
-        <v>8.8935</v>
+        <v>10.2235</v>
       </c>
     </row>
     <row r="326">
@@ -15435,10 +15435,10 @@
         <v>0.7</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-0.906</v>
       </c>
       <c r="J326" t="n">
-        <v>-32.83</v>
+        <v>-31.71</v>
       </c>
     </row>
     <row r="327">
@@ -15475,10 +15475,10 @@
         <v>1.17</v>
       </c>
       <c r="I327" t="n">
-        <v>0.3509</v>
+        <v>0.3931</v>
       </c>
       <c r="J327" t="n">
-        <v>12.2815</v>
+        <v>13.7585</v>
       </c>
     </row>
     <row r="328">
@@ -15515,10 +15515,10 @@
         <v>1.1</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2402</v>
+        <v>0.2549</v>
       </c>
       <c r="J328" t="n">
-        <v>8.407</v>
+        <v>8.9215</v>
       </c>
     </row>
     <row r="329">
@@ -15555,10 +15555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1414</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="J329" t="n">
-        <v>-4.949</v>
+        <v>-2.975</v>
       </c>
     </row>
     <row r="330">
@@ -15595,10 +15595,10 @@
         <v>0.88</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2512</v>
+        <v>-0.1525</v>
       </c>
       <c r="J330" t="n">
-        <v>-8.792</v>
+        <v>-5.3375</v>
       </c>
     </row>
     <row r="331">
@@ -15635,10 +15635,10 @@
         <v>0.75</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4468</v>
+        <v>-0.2845</v>
       </c>
       <c r="J331" t="n">
-        <v>-15.638</v>
+        <v>-9.9575</v>
       </c>
     </row>
     <row r="332">
@@ -15675,10 +15675,10 @@
         <v>1.62</v>
       </c>
       <c r="I332" t="n">
-        <v>1.3684</v>
+        <v>1.2501</v>
       </c>
       <c r="J332" t="n">
-        <v>24.6312</v>
+        <v>22.5018</v>
       </c>
     </row>
     <row r="333">
@@ -15715,10 +15715,10 @@
         <v>1.45</v>
       </c>
       <c r="I333" t="n">
-        <v>1.0236</v>
+        <v>1.0439</v>
       </c>
       <c r="J333" t="n">
-        <v>18.4248</v>
+        <v>18.7902</v>
       </c>
     </row>
     <row r="334">
@@ -15755,10 +15755,10 @@
         <v>1.39</v>
       </c>
       <c r="I334" t="n">
-        <v>0.8793</v>
+        <v>0.9492</v>
       </c>
       <c r="J334" t="n">
-        <v>15.8274</v>
+        <v>17.0856</v>
       </c>
     </row>
     <row r="335">
@@ -15795,10 +15795,10 @@
         <v>1.34</v>
       </c>
       <c r="I335" t="n">
-        <v>0.7488</v>
+        <v>0.8468</v>
       </c>
       <c r="J335" t="n">
-        <v>13.4784</v>
+        <v>15.2424</v>
       </c>
     </row>
     <row r="336">
@@ -15835,10 +15835,10 @@
         <v>1.14</v>
       </c>
       <c r="I336" t="n">
-        <v>0.2721</v>
+        <v>0.369</v>
       </c>
       <c r="J336" t="n">
-        <v>4.8978</v>
+        <v>6.642</v>
       </c>
     </row>
     <row r="337">
@@ -15875,10 +15875,10 @@
         <v>1.35</v>
       </c>
       <c r="I337" t="n">
-        <v>0.6871</v>
+        <v>0.8668</v>
       </c>
       <c r="J337" t="n">
-        <v>12.3678</v>
+        <v>15.6024</v>
       </c>
     </row>
     <row r="338">
@@ -15915,10 +15915,10 @@
         <v>0.66</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.5051</v>
+        <v>-0.3395</v>
       </c>
       <c r="J338" t="n">
-        <v>-9.091799999999999</v>
+        <v>-6.111</v>
       </c>
     </row>
     <row r="339">
@@ -15955,10 +15955,10 @@
         <v>0.59</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.6041</v>
+        <v>-0.405</v>
       </c>
       <c r="J339" t="n">
-        <v>-10.8738</v>
+        <v>-7.29</v>
       </c>
     </row>
     <row r="340">
@@ -15995,10 +15995,10 @@
         <v>0.57</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.631</v>
+        <v>-0.4237</v>
       </c>
       <c r="J340" t="n">
-        <v>-11.358</v>
+        <v>-7.6266</v>
       </c>
     </row>
     <row r="341">
@@ -16035,10 +16035,10 @@
         <v>0.53</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6836</v>
+        <v>-0.4611</v>
       </c>
       <c r="J341" t="n">
-        <v>-12.3048</v>
+        <v>-8.299799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7485/event_7485_evp_summary.xlsx
+++ b/database/event/7485/event_7485_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.7875</v>
+        <v>8.7776</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5522</v>
+        <v>3.5482</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3291</v>
+        <v>3.3715</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7875</v>
+        <v>8.7776</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2854</v>
+        <v>4.2839</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5021</v>
+        <v>4.4937</v>
       </c>
       <c r="H2" t="n">
-        <v>9.6128</v>
+        <v>9.24</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9982</v>
+        <v>4.9895</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5021</v>
+        <v>4.4937</v>
       </c>
       <c r="K2" t="n">
         <v>99</v>
@@ -529,7 +529,7 @@
         <v>148</v>
       </c>
       <c r="M2" t="n">
-        <v>9.500299999999999</v>
+        <v>9.4832</v>
       </c>
       <c r="N2" t="n">
         <v>247</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.3361</v>
+        <v>7.4742</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9655</v>
+        <v>3.0213</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6739</v>
+        <v>2.7782</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3361</v>
+        <v>7.4742</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3113</v>
+        <v>3.2613</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0248</v>
+        <v>4.2129</v>
       </c>
       <c r="H3" t="n">
-        <v>6.1805</v>
+        <v>5.866</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2136</v>
+        <v>3.1676</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0248</v>
+        <v>4.2129</v>
       </c>
       <c r="K3" t="n">
         <v>99</v>
@@ -575,7 +575,7 @@
         <v>148</v>
       </c>
       <c r="M3" t="n">
-        <v>7.2384</v>
+        <v>7.380500000000001</v>
       </c>
       <c r="N3" t="n">
         <v>247</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.1017</v>
+        <v>7.2036</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8708</v>
+        <v>2.9119</v>
       </c>
       <c r="D4" t="n">
-        <v>2.568</v>
+        <v>2.655</v>
       </c>
       <c r="E4" t="n">
-        <v>7.1017</v>
+        <v>7.2036</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0748</v>
+        <v>3.0336</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0269</v>
+        <v>4.17</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3472</v>
+        <v>5.1149</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7803</v>
+        <v>2.762</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0269</v>
+        <v>4.17</v>
       </c>
       <c r="K4" t="n">
         <v>99</v>
@@ -621,7 +621,7 @@
         <v>148</v>
       </c>
       <c r="M4" t="n">
-        <v>6.8072</v>
+        <v>6.932</v>
       </c>
       <c r="N4" t="n">
         <v>247</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.7215</v>
+        <v>6.7704</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7171</v>
+        <v>2.7368</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3964</v>
+        <v>2.4578</v>
       </c>
       <c r="E5" t="n">
-        <v>6.7215</v>
+        <v>6.7704</v>
       </c>
       <c r="F5" t="n">
-        <v>2.83</v>
+        <v>2.7703</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8915</v>
+        <v>4.0001</v>
       </c>
       <c r="H5" t="n">
-        <v>4.485</v>
+        <v>4.2462</v>
       </c>
       <c r="I5" t="n">
-        <v>2.332</v>
+        <v>2.2929</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8915</v>
+        <v>4.0001</v>
       </c>
       <c r="K5" t="n">
         <v>109</v>
@@ -667,7 +667,7 @@
         <v>120</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2235</v>
+        <v>6.292999999999999</v>
       </c>
       <c r="N5" t="n">
         <v>229</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.1859</v>
+        <v>5.0634</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0963</v>
+        <v>2.0468</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7032</v>
+        <v>1.6808</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1859</v>
+        <v>5.0634</v>
       </c>
       <c r="F6" t="n">
-        <v>3.189</v>
+        <v>2.8721</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9969</v>
+        <v>2.1913</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6428</v>
+        <v>3.5612</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7926</v>
+        <v>3.653</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9969</v>
+        <v>2.1913</v>
       </c>
       <c r="K6" t="n">
         <v>122</v>
@@ -713,7 +713,7 @@
         <v>127</v>
       </c>
       <c r="M6" t="n">
-        <v>5.7895</v>
+        <v>5.8443</v>
       </c>
       <c r="N6" t="n">
         <v>249</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1688</v>
+        <v>4.376</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6852</v>
+        <v>1.7689</v>
       </c>
       <c r="D7" t="n">
-        <v>1.244</v>
+        <v>1.3678</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1688</v>
+        <v>4.376</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2264</v>
+        <v>1.1728</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9425</v>
+        <v>3.2033</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2264</v>
+        <v>1.1728</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2768</v>
+        <v>1.203</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9425</v>
+        <v>3.2033</v>
       </c>
       <c r="K7" t="n">
         <v>122</v>
@@ -759,7 +759,7 @@
         <v>127</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2193</v>
+        <v>4.4063</v>
       </c>
       <c r="N7" t="n">
         <v>249</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6421</v>
+        <v>3.6786</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4723</v>
+        <v>1.487</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0062</v>
+        <v>1.0504</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6421</v>
+        <v>3.6786</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2753</v>
+        <v>3.2262</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3668</v>
+        <v>0.4524</v>
       </c>
       <c r="H8" t="n">
-        <v>6.0538</v>
+        <v>5.7503</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1477</v>
+        <v>3.1051</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3668</v>
+        <v>0.4524</v>
       </c>
       <c r="K8" t="n">
         <v>109</v>
@@ -805,7 +805,7 @@
         <v>120</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5145</v>
+        <v>3.5575</v>
       </c>
       <c r="N8" t="n">
         <v>229</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4457</v>
+        <v>3.4379</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3929</v>
+        <v>1.3897</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9175</v>
+        <v>0.9408</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4457</v>
+        <v>3.4379</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7042</v>
+        <v>2.043</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7415</v>
+        <v>1.3949</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7042</v>
+        <v>2.043</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7042</v>
+        <v>1.1032</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7415</v>
+        <v>1.3949</v>
       </c>
       <c r="K9" t="n">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4457</v>
+        <v>2.4981</v>
       </c>
       <c r="N9" t="n">
-        <v>125</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3868</v>
+        <v>3.3495</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3691</v>
+        <v>1.354</v>
       </c>
       <c r="D10" t="n">
-        <v>0.891</v>
+        <v>0.9006</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3868</v>
+        <v>3.3495</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0402</v>
+        <v>2.1573</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3466</v>
+        <v>1.1922</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0402</v>
+        <v>2.1573</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0608</v>
+        <v>2.2129</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3466</v>
+        <v>1.1922</v>
       </c>
       <c r="K10" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="L10" t="n">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4074</v>
+        <v>3.4051</v>
       </c>
       <c r="N10" t="n">
-        <v>229</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2197</v>
+        <v>3.2621</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3015</v>
+        <v>1.3187</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8155</v>
+        <v>0.8608</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2197</v>
+        <v>3.2621</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1988</v>
+        <v>2.4614</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0209</v>
+        <v>0.8007</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1988</v>
+        <v>2.6623</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2892</v>
+        <v>2.6623</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0209</v>
+        <v>0.8007</v>
       </c>
       <c r="K11" t="n">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="L11" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3101</v>
+        <v>3.463</v>
       </c>
       <c r="N11" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0545</v>
+        <v>2.973</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2347</v>
+        <v>1.2018</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7409</v>
+        <v>0.7292</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0545</v>
+        <v>2.973</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4908</v>
+        <v>2.4097</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5637</v>
+        <v>0.5633</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2897</v>
+        <v>3.0563</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7105</v>
+        <v>1.6504</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5637</v>
+        <v>0.5633</v>
       </c>
       <c r="K12" t="n">
         <v>109</v>
@@ -989,7 +989,7 @@
         <v>120</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2742</v>
+        <v>2.2137</v>
       </c>
       <c r="N12" t="n">
         <v>229</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6167</v>
+        <v>2.5541</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0578</v>
+        <v>1.0325</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5433</v>
+        <v>0.5385</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6167</v>
+        <v>2.5541</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4845</v>
+        <v>2.0833</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1322</v>
+        <v>0.4708</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4845</v>
+        <v>2.0833</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4845</v>
+        <v>2.137</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1322</v>
+        <v>0.4708</v>
       </c>
       <c r="K13" t="n">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="L13" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6167</v>
+        <v>2.6078</v>
       </c>
       <c r="N13" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5328</v>
+        <v>2.4972</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0238</v>
+        <v>1.0095</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5054</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5328</v>
+        <v>2.4972</v>
       </c>
       <c r="F14" t="n">
-        <v>2.132</v>
+        <v>2.3557</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4008</v>
+        <v>0.1415</v>
       </c>
       <c r="H14" t="n">
-        <v>2.132</v>
+        <v>2.431</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2197</v>
+        <v>2.431</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4008</v>
+        <v>0.1415</v>
       </c>
       <c r="K14" t="n">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="L14" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6205</v>
+        <v>2.5725</v>
       </c>
       <c r="N14" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2345</v>
+        <v>2.2606</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9033</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3708</v>
+        <v>0.4049</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2345</v>
+        <v>2.2606</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7287</v>
+        <v>1.6835</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5058</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7287</v>
+        <v>1.6835</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7998</v>
+        <v>1.7269</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5058</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="K15" t="n">
         <v>116</v>
@@ -1127,7 +1127,7 @@
         <v>59</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3056</v>
+        <v>2.304</v>
       </c>
       <c r="N15" t="n">
         <v>175</v>
@@ -1136,185 +1136,185 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2185</v>
+        <v>2.1549</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8968</v>
+        <v>0.8711</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3635</v>
+        <v>0.3568</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2185</v>
+        <v>2.1549</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6127</v>
+        <v>1.1687</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3942</v>
+        <v>0.9862</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7192</v>
+        <v>1.1687</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9338</v>
+        <v>1.1988</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3942</v>
+        <v>0.9862</v>
       </c>
       <c r="K16" t="n">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="L16" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5396</v>
+        <v>2.185</v>
       </c>
       <c r="N16" t="n">
-        <v>247</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2003</v>
+        <v>2.1321</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8894</v>
+        <v>0.8619</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3553</v>
+        <v>0.3464</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2003</v>
+        <v>2.1321</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6503</v>
+        <v>2.5419</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.45</v>
+        <v>-0.4098</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6503</v>
+        <v>3.4925</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7593</v>
+        <v>1.8859</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.45</v>
+        <v>-0.4098</v>
       </c>
       <c r="K17" t="n">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="L17" t="n">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3093</v>
+        <v>1.4761</v>
       </c>
       <c r="N17" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0754</v>
+        <v>2.0583</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8389</v>
+        <v>0.832</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2989</v>
+        <v>0.3128</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0754</v>
+        <v>2.0583</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2282</v>
+        <v>0.4348</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8472</v>
+        <v>1.6235</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2282</v>
+        <v>0.4348</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2787</v>
+        <v>0.4348</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8472</v>
+        <v>1.6235</v>
       </c>
       <c r="K18" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="L18" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1259</v>
+        <v>2.0583</v>
       </c>
       <c r="N18" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9615</v>
+        <v>2.0525</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7929</v>
+        <v>0.8297</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2475</v>
+        <v>0.3101</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9615</v>
+        <v>2.0525</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4613</v>
+        <v>2.4242</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5002</v>
+        <v>-0.3717</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4613</v>
+        <v>2.5809</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4613</v>
+        <v>2.6474</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5002</v>
+        <v>-0.3717</v>
       </c>
       <c r="K19" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="L19" t="n">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9615</v>
+        <v>2.2757</v>
       </c>
       <c r="N19" t="n">
-        <v>190</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4393</v>
+        <v>1.4345</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5818</v>
+        <v>0.5799</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0118</v>
+        <v>0.0288</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4393</v>
+        <v>1.4345</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8998</v>
+        <v>0.8283</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5395</v>
+        <v>0.6062</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8998</v>
+        <v>0.8283</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8998</v>
+        <v>0.8283</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5395</v>
+        <v>0.6062</v>
       </c>
       <c r="K20" t="n">
         <v>106</v>
@@ -1357,7 +1357,7 @@
         <v>84</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4393</v>
+        <v>1.4345</v>
       </c>
       <c r="N20" t="n">
         <v>190</v>
@@ -1366,231 +1366,231 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3516</v>
+        <v>1.2837</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5464</v>
+        <v>0.5189</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0278</v>
+        <v>-0.0398</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3516</v>
+        <v>1.2837</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3516</v>
+        <v>-0.1471</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1.4308</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3516</v>
+        <v>-0.1471</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3516</v>
+        <v>-0.1509</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.4308</v>
       </c>
       <c r="K21" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3516</v>
+        <v>1.2799</v>
       </c>
       <c r="N21" t="n">
-        <v>115</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1793</v>
+        <v>1.241</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4767</v>
+        <v>0.5017</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1056</v>
+        <v>-0.0593</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1793</v>
+        <v>1.241</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2186</v>
+        <v>1.241</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0393</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2186</v>
+        <v>1.241</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6336000000000001</v>
+        <v>1.241</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0393</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="L22" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5943000000000001</v>
+        <v>1.241</v>
       </c>
       <c r="N22" t="n">
-        <v>229</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1136</v>
+        <v>1.1806</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4502</v>
+        <v>0.4772</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1353</v>
+        <v>-0.0868</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1136</v>
+        <v>1.1806</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7839</v>
+        <v>1.2198</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6703</v>
+        <v>-0.0392</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7839</v>
+        <v>1.2198</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7839</v>
+        <v>0.6587</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6703</v>
+        <v>-0.0392</v>
       </c>
       <c r="K23" t="n">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="L23" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1136</v>
+        <v>0.6194999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>125</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ewjerkz</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0802</v>
+        <v>1.0564</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4367</v>
+        <v>0.427</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1504</v>
+        <v>-0.1433</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0802</v>
+        <v>1.0564</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0802</v>
+        <v>1.7509</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.6945</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0802</v>
+        <v>1.7509</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0802</v>
+        <v>1.7509</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.6945</v>
       </c>
       <c r="K24" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0802</v>
+        <v>1.0564</v>
       </c>
       <c r="N24" t="n">
-        <v>88</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>ewjerkz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0754</v>
+        <v>0.9686</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4347</v>
+        <v>0.3915</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1525</v>
+        <v>-0.1833</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0754</v>
+        <v>0.9686</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1849</v>
+        <v>0.9686</v>
       </c>
       <c r="G25" t="n">
-        <v>1.2603</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1849</v>
+        <v>0.9686</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1925</v>
+        <v>0.9686</v>
       </c>
       <c r="J25" t="n">
-        <v>1.2603</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="L25" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0678</v>
+        <v>0.9686</v>
       </c>
       <c r="N25" t="n">
-        <v>249</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8794</v>
+        <v>0.82</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3555</v>
+        <v>0.3315</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.241</v>
+        <v>-0.2509</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8794</v>
+        <v>0.82</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1386</v>
+        <v>1.1028</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2592</v>
+        <v>-0.2828</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1386</v>
+        <v>1.1028</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1386</v>
+        <v>1.1028</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2592</v>
+        <v>-0.2828</v>
       </c>
       <c r="K26" t="n">
         <v>81</v>
@@ -1633,7 +1633,7 @@
         <v>44</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8794000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>125</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8739</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3533</v>
+        <v>0.3152</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2435</v>
+        <v>-0.2693</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8739</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8739</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8739</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8739</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8739</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>115</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7726</v>
+        <v>0.7231</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3123</v>
+        <v>0.2923</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2892</v>
+        <v>-0.295</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7726</v>
+        <v>0.7231</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5093</v>
+        <v>0.4477</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2633</v>
+        <v>0.2754</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5093</v>
+        <v>0.4477</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5093</v>
+        <v>0.4477</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2633</v>
+        <v>0.2754</v>
       </c>
       <c r="K28" t="n">
         <v>106</v>
@@ -1725,7 +1725,7 @@
         <v>84</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7726</v>
+        <v>0.7231</v>
       </c>
       <c r="N28" t="n">
         <v>190</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7247</v>
+        <v>0.6848</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2929</v>
+        <v>0.2768</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3108</v>
+        <v>-0.3125</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7247</v>
+        <v>0.6848</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9647</v>
+        <v>0.9516</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.24</v>
+        <v>-0.2668</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9647</v>
+        <v>0.9516</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9647</v>
+        <v>0.9516</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.24</v>
+        <v>-0.2668</v>
       </c>
       <c r="K29" t="n">
         <v>81</v>
@@ -1771,7 +1771,7 @@
         <v>44</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7247</v>
+        <v>0.6848000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>125</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3534</v>
+        <v>0.3301</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1429</v>
+        <v>0.1334</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4785</v>
+        <v>-0.4739</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3534</v>
+        <v>0.3301</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8109</v>
+        <v>0.7302</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4575</v>
+        <v>-0.4001</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8109</v>
+        <v>0.7302</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8109</v>
+        <v>0.7302</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4575</v>
+        <v>-0.4001</v>
       </c>
       <c r="K30" t="n">
         <v>106</v>
@@ -1817,7 +1817,7 @@
         <v>84</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3533999999999999</v>
+        <v>0.3300999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>190</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.193</v>
+        <v>0.1327</v>
       </c>
       <c r="C31" t="n">
-        <v>0.078</v>
+        <v>0.0536</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.5638</v>
       </c>
       <c r="E31" t="n">
-        <v>0.193</v>
+        <v>0.1327</v>
       </c>
       <c r="F31" t="n">
-        <v>1.6478</v>
+        <v>1.6239</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.4548</v>
+        <v>-1.4912</v>
       </c>
       <c r="H31" t="n">
-        <v>1.6478</v>
+        <v>1.6239</v>
       </c>
       <c r="I31" t="n">
-        <v>1.7156</v>
+        <v>1.6657</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.4548</v>
+        <v>-1.4912</v>
       </c>
       <c r="K31" t="n">
         <v>122</v>
@@ -1863,7 +1863,7 @@
         <v>127</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2607999999999999</v>
+        <v>0.1744999999999999</v>
       </c>
       <c r="N31" t="n">
         <v>249</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.1249</v>
+        <v>0.1213</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0505</v>
+        <v>0.049</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5816</v>
+        <v>-0.569</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1249</v>
+        <v>0.1213</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1249</v>
+        <v>0.1213</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1249</v>
+        <v>0.1213</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1249</v>
+        <v>0.1213</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1249</v>
+        <v>0.1213</v>
       </c>
       <c r="N32" t="n">
         <v>57</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5134</v>
+        <v>-0.5587</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2075</v>
+        <v>-0.2258</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8698</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5134</v>
+        <v>-0.5587</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5134</v>
+        <v>-0.5587</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5134</v>
+        <v>-0.5587</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5134</v>
+        <v>-0.5587</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5134</v>
+        <v>-0.5587</v>
       </c>
       <c r="N33" t="n">
         <v>88</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6204</v>
+        <v>-0.6761</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2508</v>
+        <v>-0.2733</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9181</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6204</v>
+        <v>-0.6761</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6204</v>
+        <v>-0.6761</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6204</v>
+        <v>-0.6761</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6204</v>
+        <v>-0.6761</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6204</v>
+        <v>-0.6761</v>
       </c>
       <c r="N34" t="n">
         <v>115</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7357</v>
+        <v>-0.7751</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2974</v>
+        <v>-0.3133</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9701</v>
+        <v>-0.977</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7357</v>
+        <v>-0.7751</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7357</v>
+        <v>-0.7751</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7357</v>
+        <v>-0.7751</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7357</v>
+        <v>-0.7751</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7357</v>
+        <v>-0.7751</v>
       </c>
       <c r="N35" t="n">
         <v>88</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9649</v>
+        <v>-0.9826</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.39</v>
+        <v>-0.3972</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0736</v>
+        <v>-1.0715</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9649</v>
+        <v>-0.9826</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9649</v>
+        <v>-0.4782</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.5044</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9649</v>
+        <v>-0.4782</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9649</v>
+        <v>-0.4782</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.5044</v>
       </c>
       <c r="K36" t="n">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9649</v>
+        <v>-0.9825999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>58</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.988</v>
+        <v>-1</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3994</v>
+        <v>-0.4042</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.084</v>
+        <v>-1.0794</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.988</v>
+        <v>-1</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.4849</v>
+        <v>-1</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.5031</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.4849</v>
+        <v>-1</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4849</v>
+        <v>-1</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5031</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="L37" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.988</v>
+        <v>-1</v>
       </c>
       <c r="N37" t="n">
-        <v>190</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1994</v>
+        <v>-1.261</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4848</v>
+        <v>-0.5097</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1795</v>
+        <v>-1.1982</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1994</v>
+        <v>-1.261</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.1994</v>
+        <v>-1.261</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.1994</v>
+        <v>-1.261</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.1994</v>
+        <v>-1.261</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1994</v>
+        <v>-1.261</v>
       </c>
       <c r="N38" t="n">
         <v>88</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2743</v>
+        <v>-1.3316</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5151</v>
+        <v>-0.5383</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2133</v>
+        <v>-1.2304</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2743</v>
+        <v>-1.3316</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2743</v>
+        <v>-1.3316</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2743</v>
+        <v>-1.3316</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2743</v>
+        <v>-1.3316</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2743</v>
+        <v>-1.3316</v>
       </c>
       <c r="N39" t="n">
         <v>88</v>
@@ -2250,7 +2250,7 @@
         <v>-0.8085</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5409</v>
+        <v>-1.5346</v>
       </c>
       <c r="E40" t="n">
         <v>-2</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4763</v>
+        <v>-2.4146</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.001</v>
+        <v>-0.9761</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7559</v>
+        <v>-1.7234</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4763</v>
+        <v>-2.4146</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4763</v>
+        <v>-1.4146</v>
       </c>
       <c r="G41" t="n">
         <v>-1</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4763</v>
+        <v>-1.4146</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.537</v>
+        <v>-1.4511</v>
       </c>
       <c r="J41" t="n">
         <v>-1</v>
@@ -2323,7 +2323,7 @@
         <v>59</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.537</v>
+        <v>-2.4511</v>
       </c>
       <c r="N41" t="n">
         <v>175</v>
@@ -2336,31 +2336,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.7474</v>
+        <v>-2.4625</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.1106</v>
+        <v>-0.9954</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.8783</v>
+        <v>-1.7452</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.7474</v>
+        <v>-2.4625</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.3969</v>
+        <v>-1.1698</v>
       </c>
       <c r="G42" t="n">
-        <v>-1.3505</v>
+        <v>-1.2927</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.3969</v>
+        <v>-1.1698</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.6317</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.3505</v>
+        <v>-1.2927</v>
       </c>
       <c r="K42" t="n">
         <v>99</v>
@@ -2369,7 +2369,7 @@
         <v>148</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.0768</v>
+        <v>-1.9244</v>
       </c>
       <c r="N42" t="n">
         <v>247</v>
@@ -2475,10 +2475,10 @@
         <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1054</v>
+        <v>1.09</v>
       </c>
       <c r="J2" t="n">
-        <v>24.3188</v>
+        <v>23.98</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>1.36</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.8629</v>
       </c>
       <c r="J3" t="n">
-        <v>20.1476</v>
+        <v>18.9838</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>1.32</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.7847</v>
       </c>
       <c r="J4" t="n">
-        <v>18.1962</v>
+        <v>17.2634</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>1.25</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6691</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>14.7202</v>
+        <v>14.1834</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6338</v>
+        <v>-0.5865</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.9436</v>
+        <v>-12.903</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.13</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3537</v>
+        <v>0.3444</v>
       </c>
       <c r="J7" t="n">
-        <v>7.7814</v>
+        <v>7.5768</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2017</v>
+        <v>0.1992</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4374</v>
+        <v>4.3824</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1427</v>
+        <v>-0.159</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.1394</v>
+        <v>-3.498</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>0.72</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3006</v>
+        <v>-0.3161</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.6132</v>
+        <v>-6.9542</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>0.54</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4691</v>
+        <v>-0.4775</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.3202</v>
+        <v>-10.505</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.57</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2399</v>
+        <v>1.2796</v>
       </c>
       <c r="J12" t="n">
-        <v>27.2778</v>
+        <v>28.1512</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>1.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0144</v>
+        <v>0.9591</v>
       </c>
       <c r="J13" t="n">
-        <v>22.3168</v>
+        <v>21.1002</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>1.31</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8269</v>
+        <v>0.7803</v>
       </c>
       <c r="J14" t="n">
-        <v>18.1918</v>
+        <v>17.1666</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.274</v>
+        <v>-0.2617</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.028</v>
+        <v>-5.7574</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.61</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1312</v>
+        <v>-1.0251</v>
       </c>
       <c r="J16" t="n">
-        <v>-24.8864</v>
+        <v>-22.5522</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8817</v>
+        <v>0.8309</v>
       </c>
       <c r="J17" t="n">
-        <v>19.3974</v>
+        <v>18.2798</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.29</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6219</v>
+        <v>0.5979</v>
       </c>
       <c r="J18" t="n">
-        <v>13.6818</v>
+        <v>13.1538</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>0.76</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2721</v>
+        <v>-0.2864</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.9862</v>
+        <v>-6.3008</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>0.68</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3489</v>
+        <v>-0.3611</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.6758</v>
+        <v>-7.9442</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.46</v>
+        <v>-0.4675</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.12</v>
+        <v>-10.285</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2689</v>
+        <v>0.2582</v>
       </c>
       <c r="J22" t="n">
-        <v>4.5713</v>
+        <v>4.3894</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>0.99</v>
       </c>
       <c r="I23" t="n">
-        <v>0.031</v>
+        <v>0.0106</v>
       </c>
       <c r="J23" t="n">
-        <v>0.527</v>
+        <v>0.1802</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>0.65</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3504</v>
+        <v>-0.3673</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.9568</v>
+        <v>-6.2441</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>0.53</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4626</v>
+        <v>-0.4739</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.8642</v>
+        <v>-8.0563</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.48</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.509</v>
+        <v>-0.5175</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.653</v>
+        <v>-8.797499999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.86</v>
       </c>
       <c r="I27" t="n">
-        <v>0.95</v>
+        <v>0.9353</v>
       </c>
       <c r="J27" t="n">
-        <v>16.15</v>
+        <v>15.9001</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>1.52</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6118</v>
+        <v>0.6199</v>
       </c>
       <c r="J28" t="n">
-        <v>10.4006</v>
+        <v>10.5383</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>1.46</v>
       </c>
       <c r="I29" t="n">
-        <v>0.55</v>
+        <v>0.5615</v>
       </c>
       <c r="J29" t="n">
-        <v>9.35</v>
+        <v>9.545500000000001</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>1.13</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1704</v>
+        <v>0.1941</v>
       </c>
       <c r="J30" t="n">
-        <v>2.8968</v>
+        <v>3.2997</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>1.05</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0528</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8976</v>
+        <v>1.2733</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.74</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4359</v>
+        <v>1.5508</v>
       </c>
       <c r="J32" t="n">
-        <v>27.2821</v>
+        <v>29.4652</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.44</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0599</v>
+        <v>1.0222</v>
       </c>
       <c r="J33" t="n">
-        <v>20.1381</v>
+        <v>19.4218</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1797</v>
+        <v>0.1966</v>
       </c>
       <c r="J34" t="n">
-        <v>3.4143</v>
+        <v>3.7354</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>1.06</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1797</v>
+        <v>0.1966</v>
       </c>
       <c r="J35" t="n">
-        <v>3.4143</v>
+        <v>3.7354</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.79</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.705</v>
+        <v>-0.6512</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.395</v>
+        <v>-12.3728</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.38</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8172</v>
+        <v>0.7678</v>
       </c>
       <c r="J37" t="n">
-        <v>15.5268</v>
+        <v>14.5882</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>0.78</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2439</v>
+        <v>-0.2604</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.6341</v>
+        <v>-4.9476</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>0.76</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2635</v>
+        <v>-0.2796</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.0065</v>
+        <v>-5.3124</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.75</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2732</v>
+        <v>-0.2891</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.1908</v>
+        <v>-5.4929</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.72</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3022</v>
+        <v>-0.3174</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.7418</v>
+        <v>-6.0306</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.71</v>
       </c>
       <c r="I42" t="n">
-        <v>1.084</v>
+        <v>1.1953</v>
       </c>
       <c r="J42" t="n">
-        <v>19.512</v>
+        <v>21.5154</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.61</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9654</v>
+        <v>1.069</v>
       </c>
       <c r="J43" t="n">
-        <v>17.3772</v>
+        <v>19.242</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.42</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7351</v>
+        <v>0.82</v>
       </c>
       <c r="J44" t="n">
-        <v>13.2318</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>1.13</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3379</v>
+        <v>0.3572</v>
       </c>
       <c r="J45" t="n">
-        <v>6.0822</v>
+        <v>6.4296</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>1.04</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0767</v>
+        <v>0.108</v>
       </c>
       <c r="J46" t="n">
-        <v>1.3806</v>
+        <v>1.944</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.24</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5596</v>
+        <v>0.5974</v>
       </c>
       <c r="J47" t="n">
-        <v>10.0728</v>
+        <v>10.7532</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>0.68</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.3121</v>
+        <v>-0.3326</v>
       </c>
       <c r="J48" t="n">
-        <v>-5.6178</v>
+        <v>-5.9868</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.68</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3121</v>
+        <v>-0.3326</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.6178</v>
+        <v>-5.9868</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.45</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5339</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.444599999999999</v>
+        <v>-9.610200000000001</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.3</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6657</v>
+        <v>-0.6641</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.9826</v>
+        <v>-11.9538</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.29</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6167</v>
+        <v>0.6784</v>
       </c>
       <c r="J52" t="n">
-        <v>13.5674</v>
+        <v>14.9248</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>1.13</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3785</v>
+        <v>0.4024</v>
       </c>
       <c r="J53" t="n">
-        <v>8.327</v>
+        <v>8.8528</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>1.08</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2713</v>
+        <v>0.2748</v>
       </c>
       <c r="J54" t="n">
-        <v>5.9686</v>
+        <v>6.0456</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0162</v>
+        <v>-0.0111</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.3564</v>
+        <v>-0.2442</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.87</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4551</v>
+        <v>-0.4343</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.0122</v>
+        <v>-9.554600000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.05</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1927</v>
+        <v>0.1868</v>
       </c>
       <c r="J57" t="n">
-        <v>4.2394</v>
+        <v>4.1096</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>0.9</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1163</v>
+        <v>-0.1332</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.5586</v>
+        <v>-2.9304</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>0.88</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1384</v>
+        <v>-0.1557</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.0448</v>
+        <v>-3.4254</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>0.73</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2861</v>
+        <v>-0.303</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.2942</v>
+        <v>-6.666</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.59</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4182</v>
+        <v>-0.4301</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.2004</v>
+        <v>-9.462199999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.31</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4186</v>
+        <v>0.4647</v>
       </c>
       <c r="J62" t="n">
-        <v>10.0464</v>
+        <v>11.1528</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2726</v>
+        <v>0.2807</v>
       </c>
       <c r="J63" t="n">
-        <v>6.5424</v>
+        <v>6.7368</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>0.97</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0527</v>
+        <v>-0.0602</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.2648</v>
+        <v>-1.4448</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.091</v>
+        <v>-0.1013</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.184</v>
+        <v>-2.4312</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.76</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2817</v>
+        <v>-0.2939</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.7608</v>
+        <v>-7.0536</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.34</v>
       </c>
       <c r="I67" t="n">
-        <v>0.406</v>
+        <v>0.458</v>
       </c>
       <c r="J67" t="n">
-        <v>9.744</v>
+        <v>10.992</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.31</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3853</v>
+        <v>0.43</v>
       </c>
       <c r="J68" t="n">
-        <v>9.247199999999999</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>1.12</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1866</v>
+        <v>0.2031</v>
       </c>
       <c r="J69" t="n">
-        <v>4.4784</v>
+        <v>4.8744</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>0.99</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0335</v>
+        <v>-0.0352</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.804</v>
+        <v>-0.8448</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.92</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1262</v>
+        <v>-0.1349</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.0288</v>
+        <v>-3.2376</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>1.64</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0621</v>
+        <v>1.161</v>
       </c>
       <c r="J72" t="n">
-        <v>23.3662</v>
+        <v>25.542</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>1.25</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5451</v>
+        <v>0.6027</v>
       </c>
       <c r="J73" t="n">
-        <v>11.9922</v>
+        <v>13.2594</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4003</v>
+        <v>0.4369</v>
       </c>
       <c r="J74" t="n">
-        <v>8.8066</v>
+        <v>9.611800000000001</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0343</v>
+        <v>-0.0236</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.7546</v>
+        <v>-0.5192</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-0.878</v>
       </c>
       <c r="J76" t="n">
-        <v>-21.1244</v>
+        <v>-19.316</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>1.26</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4666</v>
+        <v>0.5152</v>
       </c>
       <c r="J77" t="n">
-        <v>10.2652</v>
+        <v>11.3344</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>1.02</v>
       </c>
       <c r="I78" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0776</v>
       </c>
       <c r="J78" t="n">
-        <v>1.584</v>
+        <v>1.7072</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0046</v>
+        <v>0.0033</v>
       </c>
       <c r="J79" t="n">
-        <v>0.1012</v>
+        <v>0.0726</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1525</v>
+        <v>-0.1665</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.355</v>
+        <v>-3.663</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.68</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3515</v>
+        <v>-0.3631</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.733</v>
+        <v>-7.9882</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.75</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1913</v>
+        <v>1.2985</v>
       </c>
       <c r="J82" t="n">
-        <v>26.2086</v>
+        <v>28.567</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>0.555</v>
+        <v>0.6148</v>
       </c>
       <c r="J83" t="n">
-        <v>12.21</v>
+        <v>13.5256</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>1.23</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5129</v>
+        <v>0.5679</v>
       </c>
       <c r="J84" t="n">
-        <v>11.2838</v>
+        <v>12.4938</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>0.83</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5888</v>
+        <v>-0.5498</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.9536</v>
+        <v>-12.0956</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.744</v>
+        <v>-0.6878</v>
       </c>
       <c r="J86" t="n">
-        <v>-16.368</v>
+        <v>-15.1316</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3651</v>
+        <v>0.3845</v>
       </c>
       <c r="J87" t="n">
-        <v>8.0322</v>
+        <v>8.459</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3267</v>
+        <v>0.3305</v>
       </c>
       <c r="J88" t="n">
-        <v>7.1874</v>
+        <v>7.271</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>0.9</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1329</v>
+        <v>-0.1459</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.9238</v>
+        <v>-3.2098</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1655</v>
+        <v>-0.1791</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.641</v>
+        <v>-3.9402</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.86</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1761</v>
+        <v>-0.1898</v>
       </c>
       <c r="J91" t="n">
-        <v>-3.8742</v>
+        <v>-4.1756</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.34</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5444</v>
+        <v>0.6049</v>
       </c>
       <c r="J92" t="n">
-        <v>11.4324</v>
+        <v>12.7029</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>1.18</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3761</v>
+        <v>0.4019</v>
       </c>
       <c r="J93" t="n">
-        <v>7.8981</v>
+        <v>8.4399</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0351</v>
+        <v>-0.042</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.7371</v>
+        <v>-0.882</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>0.86</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1761</v>
+        <v>-0.1898</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.6981</v>
+        <v>-3.9858</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>0.58</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4462</v>
+        <v>-0.4537</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.370200000000001</v>
+        <v>-9.527699999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.51</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8932</v>
+        <v>0.9819</v>
       </c>
       <c r="J97" t="n">
-        <v>18.7572</v>
+        <v>20.6199</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>1.14</v>
       </c>
       <c r="I98" t="n">
-        <v>0.385</v>
+        <v>0.4156</v>
       </c>
       <c r="J98" t="n">
-        <v>8.085000000000001</v>
+        <v>8.727600000000001</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>1.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2852</v>
+        <v>0.2915</v>
       </c>
       <c r="J99" t="n">
-        <v>5.9892</v>
+        <v>6.1215</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>1.04</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1312</v>
+        <v>0.1461</v>
       </c>
       <c r="J100" t="n">
-        <v>2.7552</v>
+        <v>3.0681</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.98</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1324</v>
+        <v>-0.1263</v>
       </c>
       <c r="J101" t="n">
-        <v>-2.7804</v>
+        <v>-2.6523</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.06</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1971</v>
+        <v>0.1958</v>
       </c>
       <c r="J102" t="n">
-        <v>4.5333</v>
+        <v>4.5034</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0639</v>
+        <v>-0.077</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.4697</v>
+        <v>-1.771</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>0.8</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2241</v>
+        <v>-0.2408</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.1543</v>
+        <v>-5.5384</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>0.8</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2241</v>
+        <v>-0.2408</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.1543</v>
+        <v>-5.5384</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.78</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2439</v>
+        <v>-0.2604</v>
       </c>
       <c r="J106" t="n">
-        <v>-5.6097</v>
+        <v>-5.9892</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.31</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6267</v>
+        <v>0.6933</v>
       </c>
       <c r="J107" t="n">
-        <v>14.4141</v>
+        <v>15.9459</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>1.21</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4865</v>
+        <v>0.5377</v>
       </c>
       <c r="J108" t="n">
-        <v>11.1895</v>
+        <v>12.3671</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>1.17</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4286</v>
+        <v>0.4722</v>
       </c>
       <c r="J109" t="n">
-        <v>9.857799999999999</v>
+        <v>10.8606</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1637</v>
+        <v>0.1774</v>
       </c>
       <c r="J110" t="n">
-        <v>3.7651</v>
+        <v>4.0802</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>1.03</v>
       </c>
       <c r="I111" t="n">
-        <v>0.096</v>
+        <v>0.1122</v>
       </c>
       <c r="J111" t="n">
-        <v>2.208</v>
+        <v>2.5806</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.74</v>
       </c>
       <c r="I112" t="n">
-        <v>0.623</v>
+        <v>0.72</v>
       </c>
       <c r="J112" t="n">
-        <v>10.591</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.68</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.6795</v>
       </c>
       <c r="J113" t="n">
-        <v>9.9994</v>
+        <v>11.5515</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>1.49</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4762</v>
+        <v>0.5481</v>
       </c>
       <c r="J114" t="n">
-        <v>8.0954</v>
+        <v>9.3177</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>1.39</v>
       </c>
       <c r="I115" t="n">
-        <v>0.416</v>
+        <v>0.4761</v>
       </c>
       <c r="J115" t="n">
-        <v>7.072</v>
+        <v>8.0937</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>1.02</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0047</v>
+        <v>0.0142</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.0799</v>
+        <v>0.2414</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.16</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3542</v>
+        <v>0.353</v>
       </c>
       <c r="J117" t="n">
-        <v>6.0214</v>
+        <v>6.001</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>0.92</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0767</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.3039</v>
+        <v>-1.6439</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.64</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3597</v>
+        <v>-0.3763</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.1149</v>
+        <v>-6.3971</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>0.55</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4439</v>
+        <v>-0.4563</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.5463</v>
+        <v>-7.7571</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.48</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.509</v>
+        <v>-0.5175</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.653</v>
+        <v>-8.797499999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.62</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8263</v>
+        <v>0.9173</v>
       </c>
       <c r="J122" t="n">
-        <v>19.0049</v>
+        <v>21.0979</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.16</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3588</v>
+        <v>0.3729</v>
       </c>
       <c r="J123" t="n">
-        <v>8.2524</v>
+        <v>8.576700000000001</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>0.86</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1731</v>
+        <v>-0.1875</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.9813</v>
+        <v>-4.3125</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>0.59</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4343</v>
+        <v>-0.4428</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.988899999999999</v>
+        <v>-10.1844</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.58</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4435</v>
+        <v>-0.4515</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.2005</v>
+        <v>-10.3845</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.65</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0534</v>
+        <v>1.1554</v>
       </c>
       <c r="J127" t="n">
-        <v>24.2282</v>
+        <v>26.5742</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.38</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7094</v>
+        <v>0.7863</v>
       </c>
       <c r="J128" t="n">
-        <v>16.3162</v>
+        <v>18.0849</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>1.33</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6431</v>
+        <v>0.7138</v>
       </c>
       <c r="J129" t="n">
-        <v>14.7913</v>
+        <v>16.4174</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>0.96</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.22</v>
+        <v>-0.2075</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.06</v>
+        <v>-4.7725</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.74</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8293</v>
+        <v>-0.7611</v>
       </c>
       <c r="J131" t="n">
-        <v>-19.0739</v>
+        <v>-17.5053</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.62</v>
       </c>
       <c r="I132" t="n">
-        <v>0.867</v>
+        <v>0.9555</v>
       </c>
       <c r="J132" t="n">
-        <v>16.473</v>
+        <v>18.1545</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>0.96</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0491</v>
+        <v>-0.0617</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.9329</v>
+        <v>-1.1723</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3292</v>
+        <v>-0.3439</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.2548</v>
+        <v>-6.5341</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>0.62</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3951</v>
+        <v>-0.4072</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.5069</v>
+        <v>-7.7368</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.44</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5599</v>
+        <v>-0.5631</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.6381</v>
+        <v>-10.6989</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>2.61</v>
       </c>
       <c r="I137" t="n">
-        <v>2.0761</v>
+        <v>2.2262</v>
       </c>
       <c r="J137" t="n">
-        <v>39.4459</v>
+        <v>42.2978</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.72</v>
       </c>
       <c r="I138" t="n">
-        <v>1.087</v>
+        <v>1.2</v>
       </c>
       <c r="J138" t="n">
-        <v>20.653</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1631</v>
+        <v>0.1925</v>
       </c>
       <c r="J139" t="n">
-        <v>3.0989</v>
+        <v>3.6575</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5375</v>
+        <v>-0.4923</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.2125</v>
+        <v>-9.3537</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.86</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5648</v>
+        <v>-0.5171</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.7312</v>
+        <v>-9.8249</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.01</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1176</v>
+        <v>0.1016</v>
       </c>
       <c r="J142" t="n">
-        <v>1.9992</v>
+        <v>1.7272</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>0.87</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.137</v>
+        <v>-0.1572</v>
       </c>
       <c r="J143" t="n">
-        <v>-2.329</v>
+        <v>-2.6724</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>0.77</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2399</v>
+        <v>-0.2594</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.0783</v>
+        <v>-4.4098</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.63</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3703</v>
+        <v>-0.3862</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.2951</v>
+        <v>-6.5654</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.51</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4823</v>
+        <v>-0.4923</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.1991</v>
+        <v>-8.3691</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>2.23</v>
       </c>
       <c r="I147" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J147" t="n">
-        <v>31.1746</v>
+        <v>32.9324</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.48</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0862</v>
+        <v>1.0497</v>
       </c>
       <c r="J148" t="n">
-        <v>18.4654</v>
+        <v>17.8449</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.21</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5545</v>
+        <v>0.5465</v>
       </c>
       <c r="J149" t="n">
-        <v>9.426500000000001</v>
+        <v>9.2905</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>1.08</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2088</v>
+        <v>0.2315</v>
       </c>
       <c r="J150" t="n">
-        <v>3.5496</v>
+        <v>3.9355</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.77</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7842</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.3314</v>
+        <v>-12.1754</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.17</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3873</v>
+        <v>0.385</v>
       </c>
       <c r="J152" t="n">
-        <v>9.295199999999999</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>0.96</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.062</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.488</v>
+        <v>-1.716</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>0.95</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0745</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="J154" t="n">
-        <v>-1.788</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0867</v>
+        <v>-0.0979</v>
       </c>
       <c r="J155" t="n">
-        <v>-2.0808</v>
+        <v>-2.3496</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>0.91</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1215</v>
+        <v>-0.1342</v>
       </c>
       <c r="J156" t="n">
-        <v>-2.916</v>
+        <v>-3.2208</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9275</v>
+        <v>0.8636</v>
       </c>
       <c r="J157" t="n">
-        <v>22.26</v>
+        <v>20.7264</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4068</v>
+        <v>0.4008</v>
       </c>
       <c r="J158" t="n">
-        <v>9.763199999999999</v>
+        <v>9.619199999999999</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4068</v>
+        <v>0.4008</v>
       </c>
       <c r="J159" t="n">
-        <v>9.763199999999999</v>
+        <v>9.619199999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>1.06</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2114</v>
+        <v>0.2185</v>
       </c>
       <c r="J160" t="n">
-        <v>5.0736</v>
+        <v>5.244</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>0.76</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7478</v>
+        <v>-0.695</v>
       </c>
       <c r="J161" t="n">
-        <v>-17.9472</v>
+        <v>-16.68</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.85</v>
       </c>
       <c r="I162" t="n">
-        <v>1.5201</v>
+        <v>1.514</v>
       </c>
       <c r="J162" t="n">
-        <v>25.8417</v>
+        <v>25.738</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>1.62</v>
       </c>
       <c r="I163" t="n">
-        <v>1.2504</v>
+        <v>1.2284</v>
       </c>
       <c r="J163" t="n">
-        <v>21.2568</v>
+        <v>20.8828</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>1.28</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7133</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="J164" t="n">
-        <v>12.1261</v>
+        <v>11.713</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>1.17</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4476</v>
+        <v>0.4519</v>
       </c>
       <c r="J165" t="n">
-        <v>7.6092</v>
+        <v>7.6823</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>1.01</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.0371</v>
+        <v>-0.0042</v>
       </c>
       <c r="J166" t="n">
-        <v>-0.6307</v>
+        <v>-0.07140000000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.5</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0525</v>
+        <v>0.9943</v>
       </c>
       <c r="J167" t="n">
-        <v>17.8925</v>
+        <v>16.9031</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>0.85</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1657</v>
+        <v>-0.1844</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.8169</v>
+        <v>-3.1348</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.64</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3669</v>
+        <v>-0.3819</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.2373</v>
+        <v>-6.4923</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.58</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4231</v>
+        <v>-0.4354</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.1927</v>
+        <v>-7.4018</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.42</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5704</v>
+        <v>-0.574</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.6968</v>
+        <v>-9.757999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.39</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.5829</v>
       </c>
       <c r="J172" t="n">
-        <v>13.1626</v>
+        <v>12.8238</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.03</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0738</v>
+        <v>0.0809</v>
       </c>
       <c r="J173" t="n">
-        <v>1.6236</v>
+        <v>1.7798</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>0.91</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1204</v>
+        <v>-0.1334</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.6488</v>
+        <v>-2.9348</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>0.87</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1641</v>
+        <v>-0.1781</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.6102</v>
+        <v>-3.9182</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3524</v>
+        <v>-0.3638</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.7528</v>
+        <v>-8.0036</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>1.67</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8292</v>
+        <v>0.8118</v>
       </c>
       <c r="J177" t="n">
-        <v>18.2424</v>
+        <v>17.8596</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>1.31</v>
       </c>
       <c r="I178" t="n">
-        <v>0.424</v>
+        <v>0.4343</v>
       </c>
       <c r="J178" t="n">
-        <v>9.327999999999999</v>
+        <v>9.554600000000001</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>1.02</v>
       </c>
       <c r="I179" t="n">
-        <v>0.034</v>
+        <v>0.0448</v>
       </c>
       <c r="J179" t="n">
-        <v>0.748</v>
+        <v>0.9856</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>0.9</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1473</v>
+        <v>-0.1571</v>
       </c>
       <c r="J180" t="n">
-        <v>-3.2406</v>
+        <v>-3.4562</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.7</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3486</v>
+        <v>-0.3574</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.6692</v>
+        <v>-7.8628</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.49</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1079</v>
+        <v>1.0721</v>
       </c>
       <c r="J182" t="n">
-        <v>19.9422</v>
+        <v>19.2978</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9992</v>
+        <v>0.9472</v>
       </c>
       <c r="J183" t="n">
-        <v>17.9856</v>
+        <v>17.0496</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.32</v>
       </c>
       <c r="I184" t="n">
-        <v>0.8164</v>
+        <v>0.7774</v>
       </c>
       <c r="J184" t="n">
-        <v>14.6952</v>
+        <v>13.9932</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>1.26</v>
       </c>
       <c r="I185" t="n">
-        <v>0.6843</v>
+        <v>0.66</v>
       </c>
       <c r="J185" t="n">
-        <v>12.3174</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>1.01</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.0174</v>
+        <v>0.0097</v>
       </c>
       <c r="J186" t="n">
-        <v>-0.3132</v>
+        <v>0.1746</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.08</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2713</v>
+        <v>0.261</v>
       </c>
       <c r="J187" t="n">
-        <v>4.8834</v>
+        <v>4.698</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2713</v>
+        <v>0.261</v>
       </c>
       <c r="J188" t="n">
-        <v>4.8834</v>
+        <v>4.698</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>0.73</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2836</v>
+        <v>-0.3011</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.1048</v>
+        <v>-5.4198</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.71</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3027</v>
+        <v>-0.3197</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.4486</v>
+        <v>-5.7546</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.46</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5356</v>
+        <v>-0.5412</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.6408</v>
+        <v>-9.7416</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.19</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5087</v>
+        <v>0.4818</v>
       </c>
       <c r="J192" t="n">
-        <v>9.156599999999999</v>
+        <v>8.6724</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>0.84</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1766</v>
+        <v>-0.1952</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.1788</v>
+        <v>-3.5136</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>0.77</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.244</v>
+        <v>-0.2626</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.392</v>
+        <v>-4.7268</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3203</v>
+        <v>-0.337</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.7654</v>
+        <v>-6.066</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>0.52</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4793</v>
+        <v>-0.4884</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.6274</v>
+        <v>-8.7912</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.94</v>
       </c>
       <c r="I197" t="n">
-        <v>1.6256</v>
+        <v>1.6243</v>
       </c>
       <c r="J197" t="n">
-        <v>29.2608</v>
+        <v>29.2374</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.53</v>
       </c>
       <c r="I198" t="n">
-        <v>1.1436</v>
+        <v>1.1135</v>
       </c>
       <c r="J198" t="n">
-        <v>20.5848</v>
+        <v>20.043</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>1.21</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5493</v>
+        <v>0.5429</v>
       </c>
       <c r="J199" t="n">
-        <v>9.8874</v>
+        <v>9.7722</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>1.14</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3712</v>
+        <v>0.3822</v>
       </c>
       <c r="J200" t="n">
-        <v>6.6816</v>
+        <v>6.8796</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>1.07</v>
       </c>
       <c r="I201" t="n">
-        <v>0.1734</v>
+        <v>0.1997</v>
       </c>
       <c r="J201" t="n">
-        <v>3.1212</v>
+        <v>3.5946</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>1.53</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6685</v>
+        <v>0.6649</v>
       </c>
       <c r="J202" t="n">
-        <v>14.707</v>
+        <v>14.6278</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>1.43</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5569</v>
+        <v>0.5609</v>
       </c>
       <c r="J203" t="n">
-        <v>12.2518</v>
+        <v>12.3398</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>1.2</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2866</v>
+        <v>0.3027</v>
       </c>
       <c r="J204" t="n">
-        <v>6.3052</v>
+        <v>6.6594</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>1.04</v>
       </c>
       <c r="I205" t="n">
-        <v>0.0665</v>
+        <v>0.0805</v>
       </c>
       <c r="J205" t="n">
-        <v>1.463</v>
+        <v>1.771</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.54</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4962</v>
+        <v>-0.499</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.9164</v>
+        <v>-10.978</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.21</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3587</v>
+        <v>0.3598</v>
       </c>
       <c r="J207" t="n">
-        <v>7.8914</v>
+        <v>7.9156</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.2</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3445</v>
+        <v>0.3464</v>
       </c>
       <c r="J208" t="n">
-        <v>7.579</v>
+        <v>7.6208</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>0.95</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0728</v>
+        <v>-0.0837</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.6016</v>
+        <v>-1.8414</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>0.82</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2148</v>
+        <v>-0.2293</v>
       </c>
       <c r="J210" t="n">
-        <v>-4.7256</v>
+        <v>-5.0446</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.65</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3794</v>
+        <v>-0.39</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.3468</v>
+        <v>-8.58</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>1.24</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5395</v>
       </c>
       <c r="J212" t="n">
-        <v>12.972</v>
+        <v>12.4085</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>0.98</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0224</v>
+        <v>-0.0323</v>
       </c>
       <c r="J213" t="n">
-        <v>-0.5152</v>
+        <v>-0.7429</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2139</v>
+        <v>-0.2308</v>
       </c>
       <c r="J214" t="n">
-        <v>-4.9197</v>
+        <v>-5.3084</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.72</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3019</v>
+        <v>-0.3172</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.9437</v>
+        <v>-7.2956</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.63</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3871</v>
+        <v>-0.3993</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.9033</v>
+        <v>-9.1839</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.54</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1951</v>
+        <v>1.1612</v>
       </c>
       <c r="J217" t="n">
-        <v>27.4873</v>
+        <v>26.7076</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.39</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9907</v>
+        <v>0.9327</v>
       </c>
       <c r="J218" t="n">
-        <v>22.7861</v>
+        <v>21.4521</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>1.15</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4391</v>
+        <v>0.435</v>
       </c>
       <c r="J219" t="n">
-        <v>10.0993</v>
+        <v>10.005</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>1.05</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1548</v>
+        <v>0.1712</v>
       </c>
       <c r="J220" t="n">
-        <v>3.5604</v>
+        <v>3.9376</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>0.82</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6206</v>
+        <v>-0.5773</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.2738</v>
+        <v>-13.2779</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.06</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1834</v>
+        <v>0.1858</v>
       </c>
       <c r="J222" t="n">
-        <v>3.4846</v>
+        <v>3.5302</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>0.95</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0809</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.311</v>
+        <v>-1.5371</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J224" t="n">
-        <v>-1.5428</v>
+        <v>-1.7822</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>0.89</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1364</v>
+        <v>-0.1514</v>
       </c>
       <c r="J225" t="n">
-        <v>-2.5916</v>
+        <v>-2.8766</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.75</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2784</v>
+        <v>-0.2932</v>
       </c>
       <c r="J226" t="n">
-        <v>-5.2896</v>
+        <v>-5.5708</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>1.53</v>
       </c>
       <c r="I227" t="n">
-        <v>1.1647</v>
+        <v>1.132</v>
       </c>
       <c r="J227" t="n">
-        <v>22.1293</v>
+        <v>21.508</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>1.35</v>
       </c>
       <c r="I228" t="n">
-        <v>0.8895</v>
+        <v>0.8403</v>
       </c>
       <c r="J228" t="n">
-        <v>16.9005</v>
+        <v>15.9657</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>1.24</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6442</v>
+        <v>0.6229</v>
       </c>
       <c r="J229" t="n">
-        <v>12.2398</v>
+        <v>11.8351</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>1.16</v>
       </c>
       <c r="I230" t="n">
-        <v>0.449</v>
+        <v>0.4474</v>
       </c>
       <c r="J230" t="n">
-        <v>8.531000000000001</v>
+        <v>8.5006</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>1.04</v>
       </c>
       <c r="I231" t="n">
-        <v>0.1036</v>
+        <v>0.1269</v>
       </c>
       <c r="J231" t="n">
-        <v>1.9684</v>
+        <v>2.4111</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>0.87</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.1107</v>
+        <v>-0.1366</v>
       </c>
       <c r="J232" t="n">
-        <v>-1.7712</v>
+        <v>-2.1856</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>0.71</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.2821</v>
+        <v>-0.3039</v>
       </c>
       <c r="J233" t="n">
-        <v>-4.5136</v>
+        <v>-4.8624</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>0.63</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3548</v>
+        <v>-0.3742</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.6768</v>
+        <v>-5.9872</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>0.61</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.373</v>
+        <v>-0.3916</v>
       </c>
       <c r="J235" t="n">
-        <v>-5.968</v>
+        <v>-6.2656</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.47</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5039</v>
+        <v>-0.5148</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.0624</v>
+        <v>-8.236800000000001</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.8</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4365</v>
+        <v>1.4305</v>
       </c>
       <c r="J237" t="n">
-        <v>22.984</v>
+        <v>22.888</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>1.73</v>
       </c>
       <c r="I238" t="n">
-        <v>1.3571</v>
+        <v>1.3462</v>
       </c>
       <c r="J238" t="n">
-        <v>21.7136</v>
+        <v>21.5392</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>1.66</v>
       </c>
       <c r="I239" t="n">
-        <v>1.2771</v>
+        <v>1.2609</v>
       </c>
       <c r="J239" t="n">
-        <v>20.4336</v>
+        <v>20.1744</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>1.32</v>
       </c>
       <c r="I240" t="n">
-        <v>0.7785</v>
+        <v>0.7514</v>
       </c>
       <c r="J240" t="n">
-        <v>12.456</v>
+        <v>12.0224</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>1.06</v>
       </c>
       <c r="I241" t="n">
-        <v>0.1146</v>
+        <v>0.151</v>
       </c>
       <c r="J241" t="n">
-        <v>1.8336</v>
+        <v>2.416</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.09</v>
       </c>
       <c r="I242" t="n">
-        <v>0.1992</v>
+        <v>0.202</v>
       </c>
       <c r="J242" t="n">
-        <v>4.1832</v>
+        <v>4.242</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.03</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0921</v>
+        <v>0.0945</v>
       </c>
       <c r="J243" t="n">
-        <v>1.9341</v>
+        <v>1.9845</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>0.89</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.134</v>
+        <v>-0.1496</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.814</v>
+        <v>-3.1416</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>0.72</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3035</v>
+        <v>-0.3184</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.3735</v>
+        <v>-6.6864</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.71</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3131</v>
+        <v>-0.3277</v>
       </c>
       <c r="J246" t="n">
-        <v>-6.5751</v>
+        <v>-6.8817</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>2.06</v>
       </c>
       <c r="I247" t="n">
-        <v>1.1199</v>
+        <v>1.1158</v>
       </c>
       <c r="J247" t="n">
-        <v>23.5179</v>
+        <v>23.4318</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>1.51</v>
       </c>
       <c r="I248" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6331</v>
       </c>
       <c r="J248" t="n">
-        <v>13.2636</v>
+        <v>13.2951</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>1.19</v>
       </c>
       <c r="I249" t="n">
-        <v>0.2687</v>
+        <v>0.2866</v>
       </c>
       <c r="J249" t="n">
-        <v>5.6427</v>
+        <v>6.0186</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>0.7</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3569</v>
+        <v>-0.364</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.4949</v>
+        <v>-7.644</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.61</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.439</v>
+        <v>-0.4434</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.218999999999999</v>
+        <v>-9.311400000000001</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.62</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2545</v>
+        <v>1.232</v>
       </c>
       <c r="J252" t="n">
-        <v>25.09</v>
+        <v>24.64</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1.49</v>
       </c>
       <c r="I253" t="n">
-        <v>1.097</v>
+        <v>1.0623</v>
       </c>
       <c r="J253" t="n">
-        <v>21.94</v>
+        <v>21.246</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>1.32</v>
       </c>
       <c r="I254" t="n">
-        <v>0.8073</v>
+        <v>0.7713</v>
       </c>
       <c r="J254" t="n">
-        <v>16.146</v>
+        <v>15.426</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>1.24</v>
       </c>
       <c r="I255" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="J255" t="n">
-        <v>12.49</v>
+        <v>12.188</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>1.15</v>
       </c>
       <c r="I256" t="n">
-        <v>0.4007</v>
+        <v>0.4084</v>
       </c>
       <c r="J256" t="n">
-        <v>8.013999999999999</v>
+        <v>8.167999999999999</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>0.99</v>
       </c>
       <c r="I257" t="n">
-        <v>0.0384</v>
+        <v>0.012</v>
       </c>
       <c r="J257" t="n">
-        <v>0.768</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>0.8</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2102</v>
+        <v>-0.2302</v>
       </c>
       <c r="J258" t="n">
-        <v>-4.204</v>
+        <v>-4.604</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>0.75</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2576</v>
+        <v>-0.2771</v>
       </c>
       <c r="J259" t="n">
-        <v>-5.152</v>
+        <v>-5.542</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>0.64</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3603</v>
+        <v>-0.3768</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.206</v>
+        <v>-7.536</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.59</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4072</v>
+        <v>-0.4214</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.144</v>
+        <v>-8.428000000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.99</v>
       </c>
       <c r="I262" t="n">
-        <v>1.6542</v>
+        <v>1.6587</v>
       </c>
       <c r="J262" t="n">
-        <v>28.1214</v>
+        <v>28.1979</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>1.89</v>
       </c>
       <c r="I263" t="n">
-        <v>1.5425</v>
+        <v>1.5415</v>
       </c>
       <c r="J263" t="n">
-        <v>26.2225</v>
+        <v>26.2055</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>1.34</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8277</v>
+        <v>0.7938</v>
       </c>
       <c r="J264" t="n">
-        <v>14.0709</v>
+        <v>13.4946</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>1.32</v>
       </c>
       <c r="I265" t="n">
-        <v>0.7832</v>
+        <v>0.7547</v>
       </c>
       <c r="J265" t="n">
-        <v>13.3144</v>
+        <v>12.8299</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.91</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4365</v>
+        <v>-0.397</v>
       </c>
       <c r="J266" t="n">
-        <v>-7.4205</v>
+        <v>-6.749</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>0.86</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.132</v>
+        <v>-0.1558</v>
       </c>
       <c r="J267" t="n">
-        <v>-2.244</v>
+        <v>-2.6486</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>0.83</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1656</v>
+        <v>-0.189</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.8152</v>
+        <v>-3.213</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>0.78</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2187</v>
+        <v>-0.241</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.7179</v>
+        <v>-4.097</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.58</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4062</v>
+        <v>-0.4222</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.9054</v>
+        <v>-7.1774</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.4</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5747</v>
+        <v>-0.5799</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.7699</v>
+        <v>-9.8583</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>1.69</v>
       </c>
       <c r="I272" t="n">
-        <v>0.8159</v>
+        <v>0.8047</v>
       </c>
       <c r="J272" t="n">
-        <v>14.6862</v>
+        <v>14.4846</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>1.43</v>
       </c>
       <c r="I273" t="n">
-        <v>0.5384</v>
+        <v>0.5468</v>
       </c>
       <c r="J273" t="n">
-        <v>9.6912</v>
+        <v>9.8424</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>1.26</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3478</v>
+        <v>0.3648</v>
       </c>
       <c r="J274" t="n">
-        <v>6.2604</v>
+        <v>6.5664</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>0.96</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.0917</v>
       </c>
       <c r="J275" t="n">
-        <v>-1.5822</v>
+        <v>-1.6506</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.89</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.1706</v>
+        <v>-0.178</v>
       </c>
       <c r="J276" t="n">
-        <v>-3.0708</v>
+        <v>-3.204</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>0.96</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.0416</v>
+        <v>-0.0559</v>
       </c>
       <c r="J277" t="n">
-        <v>-0.7488</v>
+        <v>-1.0062</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>0.92</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0921</v>
+        <v>-0.1087</v>
       </c>
       <c r="J278" t="n">
-        <v>-1.6578</v>
+        <v>-1.9566</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>0.79</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2274</v>
+        <v>-0.2455</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.0932</v>
+        <v>-4.419</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>0.79</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2274</v>
+        <v>-0.2455</v>
       </c>
       <c r="J280" t="n">
-        <v>-4.0932</v>
+        <v>-4.419</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>0.66</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3518</v>
+        <v>-0.3668</v>
       </c>
       <c r="J281" t="n">
-        <v>-6.3324</v>
+        <v>-6.6024</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>1.32</v>
       </c>
       <c r="I282" t="n">
-        <v>0.6835</v>
+        <v>0.6522</v>
       </c>
       <c r="J282" t="n">
-        <v>16.404</v>
+        <v>15.6528</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>1.17</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4076</v>
+        <v>0.3999</v>
       </c>
       <c r="J283" t="n">
-        <v>9.782400000000001</v>
+        <v>9.5976</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>0.91</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1156</v>
+        <v>-0.1297</v>
       </c>
       <c r="J284" t="n">
-        <v>-2.7744</v>
+        <v>-3.1128</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>0.71</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3182</v>
+        <v>-0.3317</v>
       </c>
       <c r="J285" t="n">
-        <v>-7.6368</v>
+        <v>-7.9608</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.53</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4853</v>
+        <v>-0.4918</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.6472</v>
+        <v>-11.8032</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1.52</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1584</v>
+        <v>1.124</v>
       </c>
       <c r="J287" t="n">
-        <v>27.8016</v>
+        <v>26.976</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>1.45</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0693</v>
+        <v>1.0252</v>
       </c>
       <c r="J288" t="n">
-        <v>25.6632</v>
+        <v>24.6048</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>1.22</v>
       </c>
       <c r="I289" t="n">
-        <v>0.6022</v>
+        <v>0.5843</v>
       </c>
       <c r="J289" t="n">
-        <v>14.4528</v>
+        <v>14.0232</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>1.15</v>
       </c>
       <c r="I290" t="n">
-        <v>0.4293</v>
+        <v>0.4283</v>
       </c>
       <c r="J290" t="n">
-        <v>10.3032</v>
+        <v>10.2792</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>0.84</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5786</v>
+        <v>-0.5375</v>
       </c>
       <c r="J291" t="n">
-        <v>-13.8864</v>
+        <v>-12.9</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.49</v>
       </c>
       <c r="I292" t="n">
-        <v>0.9543</v>
+        <v>0.8995</v>
       </c>
       <c r="J292" t="n">
-        <v>21.9489</v>
+        <v>20.6885</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>0.99</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.0176</v>
+        <v>-0.023</v>
       </c>
       <c r="J293" t="n">
-        <v>-0.4048</v>
+        <v>-0.529</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>0.97</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.0472</v>
+        <v>-0.0561</v>
       </c>
       <c r="J294" t="n">
-        <v>-1.0856</v>
+        <v>-1.2903</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.96</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.0601</v>
+        <v>-0.0701</v>
       </c>
       <c r="J295" t="n">
-        <v>-1.3823</v>
+        <v>-1.6123</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.39</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6131</v>
+        <v>-0.6116</v>
       </c>
       <c r="J296" t="n">
-        <v>-14.1013</v>
+        <v>-14.0668</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>1.76</v>
       </c>
       <c r="I297" t="n">
-        <v>1.4788</v>
+        <v>1.46</v>
       </c>
       <c r="J297" t="n">
-        <v>34.0124</v>
+        <v>33.58</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.17</v>
       </c>
       <c r="I298" t="n">
-        <v>0.493</v>
+        <v>0.4831</v>
       </c>
       <c r="J298" t="n">
-        <v>11.339</v>
+        <v>11.1113</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.12</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3657</v>
+        <v>0.3666</v>
       </c>
       <c r="J299" t="n">
-        <v>8.411099999999999</v>
+        <v>8.431800000000001</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>0.99</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0944</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J300" t="n">
-        <v>-2.1712</v>
+        <v>-2.001</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>0.78</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.7177</v>
+        <v>-0.6647</v>
       </c>
       <c r="J301" t="n">
-        <v>-16.5071</v>
+        <v>-15.2881</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>1.32</v>
       </c>
       <c r="I302" t="n">
-        <v>0.8534</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="J302" t="n">
-        <v>20.4816</v>
+        <v>19.2696</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>1.31</v>
       </c>
       <c r="I303" t="n">
-        <v>0.8302</v>
+        <v>0.7826</v>
       </c>
       <c r="J303" t="n">
-        <v>19.9248</v>
+        <v>18.7824</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>1.29</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7834</v>
+        <v>0.7416</v>
       </c>
       <c r="J304" t="n">
-        <v>18.8016</v>
+        <v>17.7984</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>0.96</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2057</v>
+        <v>-0.1975</v>
       </c>
       <c r="J305" t="n">
-        <v>-4.9368</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>0.9</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3922</v>
+        <v>-0.3722</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.412800000000001</v>
+        <v>-8.9328</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>1.32</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6369</v>
+        <v>0.6178</v>
       </c>
       <c r="J307" t="n">
-        <v>15.2856</v>
+        <v>14.8272</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>1.1</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2374</v>
+        <v>0.246</v>
       </c>
       <c r="J308" t="n">
-        <v>5.6976</v>
+        <v>5.904</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>1.08</v>
       </c>
       <c r="I309" t="n">
-        <v>0.1967</v>
+        <v>0.2065</v>
       </c>
       <c r="J309" t="n">
-        <v>4.7208</v>
+        <v>4.956</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>1.05</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1326</v>
+        <v>0.1431</v>
       </c>
       <c r="J310" t="n">
-        <v>3.1824</v>
+        <v>3.4344</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.65</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3874</v>
+        <v>-0.3963</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.297599999999999</v>
+        <v>-9.511200000000001</v>
       </c>
     </row>
     <row r="312">
@@ -14875,10 +14875,10 @@
         <v>1.77</v>
       </c>
       <c r="I312" t="n">
-        <v>1.5041</v>
+        <v>1.4845</v>
       </c>
       <c r="J312" t="n">
-        <v>33.0902</v>
+        <v>32.659</v>
       </c>
     </row>
     <row r="313">
@@ -14915,10 +14915,10 @@
         <v>1.44</v>
       </c>
       <c r="I313" t="n">
-        <v>1.0813</v>
+        <v>1.034</v>
       </c>
       <c r="J313" t="n">
-        <v>23.7886</v>
+        <v>22.748</v>
       </c>
     </row>
     <row r="314">
@@ -14955,10 +14955,10 @@
         <v>1.1</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3181</v>
+        <v>0.3209</v>
       </c>
       <c r="J314" t="n">
-        <v>6.9982</v>
+        <v>7.0598</v>
       </c>
     </row>
     <row r="315">
@@ -14995,10 +14995,10 @@
         <v>0.79</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.6835</v>
+        <v>-0.636</v>
       </c>
       <c r="J315" t="n">
-        <v>-15.037</v>
+        <v>-13.992</v>
       </c>
     </row>
     <row r="316">
@@ -15035,10 +15035,10 @@
         <v>0.55</v>
       </c>
       <c r="I316" t="n">
-        <v>-1.2629</v>
+        <v>-1.1391</v>
       </c>
       <c r="J316" t="n">
-        <v>-27.7838</v>
+        <v>-25.0602</v>
       </c>
     </row>
     <row r="317">
@@ -15075,10 +15075,10 @@
         <v>1.37</v>
       </c>
       <c r="I317" t="n">
-        <v>0.7692</v>
+        <v>0.7295</v>
       </c>
       <c r="J317" t="n">
-        <v>16.9224</v>
+        <v>16.049</v>
       </c>
     </row>
     <row r="318">
@@ -15115,10 +15115,10 @@
         <v>1.02</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0805</v>
+        <v>0.0838</v>
       </c>
       <c r="J318" t="n">
-        <v>1.771</v>
+        <v>1.8436</v>
       </c>
     </row>
     <row r="319">
@@ -15155,10 +15155,10 @@
         <v>0.93</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.1067</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.0614</v>
+        <v>-2.3474</v>
       </c>
     </row>
     <row r="320">
@@ -15195,10 +15195,10 @@
         <v>0.75</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2801</v>
+        <v>-0.2945</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.1622</v>
+        <v>-6.479</v>
       </c>
     </row>
     <row r="321">
@@ -15235,10 +15235,10 @@
         <v>0.59</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.431</v>
+        <v>-0.4401</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.481999999999999</v>
+        <v>-9.6822</v>
       </c>
     </row>
     <row r="322">
@@ -15275,10 +15275,10 @@
         <v>1.51</v>
       </c>
       <c r="I322" t="n">
-        <v>1.1764</v>
+        <v>1.1375</v>
       </c>
       <c r="J322" t="n">
-        <v>41.174</v>
+        <v>39.8125</v>
       </c>
     </row>
     <row r="323">
@@ -15315,10 +15315,10 @@
         <v>1.17</v>
       </c>
       <c r="I323" t="n">
-        <v>0.5018</v>
+        <v>0.4891</v>
       </c>
       <c r="J323" t="n">
-        <v>17.563</v>
+        <v>17.1185</v>
       </c>
     </row>
     <row r="324">
@@ -15355,10 +15355,10 @@
         <v>1.13</v>
       </c>
       <c r="I324" t="n">
-        <v>0.3992</v>
+        <v>0.3956</v>
       </c>
       <c r="J324" t="n">
-        <v>13.972</v>
+        <v>13.846</v>
       </c>
     </row>
     <row r="325">
@@ -15395,10 +15395,10 @@
         <v>1.09</v>
       </c>
       <c r="I325" t="n">
-        <v>0.2921</v>
+        <v>0.2963</v>
       </c>
       <c r="J325" t="n">
-        <v>10.2235</v>
+        <v>10.3705</v>
       </c>
     </row>
     <row r="326">
@@ -15435,10 +15435,10 @@
         <v>0.7</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.906</v>
+        <v>-0.8318</v>
       </c>
       <c r="J326" t="n">
-        <v>-31.71</v>
+        <v>-29.113</v>
       </c>
     </row>
     <row r="327">
@@ -15475,10 +15475,10 @@
         <v>1.17</v>
       </c>
       <c r="I327" t="n">
-        <v>0.3931</v>
+        <v>0.3893</v>
       </c>
       <c r="J327" t="n">
-        <v>13.7585</v>
+        <v>13.6255</v>
       </c>
     </row>
     <row r="328">
@@ -15515,10 +15515,10 @@
         <v>1.1</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2549</v>
+        <v>0.2587</v>
       </c>
       <c r="J328" t="n">
-        <v>8.9215</v>
+        <v>9.054500000000001</v>
       </c>
     </row>
     <row r="329">
@@ -15555,10 +15555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="J329" t="n">
-        <v>-2.975</v>
+        <v>-3.381</v>
       </c>
     </row>
     <row r="330">
@@ -15595,10 +15595,10 @@
         <v>0.88</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1525</v>
+        <v>-0.1665</v>
       </c>
       <c r="J330" t="n">
-        <v>-5.3375</v>
+        <v>-5.8275</v>
       </c>
     </row>
     <row r="331">
@@ -15635,10 +15635,10 @@
         <v>0.75</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.2845</v>
+        <v>-0.298</v>
       </c>
       <c r="J331" t="n">
-        <v>-9.9575</v>
+        <v>-10.43</v>
       </c>
     </row>
     <row r="332">
@@ -15675,10 +15675,10 @@
         <v>1.62</v>
       </c>
       <c r="I332" t="n">
-        <v>1.2501</v>
+        <v>1.2281</v>
       </c>
       <c r="J332" t="n">
-        <v>22.5018</v>
+        <v>22.1058</v>
       </c>
     </row>
     <row r="333">
@@ -15715,10 +15715,10 @@
         <v>1.45</v>
       </c>
       <c r="I333" t="n">
-        <v>1.0439</v>
+        <v>1.0009</v>
       </c>
       <c r="J333" t="n">
-        <v>18.7902</v>
+        <v>18.0162</v>
       </c>
     </row>
     <row r="334">
@@ -15755,10 +15755,10 @@
         <v>1.39</v>
       </c>
       <c r="I334" t="n">
-        <v>0.9492</v>
+        <v>0.8995</v>
       </c>
       <c r="J334" t="n">
-        <v>17.0856</v>
+        <v>16.191</v>
       </c>
     </row>
     <row r="335">
@@ -15795,10 +15795,10 @@
         <v>1.34</v>
       </c>
       <c r="I335" t="n">
-        <v>0.8468</v>
+        <v>0.8069</v>
       </c>
       <c r="J335" t="n">
-        <v>15.2424</v>
+        <v>14.5242</v>
       </c>
     </row>
     <row r="336">
@@ -15835,10 +15835,10 @@
         <v>1.14</v>
       </c>
       <c r="I336" t="n">
-        <v>0.369</v>
+        <v>0.3807</v>
       </c>
       <c r="J336" t="n">
-        <v>6.642</v>
+        <v>6.8526</v>
       </c>
     </row>
     <row r="337">
@@ -15875,10 +15875,10 @@
         <v>1.35</v>
       </c>
       <c r="I337" t="n">
-        <v>0.8668</v>
+        <v>0.7968</v>
       </c>
       <c r="J337" t="n">
-        <v>15.6024</v>
+        <v>14.3424</v>
       </c>
     </row>
     <row r="338">
@@ -15915,10 +15915,10 @@
         <v>0.66</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.3395</v>
+        <v>-0.3571</v>
       </c>
       <c r="J338" t="n">
-        <v>-6.111</v>
+        <v>-6.4278</v>
       </c>
     </row>
     <row r="339">
@@ -15955,10 +15955,10 @@
         <v>0.59</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.405</v>
+        <v>-0.4197</v>
       </c>
       <c r="J339" t="n">
-        <v>-7.29</v>
+        <v>-7.5546</v>
       </c>
     </row>
     <row r="340">
@@ -15995,10 +15995,10 @@
         <v>0.57</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4237</v>
+        <v>-0.4374</v>
       </c>
       <c r="J340" t="n">
-        <v>-7.6266</v>
+        <v>-7.8732</v>
       </c>
     </row>
     <row r="341">
@@ -16035,10 +16035,10 @@
         <v>0.53</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4611</v>
+        <v>-0.4727</v>
       </c>
       <c r="J341" t="n">
-        <v>-8.299799999999999</v>
+        <v>-8.508599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7485/event_7485_evp_summary.xlsx
+++ b/database/event/7485/event_7485_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.7776</v>
+        <v>9.077400000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5482</v>
+        <v>3.6694</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3715</v>
+        <v>3.4409</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7776</v>
+        <v>9.077400000000001</v>
       </c>
       <c r="F2" t="n">
         <v>4.2839</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.4742</v>
+        <v>7.5549</v>
       </c>
       <c r="C3" t="n">
-        <v>3.0213</v>
+        <v>3.054</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7782</v>
+        <v>2.7608</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4742</v>
+        <v>7.5549</v>
       </c>
       <c r="F3" t="n">
         <v>3.2613</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.2036</v>
+        <v>7.3275</v>
       </c>
       <c r="C4" t="n">
-        <v>2.9119</v>
+        <v>2.962</v>
       </c>
       <c r="D4" t="n">
-        <v>2.655</v>
+        <v>2.6592</v>
       </c>
       <c r="E4" t="n">
-        <v>7.2036</v>
+        <v>7.3275</v>
       </c>
       <c r="F4" t="n">
         <v>3.0336</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.7704</v>
+        <v>6.7952</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7368</v>
+        <v>2.7469</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4578</v>
+        <v>2.4214</v>
       </c>
       <c r="E5" t="n">
-        <v>6.7704</v>
+        <v>6.7952</v>
       </c>
       <c r="F5" t="n">
         <v>2.7703</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0634</v>
+        <v>5.446</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0468</v>
+        <v>2.2015</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6808</v>
+        <v>1.8188</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0634</v>
+        <v>5.446</v>
       </c>
       <c r="F6" t="n">
         <v>2.8721</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.376</v>
+        <v>4.5157</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7689</v>
+        <v>1.8254</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3678</v>
+        <v>1.4032</v>
       </c>
       <c r="E7" t="n">
-        <v>4.376</v>
+        <v>4.5157</v>
       </c>
       <c r="F7" t="n">
         <v>1.1728</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6786</v>
+        <v>3.6933</v>
       </c>
       <c r="C8" t="n">
-        <v>1.487</v>
+        <v>1.493</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0504</v>
+        <v>1.0359</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6786</v>
+        <v>3.6933</v>
       </c>
       <c r="F8" t="n">
         <v>3.2262</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4379</v>
+        <v>3.6225</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3897</v>
+        <v>1.4643</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9408</v>
+        <v>1.0043</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4379</v>
+        <v>3.6225</v>
       </c>
       <c r="F9" t="n">
-        <v>2.043</v>
+        <v>2.4614</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3949</v>
+        <v>0.8007</v>
       </c>
       <c r="H9" t="n">
-        <v>2.043</v>
+        <v>2.6623</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1032</v>
+        <v>2.6623</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3949</v>
+        <v>0.8007</v>
       </c>
       <c r="K9" t="n">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="L9" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4981</v>
+        <v>3.463</v>
       </c>
       <c r="N9" t="n">
-        <v>229</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3495</v>
+        <v>3.3858</v>
       </c>
       <c r="C10" t="n">
-        <v>1.354</v>
+        <v>1.3687</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9006</v>
+        <v>0.8985</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3495</v>
+        <v>3.3858</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1573</v>
+        <v>2.043</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1922</v>
+        <v>1.3949</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1573</v>
+        <v>2.043</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2129</v>
+        <v>1.1032</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1922</v>
+        <v>1.3949</v>
       </c>
       <c r="K10" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L10" t="n">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4051</v>
+        <v>2.4981</v>
       </c>
       <c r="N10" t="n">
-        <v>175</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2621</v>
+        <v>3.236</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3187</v>
+        <v>1.3081</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8608</v>
+        <v>0.8316</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2621</v>
+        <v>3.236</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4614</v>
+        <v>2.1573</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8007</v>
+        <v>1.1922</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6623</v>
+        <v>2.1573</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6623</v>
+        <v>2.2129</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8007</v>
+        <v>1.1922</v>
       </c>
       <c r="K11" t="n">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="L11" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M11" t="n">
-        <v>3.463</v>
+        <v>3.4051</v>
       </c>
       <c r="N11" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.973</v>
+        <v>3.0783</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2018</v>
+        <v>1.2444</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7292</v>
+        <v>0.7612</v>
       </c>
       <c r="E12" t="n">
-        <v>2.973</v>
+        <v>3.0783</v>
       </c>
       <c r="F12" t="n">
         <v>2.4097</v>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5541</v>
+        <v>2.8401</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0325</v>
+        <v>1.1481</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5385</v>
+        <v>0.6548</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5541</v>
+        <v>2.8401</v>
       </c>
       <c r="F13" t="n">
         <v>2.0833</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4972</v>
+        <v>2.568</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0095</v>
+        <v>1.0381</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5332</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4972</v>
+        <v>2.568</v>
       </c>
       <c r="F14" t="n">
         <v>2.3557</v>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2606</v>
+        <v>2.5028</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9137999999999999</v>
+        <v>1.0117</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4049</v>
+        <v>0.5041</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2606</v>
+        <v>2.5028</v>
       </c>
       <c r="F15" t="n">
         <v>1.6835</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1549</v>
+        <v>2.2426</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8711</v>
+        <v>0.9065</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3568</v>
+        <v>0.3879</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1549</v>
+        <v>2.2426</v>
       </c>
       <c r="F16" t="n">
         <v>1.1687</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1321</v>
+        <v>2.1914</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8619</v>
+        <v>0.8858</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3464</v>
+        <v>0.365</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1321</v>
+        <v>2.1914</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5419</v>
+        <v>0.4348</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4098</v>
+        <v>1.6235</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4925</v>
+        <v>0.4348</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8859</v>
+        <v>0.4348</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4098</v>
+        <v>1.6235</v>
       </c>
       <c r="K17" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L17" t="n">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4761</v>
+        <v>2.0583</v>
       </c>
       <c r="N17" t="n">
-        <v>247</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0583</v>
+        <v>2.0404</v>
       </c>
       <c r="C18" t="n">
-        <v>0.832</v>
+        <v>0.8248</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3128</v>
+        <v>0.2976</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0583</v>
+        <v>2.0404</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4348</v>
+        <v>2.5419</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6235</v>
+        <v>-0.4098</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4348</v>
+        <v>3.4925</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4348</v>
+        <v>1.8859</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6235</v>
+        <v>-0.4098</v>
       </c>
       <c r="K18" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L18" t="n">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0583</v>
+        <v>1.4761</v>
       </c>
       <c r="N18" t="n">
-        <v>190</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19">
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0525</v>
+        <v>1.8967</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8297</v>
+        <v>0.7667</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3101</v>
+        <v>0.2334</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0525</v>
+        <v>1.8967</v>
       </c>
       <c r="F19" t="n">
         <v>2.4242</v>
@@ -1324,16 +1324,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4345</v>
+        <v>1.5444</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5799</v>
+        <v>0.6243</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0288</v>
+        <v>0.076</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4345</v>
+        <v>1.5444</v>
       </c>
       <c r="F20" t="n">
         <v>0.8283</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2837</v>
+        <v>1.4837</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5189</v>
+        <v>0.5998</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0398</v>
+        <v>0.0489</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2837</v>
+        <v>1.4837</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1471</v>
+        <v>1.241</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4308</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1471</v>
+        <v>1.241</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1509</v>
+        <v>1.241</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4308</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="L21" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2799</v>
+        <v>1.241</v>
       </c>
       <c r="N21" t="n">
-        <v>249</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.241</v>
+        <v>1.2126</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5017</v>
+        <v>0.4902</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0593</v>
+        <v>-0.0722</v>
       </c>
       <c r="E22" t="n">
-        <v>1.241</v>
+        <v>1.2126</v>
       </c>
       <c r="F22" t="n">
-        <v>1.241</v>
+        <v>-0.1471</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1.4308</v>
       </c>
       <c r="H22" t="n">
-        <v>1.241</v>
+        <v>-0.1471</v>
       </c>
       <c r="I22" t="n">
-        <v>1.241</v>
+        <v>-0.1509</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1.4308</v>
       </c>
       <c r="K22" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="M22" t="n">
-        <v>1.241</v>
+        <v>1.2799</v>
       </c>
       <c r="N22" t="n">
-        <v>115</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23">
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1806</v>
+        <v>1.1397</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4772</v>
+        <v>0.4607</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0868</v>
+        <v>-0.1047</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1806</v>
+        <v>1.1397</v>
       </c>
       <c r="F23" t="n">
         <v>1.2198</v>
@@ -1504,127 +1504,127 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>ewjerkz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0564</v>
+        <v>1.0903</v>
       </c>
       <c r="C24" t="n">
-        <v>0.427</v>
+        <v>0.4407</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1433</v>
+        <v>-0.1268</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0564</v>
+        <v>1.0903</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7509</v>
+        <v>0.9686</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6945</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7509</v>
+        <v>0.9686</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7509</v>
+        <v>0.9686</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6945</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="L24" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0564</v>
+        <v>0.9686</v>
       </c>
       <c r="N24" t="n">
-        <v>125</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ewjerkz</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9686</v>
+        <v>0.989</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3915</v>
+        <v>0.3998</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1833</v>
+        <v>-0.1721</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9686</v>
+        <v>0.989</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9686</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9686</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9686</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9686</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.82</v>
+        <v>0.9562</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3315</v>
+        <v>0.3865</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2509</v>
+        <v>-0.1867</v>
       </c>
       <c r="E26" t="n">
-        <v>0.82</v>
+        <v>0.9562</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1028</v>
+        <v>1.7509</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2828</v>
+        <v>-0.6945</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1028</v>
+        <v>1.7509</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1028</v>
+        <v>1.7509</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2828</v>
+        <v>-0.6945</v>
       </c>
       <c r="K26" t="n">
         <v>81</v>
@@ -1633,7 +1633,7 @@
         <v>44</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8200000000000001</v>
+        <v>1.0564</v>
       </c>
       <c r="N26" t="n">
         <v>125</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7901</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3152</v>
+        <v>0.3194</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2693</v>
+        <v>-0.2609</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7901</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7796999999999999</v>
+        <v>1.1028</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.2828</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7796999999999999</v>
+        <v>1.1028</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7796999999999999</v>
+        <v>1.1028</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.2828</v>
       </c>
       <c r="K27" t="n">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28">
@@ -1692,16 +1692,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7231</v>
+        <v>0.751</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2923</v>
+        <v>0.3036</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.295</v>
+        <v>-0.2784</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7231</v>
+        <v>0.751</v>
       </c>
       <c r="F28" t="n">
         <v>0.4477</v>
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6848</v>
+        <v>0.6133</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2768</v>
+        <v>0.2479</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3125</v>
+        <v>-0.3399</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6848</v>
+        <v>0.6133</v>
       </c>
       <c r="F29" t="n">
         <v>0.9516</v>
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3301</v>
+        <v>0.3432</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1334</v>
+        <v>0.1387</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4739</v>
+        <v>-0.4605</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3301</v>
+        <v>0.3432</v>
       </c>
       <c r="F30" t="n">
         <v>0.7302</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1327</v>
+        <v>0.0993</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0536</v>
+        <v>0.0401</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5638</v>
+        <v>-0.5695</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1327</v>
+        <v>0.0993</v>
       </c>
       <c r="F31" t="n">
-        <v>1.6239</v>
+        <v>0.1213</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.4912</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.6239</v>
+        <v>0.1213</v>
       </c>
       <c r="I31" t="n">
-        <v>1.6657</v>
+        <v>0.1213</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.4912</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="L31" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1744999999999999</v>
+        <v>0.1213</v>
       </c>
       <c r="N31" t="n">
-        <v>249</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.1213</v>
+        <v>0.0577</v>
       </c>
       <c r="C32" t="n">
-        <v>0.049</v>
+        <v>0.0233</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.569</v>
+        <v>-0.588</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1213</v>
+        <v>0.0577</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1213</v>
+        <v>1.6239</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-1.4912</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1213</v>
+        <v>1.6239</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1213</v>
+        <v>1.6657</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-1.4912</v>
       </c>
       <c r="K32" t="n">
-        <v>57</v>
+        <v>122</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1213</v>
+        <v>0.1744999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>57</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33">
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5587</v>
+        <v>-0.6069</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2258</v>
+        <v>-0.2453</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8784999999999999</v>
+        <v>-0.8849</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5587</v>
+        <v>-0.6069</v>
       </c>
       <c r="F33" t="n">
         <v>-0.5587</v>
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6761</v>
+        <v>-0.7164</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2733</v>
+        <v>-0.2896</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9338</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6761</v>
+        <v>-0.7164</v>
       </c>
       <c r="F34" t="n">
         <v>-0.6761</v>
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7751</v>
+        <v>-0.766</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3133</v>
+        <v>-0.3096</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.977</v>
+        <v>-0.956</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7751</v>
+        <v>-0.766</v>
       </c>
       <c r="F35" t="n">
         <v>-0.7751</v>
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9826</v>
+        <v>-1.2014</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3972</v>
+        <v>-0.4856</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0715</v>
+        <v>-1.1505</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9826</v>
+        <v>-1.2014</v>
       </c>
       <c r="F36" t="n">
         <v>-0.4782</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>MUTiRiS</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1</v>
+        <v>-1.2644</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4042</v>
+        <v>-0.5111</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0794</v>
+        <v>-1.1786</v>
       </c>
       <c r="E37" t="n">
-        <v>-1</v>
+        <v>-1.2644</v>
       </c>
       <c r="F37" t="n">
-        <v>-1</v>
+        <v>-1.261</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1</v>
+        <v>-1.261</v>
       </c>
       <c r="I37" t="n">
-        <v>-1</v>
+        <v>-1.261</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1</v>
+        <v>-1.261</v>
       </c>
       <c r="N37" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MUTiRiS</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.261</v>
+        <v>-1.3931</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5097</v>
+        <v>-0.5631</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1982</v>
+        <v>-1.2361</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.261</v>
+        <v>-1.3931</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.261</v>
+        <v>-1</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.261</v>
+        <v>-1</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.261</v>
+        <v>-1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.261</v>
+        <v>-1</v>
       </c>
       <c r="N38" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39">
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3316</v>
+        <v>-1.6813</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5383</v>
+        <v>-0.6796</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2304</v>
+        <v>-1.3648</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3316</v>
+        <v>-1.6813</v>
       </c>
       <c r="F39" t="n">
         <v>-1.3316</v>
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2</v>
+        <v>-2.4928</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8085</v>
+        <v>-1.0077</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5346</v>
+        <v>-1.7273</v>
       </c>
       <c r="E40" t="n">
-        <v>-2</v>
+        <v>-2.4928</v>
       </c>
       <c r="F40" t="n">
         <v>-2</v>
@@ -2286,93 +2286,93 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4146</v>
+        <v>-2.7704</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9761</v>
+        <v>-1.1199</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7234</v>
+        <v>-1.8513</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4146</v>
+        <v>-2.7704</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4146</v>
+        <v>-1.1698</v>
       </c>
       <c r="G41" t="n">
-        <v>-1</v>
+        <v>-1.2927</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4146</v>
+        <v>-1.1698</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.4511</v>
+        <v>-0.6317</v>
       </c>
       <c r="J41" t="n">
-        <v>-1</v>
+        <v>-1.2927</v>
       </c>
       <c r="K41" t="n">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="L41" t="n">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4511</v>
+        <v>-1.9244</v>
       </c>
       <c r="N41" t="n">
-        <v>175</v>
+        <v>247</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.4625</v>
+        <v>-2.8221</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.9954</v>
+        <v>-1.1408</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.7452</v>
+        <v>-1.8744</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.4625</v>
+        <v>-2.8221</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.1698</v>
+        <v>-1.4146</v>
       </c>
       <c r="G42" t="n">
-        <v>-1.2927</v>
+        <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.1698</v>
+        <v>-1.4146</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.6317</v>
+        <v>-1.4511</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.2927</v>
+        <v>-1</v>
       </c>
       <c r="K42" t="n">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="L42" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="M42" t="n">
-        <v>-1.9244</v>
+        <v>-2.4511</v>
       </c>
       <c r="N42" t="n">
-        <v>247</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7485/event_7485_evp_summary.xlsx
+++ b/database/event/7485/event_7485_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.077400000000001</v>
+        <v>8.806800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6694</v>
+        <v>3.56</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4409</v>
+        <v>3.4061</v>
       </c>
       <c r="E2" t="n">
-        <v>9.077400000000001</v>
+        <v>8.806800000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2839</v>
+        <v>4.0872</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4937</v>
+        <v>4.4198</v>
       </c>
       <c r="H2" t="n">
-        <v>9.24</v>
+        <v>8.9024</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9895</v>
+        <v>4.9984</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4937</v>
+        <v>4.4198</v>
       </c>
       <c r="K2" t="n">
         <v>99</v>
@@ -529,7 +529,7 @@
         <v>148</v>
       </c>
       <c r="M2" t="n">
-        <v>9.4832</v>
+        <v>9.418200000000001</v>
       </c>
       <c r="N2" t="n">
         <v>247</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.5549</v>
+        <v>7.5294</v>
       </c>
       <c r="C3" t="n">
-        <v>3.054</v>
+        <v>3.0436</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7608</v>
+        <v>2.8242</v>
       </c>
       <c r="E3" t="n">
-        <v>7.5549</v>
+        <v>7.5294</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2613</v>
+        <v>3.2239</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2129</v>
+        <v>4.2248</v>
       </c>
       <c r="H3" t="n">
-        <v>5.866</v>
+        <v>5.6612</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1676</v>
+        <v>3.1786</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2129</v>
+        <v>4.2248</v>
       </c>
       <c r="K3" t="n">
         <v>99</v>
@@ -575,7 +575,7 @@
         <v>148</v>
       </c>
       <c r="M3" t="n">
-        <v>7.380500000000001</v>
+        <v>7.4034</v>
       </c>
       <c r="N3" t="n">
         <v>247</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.3275</v>
+        <v>7.3545</v>
       </c>
       <c r="C4" t="n">
-        <v>2.962</v>
+        <v>2.9729</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6592</v>
+        <v>2.7445</v>
       </c>
       <c r="E4" t="n">
-        <v>7.3275</v>
+        <v>7.3545</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0336</v>
+        <v>3.0462</v>
       </c>
       <c r="G4" t="n">
-        <v>4.17</v>
+        <v>4.1844</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1149</v>
+        <v>4.994</v>
       </c>
       <c r="I4" t="n">
-        <v>2.762</v>
+        <v>2.804</v>
       </c>
       <c r="J4" t="n">
-        <v>4.17</v>
+        <v>4.1844</v>
       </c>
       <c r="K4" t="n">
         <v>99</v>
@@ -621,7 +621,7 @@
         <v>148</v>
       </c>
       <c r="M4" t="n">
-        <v>6.932</v>
+        <v>6.9884</v>
       </c>
       <c r="N4" t="n">
         <v>247</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.7952</v>
+        <v>6.6129</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7469</v>
+        <v>2.6732</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4214</v>
+        <v>2.4067</v>
       </c>
       <c r="E5" t="n">
-        <v>6.7952</v>
+        <v>6.6129</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7703</v>
+        <v>2.8154</v>
       </c>
       <c r="G5" t="n">
-        <v>4.0001</v>
+        <v>3.7727</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2462</v>
+        <v>4.1276</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2929</v>
+        <v>2.3175</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0001</v>
+        <v>3.7727</v>
       </c>
       <c r="K5" t="n">
         <v>109</v>
@@ -667,7 +667,7 @@
         <v>120</v>
       </c>
       <c r="M5" t="n">
-        <v>6.292999999999999</v>
+        <v>6.090199999999999</v>
       </c>
       <c r="N5" t="n">
         <v>229</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.446</v>
+        <v>5.2722</v>
       </c>
       <c r="C6" t="n">
-        <v>2.2015</v>
+        <v>2.1312</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8188</v>
+        <v>1.796</v>
       </c>
       <c r="E6" t="n">
-        <v>5.446</v>
+        <v>5.2722</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8721</v>
+        <v>2.7829</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1913</v>
+        <v>2.1067</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5612</v>
+        <v>3.4274</v>
       </c>
       <c r="I6" t="n">
-        <v>3.653</v>
+        <v>3.519</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1913</v>
+        <v>2.1067</v>
       </c>
       <c r="K6" t="n">
         <v>122</v>
@@ -713,7 +713,7 @@
         <v>127</v>
       </c>
       <c r="M6" t="n">
-        <v>5.8443</v>
+        <v>5.6257</v>
       </c>
       <c r="N6" t="n">
         <v>249</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5157</v>
+        <v>4.4062</v>
       </c>
       <c r="C7" t="n">
-        <v>1.8254</v>
+        <v>1.7811</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4032</v>
+        <v>1.4014</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5157</v>
+        <v>4.4062</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1728</v>
+        <v>1.1176</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2033</v>
+        <v>3.1489</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1728</v>
+        <v>1.1176</v>
       </c>
       <c r="I7" t="n">
-        <v>1.203</v>
+        <v>1.1475</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2033</v>
+        <v>3.1489</v>
       </c>
       <c r="K7" t="n">
         <v>122</v>
@@ -759,7 +759,7 @@
         <v>127</v>
       </c>
       <c r="M7" t="n">
-        <v>4.4063</v>
+        <v>4.2964</v>
       </c>
       <c r="N7" t="n">
         <v>249</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6933</v>
+        <v>3.6914</v>
       </c>
       <c r="C8" t="n">
-        <v>1.493</v>
+        <v>1.4922</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0359</v>
+        <v>1.0758</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6933</v>
+        <v>3.6914</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2262</v>
+        <v>3.2423</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4524</v>
+        <v>0.4344</v>
       </c>
       <c r="H8" t="n">
-        <v>5.7503</v>
+        <v>5.7303</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1051</v>
+        <v>3.2174</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4524</v>
+        <v>0.4344</v>
       </c>
       <c r="K8" t="n">
         <v>109</v>
@@ -805,7 +805,7 @@
         <v>120</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5575</v>
+        <v>3.6518</v>
       </c>
       <c r="N8" t="n">
         <v>229</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6225</v>
+        <v>3.544</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4643</v>
+        <v>1.4326</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0043</v>
+        <v>1.0087</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6225</v>
+        <v>3.544</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4614</v>
+        <v>2.4557</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8007</v>
+        <v>0.7279</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6623</v>
+        <v>2.6775</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6623</v>
+        <v>2.6775</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8007</v>
+        <v>0.7279</v>
       </c>
       <c r="K9" t="n">
         <v>81</v>
@@ -851,7 +851,7 @@
         <v>44</v>
       </c>
       <c r="M9" t="n">
-        <v>3.463</v>
+        <v>3.4054</v>
       </c>
       <c r="N9" t="n">
         <v>125</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3858</v>
+        <v>3.1536</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3687</v>
+        <v>1.2748</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8985</v>
+        <v>0.8308</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3858</v>
+        <v>3.1536</v>
       </c>
       <c r="F10" t="n">
-        <v>2.043</v>
+        <v>1.8769</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3949</v>
+        <v>1.3288</v>
       </c>
       <c r="H10" t="n">
-        <v>2.043</v>
+        <v>1.8769</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1032</v>
+        <v>1.0538</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3949</v>
+        <v>1.3288</v>
       </c>
       <c r="K10" t="n">
         <v>109</v>
@@ -897,7 +897,7 @@
         <v>120</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4981</v>
+        <v>2.3826</v>
       </c>
       <c r="N10" t="n">
         <v>229</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.236</v>
+        <v>3.004</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3081</v>
+        <v>1.2143</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8316</v>
+        <v>0.7627</v>
       </c>
       <c r="E11" t="n">
-        <v>3.236</v>
+        <v>3.004</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1573</v>
+        <v>1.9894</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1922</v>
+        <v>1.128</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1573</v>
+        <v>1.9894</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2129</v>
+        <v>2.0426</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1922</v>
+        <v>1.128</v>
       </c>
       <c r="K11" t="n">
         <v>116</v>
@@ -943,7 +943,7 @@
         <v>59</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4051</v>
+        <v>3.1706</v>
       </c>
       <c r="N11" t="n">
         <v>175</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0783</v>
+        <v>2.9858</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2444</v>
+        <v>1.207</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7612</v>
+        <v>0.7544</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0783</v>
+        <v>2.9858</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4097</v>
+        <v>2.4438</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5633</v>
+        <v>0.4367</v>
       </c>
       <c r="H12" t="n">
-        <v>3.0563</v>
+        <v>2.7323</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6504</v>
+        <v>1.5341</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5633</v>
+        <v>0.4367</v>
       </c>
       <c r="K12" t="n">
         <v>109</v>
@@ -989,7 +989,7 @@
         <v>120</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2137</v>
+        <v>1.9708</v>
       </c>
       <c r="N12" t="n">
         <v>229</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8401</v>
+        <v>2.6921</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1481</v>
+        <v>1.0882</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6548</v>
+        <v>0.6206</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8401</v>
+        <v>2.6921</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0833</v>
+        <v>1.9538</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4708</v>
+        <v>0.4524</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0833</v>
+        <v>1.9538</v>
       </c>
       <c r="I13" t="n">
-        <v>2.137</v>
+        <v>2.006</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4708</v>
+        <v>0.4524</v>
       </c>
       <c r="K13" t="n">
         <v>116</v>
@@ -1035,7 +1035,7 @@
         <v>59</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6078</v>
+        <v>2.4584</v>
       </c>
       <c r="N13" t="n">
         <v>175</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.568</v>
+        <v>2.4924</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0381</v>
+        <v>1.0075</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5332</v>
+        <v>0.5296</v>
       </c>
       <c r="E14" t="n">
-        <v>2.568</v>
+        <v>2.4924</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3557</v>
+        <v>2.3178</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1415</v>
+        <v>0.1038</v>
       </c>
       <c r="H14" t="n">
-        <v>2.431</v>
+        <v>2.3615</v>
       </c>
       <c r="I14" t="n">
-        <v>2.431</v>
+        <v>2.3615</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1415</v>
+        <v>0.1038</v>
       </c>
       <c r="K14" t="n">
         <v>81</v>
@@ -1081,7 +1081,7 @@
         <v>44</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5725</v>
+        <v>2.4653</v>
       </c>
       <c r="N14" t="n">
         <v>125</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5028</v>
+        <v>2.4558</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0117</v>
+        <v>0.9927</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5041</v>
+        <v>0.5129</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5028</v>
+        <v>2.4558</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6835</v>
+        <v>1.7121</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.5014</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6835</v>
+        <v>1.7121</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7269</v>
+        <v>1.7579</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.5014</v>
       </c>
       <c r="K15" t="n">
         <v>116</v>
@@ -1127,7 +1127,7 @@
         <v>59</v>
       </c>
       <c r="M15" t="n">
-        <v>2.304</v>
+        <v>2.2593</v>
       </c>
       <c r="N15" t="n">
         <v>175</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2426</v>
+        <v>2.2856</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9065</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3879</v>
+        <v>0.4354</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2426</v>
+        <v>2.2856</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1687</v>
+        <v>0.5551</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9862</v>
+        <v>1.5974</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1687</v>
+        <v>0.5551</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1988</v>
+        <v>0.5551</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9862</v>
+        <v>1.5974</v>
       </c>
       <c r="K16" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="L16" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="M16" t="n">
-        <v>2.185</v>
+        <v>2.1525</v>
       </c>
       <c r="N16" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1914</v>
+        <v>2.0827</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8858</v>
+        <v>0.8419</v>
       </c>
       <c r="D17" t="n">
-        <v>0.365</v>
+        <v>0.343</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1914</v>
+        <v>2.0827</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4348</v>
+        <v>1.0835</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6235</v>
+        <v>0.9115</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4348</v>
+        <v>1.0835</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4348</v>
+        <v>1.1125</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6235</v>
+        <v>0.9115</v>
       </c>
       <c r="K17" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="L17" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0583</v>
+        <v>2.024</v>
       </c>
       <c r="N17" t="n">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0404</v>
+        <v>2.0571</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8248</v>
+        <v>0.8316</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2976</v>
+        <v>0.3313</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0404</v>
+        <v>2.0571</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5419</v>
+        <v>2.5676</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4098</v>
+        <v>-0.4188</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4925</v>
+        <v>3.1972</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8859</v>
+        <v>1.7951</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4098</v>
+        <v>-0.4188</v>
       </c>
       <c r="K18" t="n">
         <v>99</v>
@@ -1265,7 +1265,7 @@
         <v>148</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4761</v>
+        <v>1.3763</v>
       </c>
       <c r="N18" t="n">
         <v>247</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8967</v>
+        <v>1.9435</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7667</v>
+        <v>0.7856</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2334</v>
+        <v>0.2796</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8967</v>
+        <v>1.9435</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4242</v>
+        <v>2.397</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3717</v>
+        <v>-0.2977</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5809</v>
+        <v>2.543</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6474</v>
+        <v>2.611</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3717</v>
+        <v>-0.2977</v>
       </c>
       <c r="K19" t="n">
         <v>122</v>
@@ -1311,7 +1311,7 @@
         <v>127</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2757</v>
+        <v>2.3133</v>
       </c>
       <c r="N19" t="n">
         <v>249</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5444</v>
+        <v>1.4535</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6243</v>
+        <v>0.5876</v>
       </c>
       <c r="D20" t="n">
-        <v>0.076</v>
+        <v>0.0564</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5444</v>
+        <v>1.4535</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8283</v>
+        <v>0.8223</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6062</v>
+        <v>0.5213</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8283</v>
+        <v>0.8223</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8283</v>
+        <v>0.8223</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6062</v>
+        <v>0.5213</v>
       </c>
       <c r="K20" t="n">
         <v>106</v>
@@ -1357,7 +1357,7 @@
         <v>84</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4345</v>
+        <v>1.3436</v>
       </c>
       <c r="N20" t="n">
         <v>190</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4837</v>
+        <v>1.4243</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5998</v>
+        <v>0.5758</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0489</v>
+        <v>0.043</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4837</v>
+        <v>1.4243</v>
       </c>
       <c r="F21" t="n">
-        <v>1.241</v>
+        <v>1.1816</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.241</v>
+        <v>1.1816</v>
       </c>
       <c r="I21" t="n">
-        <v>1.241</v>
+        <v>1.1816</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.241</v>
+        <v>1.1816</v>
       </c>
       <c r="N21" t="n">
         <v>115</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2126</v>
+        <v>1.0929</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4902</v>
+        <v>0.4418</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0722</v>
+        <v>-0.1079</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2126</v>
+        <v>1.0929</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1471</v>
+        <v>-0.1801</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4308</v>
+        <v>1.344</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1471</v>
+        <v>-0.1801</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1509</v>
+        <v>-0.1849</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4308</v>
+        <v>1.344</v>
       </c>
       <c r="K22" t="n">
         <v>122</v>
@@ -1449,7 +1449,7 @@
         <v>127</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2799</v>
+        <v>1.1591</v>
       </c>
       <c r="N22" t="n">
         <v>249</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1397</v>
+        <v>1.0825</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4607</v>
+        <v>0.4376</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1047</v>
+        <v>-0.1127</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1397</v>
+        <v>1.0825</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2198</v>
+        <v>1.2072</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0392</v>
+        <v>-0.0838</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2198</v>
+        <v>1.2072</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6587</v>
+        <v>0.6778</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0392</v>
+        <v>-0.0838</v>
       </c>
       <c r="K23" t="n">
         <v>109</v>
@@ -1495,7 +1495,7 @@
         <v>120</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6194999999999999</v>
+        <v>0.594</v>
       </c>
       <c r="N23" t="n">
         <v>229</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0903</v>
+        <v>1.0387</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4407</v>
+        <v>0.4199</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1268</v>
+        <v>-0.1326</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0903</v>
+        <v>1.0387</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9686</v>
+        <v>0.917</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9686</v>
+        <v>0.917</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9686</v>
+        <v>0.917</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9686</v>
+        <v>0.917</v>
       </c>
       <c r="N24" t="n">
         <v>88</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.989</v>
+        <v>0.9447</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3998</v>
+        <v>0.3819</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1721</v>
+        <v>-0.1754</v>
       </c>
       <c r="E25" t="n">
-        <v>0.989</v>
+        <v>0.9447</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>115</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9562</v>
+        <v>0.853</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3865</v>
+        <v>0.3448</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1867</v>
+        <v>-0.2172</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9562</v>
+        <v>0.853</v>
       </c>
       <c r="F26" t="n">
-        <v>1.7509</v>
+        <v>1.6238</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6945</v>
+        <v>-0.6706</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7509</v>
+        <v>1.6238</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7509</v>
+        <v>1.6238</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6945</v>
+        <v>-0.6706</v>
       </c>
       <c r="K26" t="n">
         <v>81</v>
@@ -1633,7 +1633,7 @@
         <v>44</v>
       </c>
       <c r="M26" t="n">
-        <v>1.0564</v>
+        <v>0.9531999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>125</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7901</v>
+        <v>0.8391</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3194</v>
+        <v>0.3392</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2609</v>
+        <v>-0.2235</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7901</v>
+        <v>0.8391</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1028</v>
+        <v>1.1225</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2828</v>
+        <v>-0.2535</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1028</v>
+        <v>1.1225</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1028</v>
+        <v>1.1225</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.2828</v>
+        <v>-0.2535</v>
       </c>
       <c r="K27" t="n">
         <v>81</v>
@@ -1679,7 +1679,7 @@
         <v>44</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8200000000000001</v>
+        <v>0.869</v>
       </c>
       <c r="N27" t="n">
         <v>125</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.751</v>
+        <v>0.68</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3036</v>
+        <v>0.2749</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2784</v>
+        <v>-0.296</v>
       </c>
       <c r="E28" t="n">
-        <v>0.751</v>
+        <v>0.68</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4477</v>
+        <v>0.4065</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2754</v>
+        <v>0.2456</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4477</v>
+        <v>0.4065</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4477</v>
+        <v>0.4065</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2754</v>
+        <v>0.2456</v>
       </c>
       <c r="K28" t="n">
         <v>106</v>
@@ -1725,7 +1725,7 @@
         <v>84</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7231</v>
+        <v>0.6521</v>
       </c>
       <c r="N28" t="n">
         <v>190</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6133</v>
+        <v>0.5321</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2479</v>
+        <v>0.2151</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3399</v>
+        <v>-0.3634</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6133</v>
+        <v>0.5321</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9516</v>
+        <v>0.8373</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2668</v>
+        <v>-0.2337</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9516</v>
+        <v>0.8373</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9516</v>
+        <v>0.8373</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2668</v>
+        <v>-0.2337</v>
       </c>
       <c r="K29" t="n">
         <v>81</v>
@@ -1771,7 +1771,7 @@
         <v>44</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6848000000000001</v>
+        <v>0.6036</v>
       </c>
       <c r="N29" t="n">
         <v>125</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3432</v>
+        <v>0.3752</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1387</v>
+        <v>0.1517</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4605</v>
+        <v>-0.4349</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3432</v>
+        <v>0.3752</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7302</v>
+        <v>0.7563</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4001</v>
+        <v>-0.3942</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7302</v>
+        <v>0.7563</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7302</v>
+        <v>0.7563</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4001</v>
+        <v>-0.3942</v>
       </c>
       <c r="K30" t="n">
         <v>106</v>
@@ -1817,7 +1817,7 @@
         <v>84</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3300999999999999</v>
+        <v>0.3621</v>
       </c>
       <c r="N30" t="n">
         <v>190</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0993</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0401</v>
+        <v>0.0344</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5695</v>
+        <v>-0.5671</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0993</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1213</v>
+        <v>1.5915</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-1.4315</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1213</v>
+        <v>1.5915</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1213</v>
+        <v>1.634</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-1.4315</v>
       </c>
       <c r="K31" t="n">
-        <v>57</v>
+        <v>122</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1213</v>
+        <v>0.2024999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>57</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0577</v>
+        <v>-0.0188</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0233</v>
+        <v>-0.0076</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.588</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0577</v>
+        <v>-0.0188</v>
       </c>
       <c r="F32" t="n">
-        <v>1.6239</v>
+        <v>0.0032</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.4912</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.6239</v>
+        <v>0.0032</v>
       </c>
       <c r="I32" t="n">
-        <v>1.6657</v>
+        <v>0.0032</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.4912</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="L32" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1744999999999999</v>
+        <v>0.0032</v>
       </c>
       <c r="N32" t="n">
-        <v>249</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6069</v>
+        <v>-0.6175</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2453</v>
+        <v>-0.2496</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8849</v>
+        <v>-0.8871</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6069</v>
+        <v>-0.6175</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5587</v>
+        <v>-0.5693</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5587</v>
+        <v>-0.5693</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5587</v>
+        <v>-0.5693</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5587</v>
+        <v>-0.5693</v>
       </c>
       <c r="N33" t="n">
         <v>88</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7164</v>
+        <v>-0.7473</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2896</v>
+        <v>-0.3021</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9338</v>
+        <v>-0.9462</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7164</v>
+        <v>-0.7473</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6761</v>
+        <v>-0.707</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6761</v>
+        <v>-0.707</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6761</v>
+        <v>-0.707</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6761</v>
+        <v>-0.707</v>
       </c>
       <c r="N34" t="n">
         <v>115</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.766</v>
+        <v>-0.7746</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3096</v>
+        <v>-0.3131</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.956</v>
+        <v>-0.9587</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.766</v>
+        <v>-0.7746</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7751</v>
+        <v>-0.7837</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7751</v>
+        <v>-0.7837</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7751</v>
+        <v>-0.7837</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7751</v>
+        <v>-0.7837</v>
       </c>
       <c r="N35" t="n">
         <v>88</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>MUTiRiS</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2014</v>
+        <v>-1.2085</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4856</v>
+        <v>-0.4885</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1505</v>
+        <v>-1.1563</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2014</v>
+        <v>-1.2085</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4782</v>
+        <v>-1.2051</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.5044</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4782</v>
+        <v>-1.2051</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4782</v>
+        <v>-1.2051</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.5044</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="L36" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9825999999999999</v>
+        <v>-1.2051</v>
       </c>
       <c r="N36" t="n">
-        <v>190</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MUTiRiS</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2644</v>
+        <v>-1.2097</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5111</v>
+        <v>-0.489</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1786</v>
+        <v>-1.1569</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2644</v>
+        <v>-1.2097</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.261</v>
+        <v>-0.4621</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.5288</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.261</v>
+        <v>-0.4621</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.261</v>
+        <v>-0.4621</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.5288</v>
       </c>
       <c r="K37" t="n">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.261</v>
+        <v>-0.9909000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>88</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3931</v>
+        <v>-1.371</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5631</v>
+        <v>-0.5542</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2361</v>
+        <v>-1.2303</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3931</v>
+        <v>-1.371</v>
       </c>
       <c r="F38" t="n">
-        <v>-1</v>
+        <v>-0.9779</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1</v>
+        <v>-0.9779</v>
       </c>
       <c r="I38" t="n">
-        <v>-1</v>
+        <v>-0.9779</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1</v>
+        <v>-0.9779</v>
       </c>
       <c r="N38" t="n">
         <v>58</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6813</v>
+        <v>-1.629</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6796</v>
+        <v>-0.6585</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3648</v>
+        <v>-1.3479</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6813</v>
+        <v>-1.629</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3316</v>
+        <v>-1.2793</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3316</v>
+        <v>-1.2793</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.3316</v>
+        <v>-1.2793</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3316</v>
+        <v>-1.2793</v>
       </c>
       <c r="N39" t="n">
         <v>88</v>
@@ -2250,7 +2250,7 @@
         <v>-1.0077</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.7273</v>
+        <v>-1.7414</v>
       </c>
       <c r="E40" t="n">
         <v>-2.4928</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.7704</v>
+        <v>-2.6953</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.1199</v>
+        <v>-1.0895</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8513</v>
+        <v>-1.8336</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.7704</v>
+        <v>-2.6953</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.1698</v>
+        <v>-1.1253</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.2927</v>
+        <v>-1.2621</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.1698</v>
+        <v>-1.1253</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6317</v>
+        <v>-0.6318</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.2927</v>
+        <v>-1.2621</v>
       </c>
       <c r="K41" t="n">
         <v>99</v>
@@ -2323,7 +2323,7 @@
         <v>148</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.9244</v>
+        <v>-1.8939</v>
       </c>
       <c r="N41" t="n">
         <v>247</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.8221</v>
+        <v>-2.8329</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.1408</v>
+        <v>-1.1452</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.8744</v>
+        <v>-1.8963</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.8221</v>
+        <v>-2.8329</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.4146</v>
+        <v>-1.4254</v>
       </c>
       <c r="G42" t="n">
         <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.4146</v>
+        <v>-1.4254</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.4511</v>
+        <v>-1.4635</v>
       </c>
       <c r="J42" t="n">
         <v>-1</v>
@@ -2369,7 +2369,7 @@
         <v>59</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.4511</v>
+        <v>-2.4635</v>
       </c>
       <c r="N42" t="n">
         <v>175</v>
@@ -2475,10 +2475,10 @@
         <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>1.09</v>
+        <v>1.092</v>
       </c>
       <c r="J2" t="n">
-        <v>23.98</v>
+        <v>24.024</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>1.36</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8629</v>
+        <v>0.8445</v>
       </c>
       <c r="J3" t="n">
-        <v>18.9838</v>
+        <v>18.579</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>1.32</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7847</v>
+        <v>0.7613</v>
       </c>
       <c r="J4" t="n">
-        <v>17.2634</v>
+        <v>16.7486</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>1.25</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>14.1834</v>
+        <v>13.5388</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5865</v>
+        <v>-0.5518</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.903</v>
+        <v>-12.1396</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.13</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3444</v>
+        <v>0.2934</v>
       </c>
       <c r="J7" t="n">
-        <v>7.5768</v>
+        <v>6.4548</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1992</v>
+        <v>0.159</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3824</v>
+        <v>3.498</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.159</v>
+        <v>-0.1415</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.498</v>
+        <v>-3.113</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>0.72</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3161</v>
+        <v>-0.299</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.9542</v>
+        <v>-6.578</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>0.54</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4775</v>
+        <v>-0.4745</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.505</v>
+        <v>-10.439</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.57</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2796</v>
+        <v>1.3063</v>
       </c>
       <c r="J12" t="n">
-        <v>28.1512</v>
+        <v>28.7386</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>1.4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9591</v>
+        <v>0.9467</v>
       </c>
       <c r="J13" t="n">
-        <v>21.1002</v>
+        <v>20.8274</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>1.31</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7803</v>
+        <v>0.7536</v>
       </c>
       <c r="J14" t="n">
-        <v>17.1666</v>
+        <v>16.5792</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2617</v>
+        <v>-0.223</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.7574</v>
+        <v>-4.906</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.61</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0251</v>
+        <v>-1.0293</v>
       </c>
       <c r="J16" t="n">
-        <v>-22.5522</v>
+        <v>-22.6446</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8309</v>
+        <v>0.7851</v>
       </c>
       <c r="J17" t="n">
-        <v>18.2798</v>
+        <v>17.2722</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.29</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5979</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>13.1538</v>
+        <v>11.8976</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>0.76</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2864</v>
+        <v>-0.2676</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.3008</v>
+        <v>-5.8872</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>0.68</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3611</v>
+        <v>-0.3469</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.9442</v>
+        <v>-7.6318</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4675</v>
+        <v>-0.4642</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.285</v>
+        <v>-10.2124</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2582</v>
+        <v>0.2543</v>
       </c>
       <c r="J22" t="n">
-        <v>4.3894</v>
+        <v>4.3231</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>0.99</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0106</v>
+        <v>0.0201</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1802</v>
+        <v>0.3417</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>0.65</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3673</v>
+        <v>-0.3538</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.2441</v>
+        <v>-6.0146</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>0.53</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4739</v>
+        <v>-0.4694</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.0563</v>
+        <v>-7.9798</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.48</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5175</v>
+        <v>-0.5184</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.797499999999999</v>
+        <v>-8.812799999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.86</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9353</v>
+        <v>0.8669</v>
       </c>
       <c r="J27" t="n">
-        <v>15.9001</v>
+        <v>14.7373</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>1.52</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6199</v>
+        <v>0.5506</v>
       </c>
       <c r="J28" t="n">
-        <v>10.5383</v>
+        <v>9.360200000000001</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>1.46</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5615</v>
+        <v>0.4946</v>
       </c>
       <c r="J29" t="n">
-        <v>9.545500000000001</v>
+        <v>8.408200000000001</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>1.13</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1941</v>
+        <v>0.1552</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2997</v>
+        <v>2.6384</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>1.05</v>
       </c>
       <c r="I31" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0525</v>
       </c>
       <c r="J31" t="n">
-        <v>1.2733</v>
+        <v>0.8925</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.74</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5508</v>
+        <v>1.5824</v>
       </c>
       <c r="J32" t="n">
-        <v>29.4652</v>
+        <v>30.0656</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.44</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0222</v>
+        <v>1.0167</v>
       </c>
       <c r="J33" t="n">
-        <v>19.4218</v>
+        <v>19.3173</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1966</v>
+        <v>0.1687</v>
       </c>
       <c r="J34" t="n">
-        <v>3.7354</v>
+        <v>3.2053</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>1.06</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1966</v>
+        <v>0.1687</v>
       </c>
       <c r="J35" t="n">
-        <v>3.7354</v>
+        <v>3.2053</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.79</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6512</v>
+        <v>-0.6194</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.3728</v>
+        <v>-11.7686</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.38</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7678</v>
+        <v>0.7238</v>
       </c>
       <c r="J37" t="n">
-        <v>14.5882</v>
+        <v>13.7522</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>0.78</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2604</v>
+        <v>-0.2412</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.9476</v>
+        <v>-4.5828</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>0.76</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2796</v>
+        <v>-0.2609</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.3124</v>
+        <v>-4.9571</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.75</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2891</v>
+        <v>-0.2708</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.4929</v>
+        <v>-5.1452</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.72</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3174</v>
+        <v>-0.3002</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.0306</v>
+        <v>-5.7038</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.71</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1953</v>
+        <v>1.1913</v>
       </c>
       <c r="J42" t="n">
-        <v>21.5154</v>
+        <v>21.4434</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.61</v>
       </c>
       <c r="I43" t="n">
-        <v>1.069</v>
+        <v>1.0599</v>
       </c>
       <c r="J43" t="n">
-        <v>19.242</v>
+        <v>19.0782</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.42</v>
       </c>
       <c r="I44" t="n">
-        <v>0.82</v>
+        <v>0.8092</v>
       </c>
       <c r="J44" t="n">
-        <v>14.76</v>
+        <v>14.5656</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>1.13</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3572</v>
+        <v>0.3251</v>
       </c>
       <c r="J45" t="n">
-        <v>6.4296</v>
+        <v>5.8518</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>1.04</v>
       </c>
       <c r="I46" t="n">
-        <v>0.108</v>
+        <v>0.083</v>
       </c>
       <c r="J46" t="n">
-        <v>1.944</v>
+        <v>1.494</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.24</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5974</v>
+        <v>0.5987</v>
       </c>
       <c r="J47" t="n">
-        <v>10.7532</v>
+        <v>10.7766</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>0.68</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.3326</v>
+        <v>-0.3203</v>
       </c>
       <c r="J48" t="n">
-        <v>-5.9868</v>
+        <v>-5.7654</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.68</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3326</v>
+        <v>-0.3203</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.9868</v>
+        <v>-5.7654</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.45</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5339</v>
+        <v>-0.5363</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.610200000000001</v>
+        <v>-9.6534</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.3</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6641</v>
+        <v>-0.6882</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.9538</v>
+        <v>-12.3876</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.29</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6784</v>
+        <v>0.6632</v>
       </c>
       <c r="J52" t="n">
-        <v>14.9248</v>
+        <v>14.5904</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>1.13</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4024</v>
+        <v>0.362</v>
       </c>
       <c r="J53" t="n">
-        <v>8.8528</v>
+        <v>7.964</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>1.08</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2748</v>
+        <v>0.2387</v>
       </c>
       <c r="J54" t="n">
-        <v>6.0456</v>
+        <v>5.2514</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0111</v>
+        <v>-0.0073</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.2442</v>
+        <v>-0.1606</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.87</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4343</v>
+        <v>-0.3914</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.554600000000001</v>
+        <v>-8.610799999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.05</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1868</v>
+        <v>0.1497</v>
       </c>
       <c r="J57" t="n">
-        <v>4.1096</v>
+        <v>3.2934</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>0.9</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1332</v>
+        <v>-0.1176</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.9304</v>
+        <v>-2.5872</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>0.88</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1557</v>
+        <v>-0.1393</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.4254</v>
+        <v>-3.0646</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>0.73</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.303</v>
+        <v>-0.2856</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.666</v>
+        <v>-6.2832</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.59</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4301</v>
+        <v>-0.4214</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.462199999999999</v>
+        <v>-9.270799999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.31</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4647</v>
+        <v>0.4796</v>
       </c>
       <c r="J62" t="n">
-        <v>11.1528</v>
+        <v>11.5104</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2807</v>
+        <v>0.2675</v>
       </c>
       <c r="J63" t="n">
-        <v>6.7368</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>0.97</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0602</v>
+        <v>-0.0471</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.4448</v>
+        <v>-1.1304</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1013</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.4312</v>
+        <v>-2.016</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.76</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2939</v>
+        <v>-0.2758</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.0536</v>
+        <v>-6.6192</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.34</v>
       </c>
       <c r="I67" t="n">
-        <v>0.458</v>
+        <v>0.3986</v>
       </c>
       <c r="J67" t="n">
-        <v>10.992</v>
+        <v>9.5664</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.31</v>
       </c>
       <c r="I68" t="n">
-        <v>0.43</v>
+        <v>0.367</v>
       </c>
       <c r="J68" t="n">
-        <v>10.32</v>
+        <v>8.808</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>1.12</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2031</v>
+        <v>0.161</v>
       </c>
       <c r="J69" t="n">
-        <v>4.8744</v>
+        <v>3.864</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>0.99</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0352</v>
+        <v>-0.026</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.8448</v>
+        <v>-0.624</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.92</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1349</v>
+        <v>-0.1157</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.2376</v>
+        <v>-2.7768</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>1.64</v>
       </c>
       <c r="I72" t="n">
-        <v>1.161</v>
+        <v>1.1581</v>
       </c>
       <c r="J72" t="n">
-        <v>25.542</v>
+        <v>25.4782</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>1.25</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6027</v>
+        <v>0.591</v>
       </c>
       <c r="J73" t="n">
-        <v>13.2594</v>
+        <v>13.002</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4369</v>
+        <v>0.4025</v>
       </c>
       <c r="J74" t="n">
-        <v>9.611800000000001</v>
+        <v>8.855</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0236</v>
+        <v>-0.0183</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.5192</v>
+        <v>-0.4026</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.878</v>
+        <v>-0.864</v>
       </c>
       <c r="J76" t="n">
-        <v>-19.316</v>
+        <v>-19.008</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>1.26</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5152</v>
+        <v>0.4831</v>
       </c>
       <c r="J77" t="n">
-        <v>11.3344</v>
+        <v>10.6282</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>1.02</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0776</v>
+        <v>0.0551</v>
       </c>
       <c r="J78" t="n">
-        <v>1.7072</v>
+        <v>1.2122</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0033</v>
+        <v>0.0016</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0726</v>
+        <v>0.0352</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1665</v>
+        <v>-0.1465</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.663</v>
+        <v>-3.223</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.68</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3631</v>
+        <v>-0.3493</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.9882</v>
+        <v>-7.6846</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.75</v>
       </c>
       <c r="I82" t="n">
-        <v>1.2985</v>
+        <v>1.3055</v>
       </c>
       <c r="J82" t="n">
-        <v>28.567</v>
+        <v>28.721</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6148</v>
+        <v>0.6032</v>
       </c>
       <c r="J83" t="n">
-        <v>13.5256</v>
+        <v>13.2704</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>1.23</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5679</v>
+        <v>0.5587</v>
       </c>
       <c r="J84" t="n">
-        <v>12.4938</v>
+        <v>12.2914</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>0.83</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5498</v>
+        <v>-0.5113</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.0956</v>
+        <v>-11.2486</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6878</v>
+        <v>-0.6573</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.1316</v>
+        <v>-14.4606</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3845</v>
+        <v>0.3288</v>
       </c>
       <c r="J87" t="n">
-        <v>8.459</v>
+        <v>7.2336</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3305</v>
+        <v>0.2778</v>
       </c>
       <c r="J88" t="n">
-        <v>7.271</v>
+        <v>6.1116</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>0.9</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1459</v>
+        <v>-0.1264</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.2098</v>
+        <v>-2.7808</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1791</v>
+        <v>-0.1587</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.9402</v>
+        <v>-3.4914</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.86</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1898</v>
+        <v>-0.1693</v>
       </c>
       <c r="J91" t="n">
-        <v>-4.1756</v>
+        <v>-3.7246</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.34</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6049</v>
+        <v>0.5773</v>
       </c>
       <c r="J92" t="n">
-        <v>12.7029</v>
+        <v>12.1233</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>1.18</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4019</v>
+        <v>0.3457</v>
       </c>
       <c r="J93" t="n">
-        <v>8.4399</v>
+        <v>7.2597</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.042</v>
+        <v>-0.0321</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.882</v>
+        <v>-0.6741</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>0.86</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1898</v>
+        <v>-0.1693</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.9858</v>
+        <v>-3.5553</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>0.58</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4537</v>
+        <v>-0.4492</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.527699999999999</v>
+        <v>-9.433199999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.51</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9819</v>
+        <v>0.9692</v>
       </c>
       <c r="J97" t="n">
-        <v>20.6199</v>
+        <v>20.3532</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>1.14</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4156</v>
+        <v>0.3795</v>
       </c>
       <c r="J98" t="n">
-        <v>8.727600000000001</v>
+        <v>7.9695</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>1.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2915</v>
+        <v>0.2581</v>
       </c>
       <c r="J99" t="n">
-        <v>6.1215</v>
+        <v>5.4201</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>1.04</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1461</v>
+        <v>0.1217</v>
       </c>
       <c r="J100" t="n">
-        <v>3.0681</v>
+        <v>2.5557</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.98</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1263</v>
+        <v>-0.099</v>
       </c>
       <c r="J101" t="n">
-        <v>-2.6523</v>
+        <v>-2.079</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.06</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1958</v>
+        <v>0.1557</v>
       </c>
       <c r="J102" t="n">
-        <v>4.5034</v>
+        <v>3.5811</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.077</v>
+        <v>-0.0644</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.771</v>
+        <v>-1.4812</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>0.8</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2408</v>
+        <v>-0.2214</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.5384</v>
+        <v>-5.0922</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>0.8</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2408</v>
+        <v>-0.2214</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.5384</v>
+        <v>-5.0922</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.78</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2604</v>
+        <v>-0.2412</v>
       </c>
       <c r="J106" t="n">
-        <v>-5.9892</v>
+        <v>-5.5476</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.31</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6933</v>
+        <v>0.6786</v>
       </c>
       <c r="J107" t="n">
-        <v>15.9459</v>
+        <v>15.6078</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>1.21</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5377</v>
+        <v>0.5284</v>
       </c>
       <c r="J108" t="n">
-        <v>12.3671</v>
+        <v>12.1532</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>1.17</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4722</v>
+        <v>0.4471</v>
       </c>
       <c r="J109" t="n">
-        <v>10.8606</v>
+        <v>10.2833</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1774</v>
+        <v>0.1504</v>
       </c>
       <c r="J110" t="n">
-        <v>4.0802</v>
+        <v>3.4592</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>1.03</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1122</v>
+        <v>0.0912</v>
       </c>
       <c r="J111" t="n">
-        <v>2.5806</v>
+        <v>2.0976</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.74</v>
       </c>
       <c r="I112" t="n">
-        <v>0.72</v>
+        <v>0.6734</v>
       </c>
       <c r="J112" t="n">
-        <v>12.24</v>
+        <v>11.4478</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.68</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6795</v>
+        <v>0.6363</v>
       </c>
       <c r="J113" t="n">
-        <v>11.5515</v>
+        <v>10.8171</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>1.49</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5481</v>
+        <v>0.5153</v>
       </c>
       <c r="J114" t="n">
-        <v>9.3177</v>
+        <v>8.7601</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>1.39</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4761</v>
+        <v>0.4276</v>
       </c>
       <c r="J115" t="n">
-        <v>8.0937</v>
+        <v>7.2692</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>1.02</v>
       </c>
       <c r="I116" t="n">
-        <v>0.0142</v>
+        <v>0.0027</v>
       </c>
       <c r="J116" t="n">
-        <v>0.2414</v>
+        <v>0.0459</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.16</v>
       </c>
       <c r="I117" t="n">
-        <v>0.353</v>
+        <v>0.3593</v>
       </c>
       <c r="J117" t="n">
-        <v>6.001</v>
+        <v>6.1081</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>0.92</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.09669999999999999</v>
+        <v>-0.0823</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.6439</v>
+        <v>-1.3991</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.64</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3763</v>
+        <v>-0.3633</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.3971</v>
+        <v>-6.1761</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>0.55</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4563</v>
+        <v>-0.4499</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.7571</v>
+        <v>-7.6483</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.48</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5175</v>
+        <v>-0.5184</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.797499999999999</v>
+        <v>-8.812799999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.62</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9173</v>
+        <v>0.8868</v>
       </c>
       <c r="J122" t="n">
-        <v>21.0979</v>
+        <v>20.3964</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.16</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3729</v>
+        <v>0.3179</v>
       </c>
       <c r="J123" t="n">
-        <v>8.576700000000001</v>
+        <v>7.3117</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>0.86</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1875</v>
+        <v>-0.1672</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.3125</v>
+        <v>-3.8456</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>0.59</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4428</v>
+        <v>-0.4367</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.1844</v>
+        <v>-10.0441</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.58</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4515</v>
+        <v>-0.4464</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.3845</v>
+        <v>-10.2672</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.65</v>
       </c>
       <c r="I127" t="n">
-        <v>1.1554</v>
+        <v>1.1502</v>
       </c>
       <c r="J127" t="n">
-        <v>26.5742</v>
+        <v>26.4546</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.38</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7863</v>
+        <v>0.7711</v>
       </c>
       <c r="J128" t="n">
-        <v>18.0849</v>
+        <v>17.7353</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>1.33</v>
       </c>
       <c r="I129" t="n">
-        <v>0.7138</v>
+        <v>0.6998</v>
       </c>
       <c r="J129" t="n">
-        <v>16.4174</v>
+        <v>16.0954</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>0.96</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2075</v>
+        <v>-0.1733</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.7725</v>
+        <v>-3.9859</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.74</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7611</v>
+        <v>-0.7376</v>
       </c>
       <c r="J131" t="n">
-        <v>-17.5053</v>
+        <v>-16.9648</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.62</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9555</v>
+        <v>0.9363</v>
       </c>
       <c r="J132" t="n">
-        <v>18.1545</v>
+        <v>17.7897</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>0.96</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0617</v>
+        <v>-0.0507</v>
       </c>
       <c r="J133" t="n">
-        <v>-1.1723</v>
+        <v>-0.9633</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3439</v>
+        <v>-0.3283</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.5341</v>
+        <v>-6.2377</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>0.62</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4072</v>
+        <v>-0.3966</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.7368</v>
+        <v>-7.5354</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.44</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5631</v>
+        <v>-0.5722</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.6989</v>
+        <v>-10.8718</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>2.61</v>
       </c>
       <c r="I137" t="n">
-        <v>2.2262</v>
+        <v>2.3451</v>
       </c>
       <c r="J137" t="n">
-        <v>42.2978</v>
+        <v>44.5569</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.72</v>
       </c>
       <c r="I138" t="n">
-        <v>1.2</v>
+        <v>1.1967</v>
       </c>
       <c r="J138" t="n">
-        <v>22.8</v>
+        <v>22.7373</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1925</v>
+        <v>0.1617</v>
       </c>
       <c r="J139" t="n">
-        <v>3.6575</v>
+        <v>3.0723</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>0.87</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4923</v>
+        <v>-0.4593</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.3537</v>
+        <v>-8.726699999999999</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.86</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5171</v>
+        <v>-0.4848</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.8249</v>
+        <v>-9.2112</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.01</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1016</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>1.7272</v>
+        <v>1.428</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>0.87</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1572</v>
+        <v>-0.1417</v>
       </c>
       <c r="J143" t="n">
-        <v>-2.6724</v>
+        <v>-2.4089</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>0.77</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2594</v>
+        <v>-0.2433</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.4098</v>
+        <v>-4.1361</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.63</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3862</v>
+        <v>-0.3738</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.5654</v>
+        <v>-6.3546</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.51</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4923</v>
+        <v>-0.49</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.3691</v>
+        <v>-8.33</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>2.23</v>
       </c>
       <c r="I147" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J147" t="n">
-        <v>32.9324</v>
+        <v>33.6906</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.48</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0497</v>
+        <v>1.0582</v>
       </c>
       <c r="J148" t="n">
-        <v>17.8449</v>
+        <v>17.9894</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.21</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5465</v>
+        <v>0.5182</v>
       </c>
       <c r="J149" t="n">
-        <v>9.2905</v>
+        <v>8.8094</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>1.08</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2315</v>
+        <v>0.201</v>
       </c>
       <c r="J150" t="n">
-        <v>3.9355</v>
+        <v>3.417</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.77</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.6932</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.1754</v>
+        <v>-11.7844</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.17</v>
       </c>
       <c r="I152" t="n">
-        <v>0.385</v>
+        <v>0.3293</v>
       </c>
       <c r="J152" t="n">
-        <v>9.24</v>
+        <v>7.9032</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>0.96</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.0576</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.716</v>
+        <v>-1.3824</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>0.95</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0697</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.04</v>
+        <v>-1.6728</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0979</v>
+        <v>-0.0814</v>
       </c>
       <c r="J155" t="n">
-        <v>-2.3496</v>
+        <v>-1.9536</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>0.91</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1342</v>
+        <v>-0.1153</v>
       </c>
       <c r="J156" t="n">
-        <v>-3.2208</v>
+        <v>-2.7672</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8636</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>20.7264</v>
+        <v>20.2128</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4008</v>
+        <v>0.3607</v>
       </c>
       <c r="J158" t="n">
-        <v>9.619199999999999</v>
+        <v>8.6568</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4008</v>
+        <v>0.3607</v>
       </c>
       <c r="J159" t="n">
-        <v>9.619199999999999</v>
+        <v>8.6568</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>1.06</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2185</v>
+        <v>0.1865</v>
       </c>
       <c r="J160" t="n">
-        <v>5.244</v>
+        <v>4.476</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>0.76</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.695</v>
+        <v>-0.6629</v>
       </c>
       <c r="J161" t="n">
-        <v>-16.68</v>
+        <v>-15.9096</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.85</v>
       </c>
       <c r="I162" t="n">
-        <v>1.514</v>
+        <v>1.5467</v>
       </c>
       <c r="J162" t="n">
-        <v>25.738</v>
+        <v>26.2939</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>1.62</v>
       </c>
       <c r="I163" t="n">
-        <v>1.2284</v>
+        <v>1.2453</v>
       </c>
       <c r="J163" t="n">
-        <v>20.8828</v>
+        <v>21.1701</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>1.28</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6676</v>
       </c>
       <c r="J164" t="n">
-        <v>11.713</v>
+        <v>11.3492</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>1.17</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4519</v>
+        <v>0.4212</v>
       </c>
       <c r="J165" t="n">
-        <v>7.6823</v>
+        <v>7.1604</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>1.01</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.0042</v>
+        <v>-0.0164</v>
       </c>
       <c r="J166" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.2788</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.5</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9943</v>
+        <v>0.9916</v>
       </c>
       <c r="J167" t="n">
-        <v>16.9031</v>
+        <v>16.8572</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>0.85</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1844</v>
+        <v>-0.1679</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.1348</v>
+        <v>-2.8543</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.64</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3819</v>
+        <v>-0.369</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.4923</v>
+        <v>-6.273</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.58</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4354</v>
+        <v>-0.4271</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.4018</v>
+        <v>-7.2607</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.42</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.574</v>
+        <v>-0.5839</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.757999999999999</v>
+        <v>-9.926299999999999</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.39</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5829</v>
+        <v>0.6075</v>
       </c>
       <c r="J172" t="n">
-        <v>12.8238</v>
+        <v>13.365</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.03</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0809</v>
+        <v>0.0668</v>
       </c>
       <c r="J173" t="n">
-        <v>1.7798</v>
+        <v>1.4696</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>0.91</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1334</v>
+        <v>-0.1146</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.9348</v>
+        <v>-2.5212</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>0.87</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1781</v>
+        <v>-0.1578</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.9182</v>
+        <v>-3.4716</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3638</v>
+        <v>-0.3501</v>
       </c>
       <c r="J176" t="n">
-        <v>-8.0036</v>
+        <v>-7.7022</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>1.67</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8118</v>
+        <v>0.7441</v>
       </c>
       <c r="J177" t="n">
-        <v>17.8596</v>
+        <v>16.3702</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>1.31</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4343</v>
+        <v>0.369</v>
       </c>
       <c r="J178" t="n">
-        <v>9.554600000000001</v>
+        <v>8.118</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>1.02</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0448</v>
+        <v>0.0311</v>
       </c>
       <c r="J179" t="n">
-        <v>0.9856</v>
+        <v>0.6842</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>0.9</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1571</v>
+        <v>-0.1371</v>
       </c>
       <c r="J180" t="n">
-        <v>-3.4562</v>
+        <v>-3.0162</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.7</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3574</v>
+        <v>-0.3446</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.8628</v>
+        <v>-7.5812</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.49</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0721</v>
+        <v>1.0817</v>
       </c>
       <c r="J182" t="n">
-        <v>19.2978</v>
+        <v>19.4706</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9472</v>
+        <v>0.9386</v>
       </c>
       <c r="J183" t="n">
-        <v>17.0496</v>
+        <v>16.8948</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.32</v>
       </c>
       <c r="I184" t="n">
-        <v>0.7774</v>
+        <v>0.7564</v>
       </c>
       <c r="J184" t="n">
-        <v>13.9932</v>
+        <v>13.6152</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>1.26</v>
       </c>
       <c r="I185" t="n">
-        <v>0.66</v>
+        <v>0.6337</v>
       </c>
       <c r="J185" t="n">
-        <v>11.88</v>
+        <v>11.4066</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>1.01</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0097</v>
+        <v>-0.0009</v>
       </c>
       <c r="J186" t="n">
-        <v>0.1746</v>
+        <v>-0.0162</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.08</v>
       </c>
       <c r="I187" t="n">
-        <v>0.261</v>
+        <v>0.2181</v>
       </c>
       <c r="J187" t="n">
-        <v>4.698</v>
+        <v>3.9258</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>0.261</v>
+        <v>0.2181</v>
       </c>
       <c r="J188" t="n">
-        <v>4.698</v>
+        <v>3.9258</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>0.73</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3011</v>
+        <v>-0.2839</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.4198</v>
+        <v>-5.1102</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.71</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3197</v>
+        <v>-0.3031</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.7546</v>
+        <v>-5.4558</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.46</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5412</v>
+        <v>-0.5462</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.7416</v>
+        <v>-9.8316</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.19</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4818</v>
+        <v>0.4335</v>
       </c>
       <c r="J192" t="n">
-        <v>8.6724</v>
+        <v>7.803</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>0.84</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1952</v>
+        <v>-0.1784</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.5136</v>
+        <v>-3.2112</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>0.77</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2626</v>
+        <v>-0.2449</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.7268</v>
+        <v>-4.4082</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.337</v>
+        <v>-0.3213</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.066</v>
+        <v>-5.7834</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>0.52</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4884</v>
+        <v>-0.4861</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.7912</v>
+        <v>-8.7498</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.94</v>
       </c>
       <c r="I197" t="n">
-        <v>1.6243</v>
+        <v>1.6665</v>
       </c>
       <c r="J197" t="n">
-        <v>29.2374</v>
+        <v>29.997</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.53</v>
       </c>
       <c r="I198" t="n">
-        <v>1.1135</v>
+        <v>1.1277</v>
       </c>
       <c r="J198" t="n">
-        <v>20.043</v>
+        <v>20.2986</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>1.21</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5429</v>
+        <v>0.5149</v>
       </c>
       <c r="J199" t="n">
-        <v>9.7722</v>
+        <v>9.2682</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>1.14</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3822</v>
+        <v>0.3504</v>
       </c>
       <c r="J200" t="n">
-        <v>6.8796</v>
+        <v>6.3072</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>1.07</v>
       </c>
       <c r="I201" t="n">
-        <v>0.1997</v>
+        <v>0.1697</v>
       </c>
       <c r="J201" t="n">
-        <v>3.5946</v>
+        <v>3.0546</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>1.53</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6649</v>
+        <v>0.5934</v>
       </c>
       <c r="J202" t="n">
-        <v>14.6278</v>
+        <v>13.0548</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>1.43</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5609</v>
+        <v>0.4906</v>
       </c>
       <c r="J203" t="n">
-        <v>12.3398</v>
+        <v>10.7932</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>1.2</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3027</v>
+        <v>0.2485</v>
       </c>
       <c r="J204" t="n">
-        <v>6.6594</v>
+        <v>5.467</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>1.04</v>
       </c>
       <c r="I205" t="n">
-        <v>0.0805</v>
+        <v>0.059</v>
       </c>
       <c r="J205" t="n">
-        <v>1.771</v>
+        <v>1.298</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.54</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.499</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.978</v>
+        <v>-11.055</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.21</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3598</v>
+        <v>0.353</v>
       </c>
       <c r="J207" t="n">
-        <v>7.9156</v>
+        <v>7.766</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.2</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3464</v>
+        <v>0.3383</v>
       </c>
       <c r="J208" t="n">
-        <v>7.6208</v>
+        <v>7.4426</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>0.95</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0837</v>
+        <v>-0.0688</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.8414</v>
+        <v>-1.5136</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>0.82</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2293</v>
+        <v>-0.2089</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.0446</v>
+        <v>-4.5958</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.65</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.39</v>
+        <v>-0.3785</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.58</v>
+        <v>-8.327</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>1.24</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5395</v>
+        <v>0.4854</v>
       </c>
       <c r="J212" t="n">
-        <v>12.4085</v>
+        <v>11.1642</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>0.98</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0323</v>
+        <v>-0.0249</v>
       </c>
       <c r="J213" t="n">
-        <v>-0.7429</v>
+        <v>-0.5727</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2308</v>
+        <v>-0.2113</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.3084</v>
+        <v>-4.8599</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.72</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3172</v>
+        <v>-0.3</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.2956</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.63</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3993</v>
+        <v>-0.388</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.1839</v>
+        <v>-8.923999999999999</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.54</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1612</v>
+        <v>1.1748</v>
       </c>
       <c r="J217" t="n">
-        <v>26.7076</v>
+        <v>27.0204</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.39</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9327</v>
+        <v>0.919</v>
       </c>
       <c r="J218" t="n">
-        <v>21.4521</v>
+        <v>21.137</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>1.15</v>
       </c>
       <c r="I219" t="n">
-        <v>0.435</v>
+        <v>0.3999</v>
       </c>
       <c r="J219" t="n">
-        <v>10.005</v>
+        <v>9.197699999999999</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>1.05</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1712</v>
+        <v>0.1449</v>
       </c>
       <c r="J220" t="n">
-        <v>3.9376</v>
+        <v>3.3327</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>0.82</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5773</v>
+        <v>-0.5406</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.2779</v>
+        <v>-12.4338</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.06</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1858</v>
+        <v>0.1461</v>
       </c>
       <c r="J222" t="n">
-        <v>3.5302</v>
+        <v>2.7759</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>0.95</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0809</v>
+        <v>-0.0674</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.5371</v>
+        <v>-1.2806</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0791</v>
       </c>
       <c r="J224" t="n">
-        <v>-1.7822</v>
+        <v>-1.5029</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>0.89</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1514</v>
+        <v>-0.1328</v>
       </c>
       <c r="J225" t="n">
-        <v>-2.8766</v>
+        <v>-2.5232</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.75</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2932</v>
+        <v>-0.2748</v>
       </c>
       <c r="J226" t="n">
-        <v>-5.5708</v>
+        <v>-5.2212</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>1.53</v>
       </c>
       <c r="I227" t="n">
-        <v>1.132</v>
+        <v>1.1446</v>
       </c>
       <c r="J227" t="n">
-        <v>21.508</v>
+        <v>21.7474</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>1.35</v>
       </c>
       <c r="I228" t="n">
-        <v>0.8403</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="J228" t="n">
-        <v>15.9657</v>
+        <v>15.6009</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>1.24</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6229</v>
+        <v>0.5938</v>
       </c>
       <c r="J229" t="n">
-        <v>11.8351</v>
+        <v>11.2822</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>1.16</v>
       </c>
       <c r="I230" t="n">
-        <v>0.4474</v>
+        <v>0.415</v>
       </c>
       <c r="J230" t="n">
-        <v>8.5006</v>
+        <v>7.885</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>1.04</v>
       </c>
       <c r="I231" t="n">
-        <v>0.1269</v>
+        <v>0.1033</v>
       </c>
       <c r="J231" t="n">
-        <v>2.4111</v>
+        <v>1.9627</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>0.87</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.1366</v>
+        <v>-0.1192</v>
       </c>
       <c r="J232" t="n">
-        <v>-2.1856</v>
+        <v>-1.9072</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>0.71</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.3039</v>
+        <v>-0.2916</v>
       </c>
       <c r="J233" t="n">
-        <v>-4.8624</v>
+        <v>-4.6656</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>0.63</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3742</v>
+        <v>-0.3632</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.9872</v>
+        <v>-5.8112</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>0.61</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3916</v>
+        <v>-0.3813</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.2656</v>
+        <v>-6.1008</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.47</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5148</v>
+        <v>-0.5147</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.236800000000001</v>
+        <v>-8.235200000000001</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.8</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4305</v>
+        <v>1.4582</v>
       </c>
       <c r="J237" t="n">
-        <v>22.888</v>
+        <v>23.3312</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>1.73</v>
       </c>
       <c r="I238" t="n">
-        <v>1.3462</v>
+        <v>1.3699</v>
       </c>
       <c r="J238" t="n">
-        <v>21.5392</v>
+        <v>21.9184</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>1.66</v>
       </c>
       <c r="I239" t="n">
-        <v>1.2609</v>
+        <v>1.2815</v>
       </c>
       <c r="J239" t="n">
-        <v>20.1744</v>
+        <v>20.504</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>1.32</v>
       </c>
       <c r="I240" t="n">
-        <v>0.7514</v>
+        <v>0.7368</v>
       </c>
       <c r="J240" t="n">
-        <v>12.0224</v>
+        <v>11.7888</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>1.06</v>
       </c>
       <c r="I241" t="n">
-        <v>0.151</v>
+        <v>0.1194</v>
       </c>
       <c r="J241" t="n">
-        <v>2.416</v>
+        <v>1.9104</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.09</v>
       </c>
       <c r="I242" t="n">
-        <v>0.202</v>
+        <v>0.1859</v>
       </c>
       <c r="J242" t="n">
-        <v>4.242</v>
+        <v>3.9039</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.03</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0945</v>
+        <v>0.0795</v>
       </c>
       <c r="J243" t="n">
-        <v>1.9845</v>
+        <v>1.6695</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>0.89</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1496</v>
+        <v>-0.1319</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.1416</v>
+        <v>-2.7699</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>0.72</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3184</v>
+        <v>-0.3013</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.6864</v>
+        <v>-6.3273</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.71</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3277</v>
+        <v>-0.3111</v>
       </c>
       <c r="J246" t="n">
-        <v>-6.8817</v>
+        <v>-6.5331</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>2.06</v>
       </c>
       <c r="I247" t="n">
-        <v>1.1158</v>
+        <v>1.0865</v>
       </c>
       <c r="J247" t="n">
-        <v>23.4318</v>
+        <v>22.8165</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>1.51</v>
       </c>
       <c r="I248" t="n">
-        <v>0.6331</v>
+        <v>0.5613</v>
       </c>
       <c r="J248" t="n">
-        <v>13.2951</v>
+        <v>11.7873</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>1.19</v>
       </c>
       <c r="I249" t="n">
-        <v>0.2866</v>
+        <v>0.2358</v>
       </c>
       <c r="J249" t="n">
-        <v>6.0186</v>
+        <v>4.9518</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>0.7</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.364</v>
+        <v>-0.3529</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.644</v>
+        <v>-7.4109</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.61</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4434</v>
+        <v>-0.4407</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.311400000000001</v>
+        <v>-9.2547</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.62</v>
       </c>
       <c r="I252" t="n">
-        <v>1.232</v>
+        <v>1.2487</v>
       </c>
       <c r="J252" t="n">
-        <v>24.64</v>
+        <v>24.974</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1.49</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0623</v>
+        <v>1.0726</v>
       </c>
       <c r="J253" t="n">
-        <v>21.246</v>
+        <v>21.452</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>1.32</v>
       </c>
       <c r="I254" t="n">
-        <v>0.7713</v>
+        <v>0.7532</v>
       </c>
       <c r="J254" t="n">
-        <v>15.426</v>
+        <v>15.064</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>1.24</v>
       </c>
       <c r="I255" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.5837</v>
       </c>
       <c r="J255" t="n">
-        <v>12.188</v>
+        <v>11.674</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>1.15</v>
       </c>
       <c r="I256" t="n">
-        <v>0.4084</v>
+        <v>0.3768</v>
       </c>
       <c r="J256" t="n">
-        <v>8.167999999999999</v>
+        <v>7.536</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>0.99</v>
       </c>
       <c r="I257" t="n">
-        <v>0.012</v>
+        <v>0.0211</v>
       </c>
       <c r="J257" t="n">
-        <v>0.24</v>
+        <v>0.422</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>0.8</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2302</v>
+        <v>-0.2143</v>
       </c>
       <c r="J258" t="n">
-        <v>-4.604</v>
+        <v>-4.286</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>0.75</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2771</v>
+        <v>-0.2611</v>
       </c>
       <c r="J259" t="n">
-        <v>-5.542</v>
+        <v>-5.222</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>0.64</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3768</v>
+        <v>-0.3638</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.536</v>
+        <v>-7.276</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.59</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4214</v>
+        <v>-0.4117</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.428000000000001</v>
+        <v>-8.234</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.99</v>
       </c>
       <c r="I262" t="n">
-        <v>1.6587</v>
+        <v>1.7026</v>
       </c>
       <c r="J262" t="n">
-        <v>28.1979</v>
+        <v>28.9442</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>1.89</v>
       </c>
       <c r="I263" t="n">
-        <v>1.5415</v>
+        <v>1.576</v>
       </c>
       <c r="J263" t="n">
-        <v>26.2055</v>
+        <v>26.792</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>1.34</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7938</v>
+        <v>0.7816</v>
       </c>
       <c r="J264" t="n">
-        <v>13.4946</v>
+        <v>13.2872</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>1.32</v>
       </c>
       <c r="I265" t="n">
-        <v>0.7547</v>
+        <v>0.7398</v>
       </c>
       <c r="J265" t="n">
-        <v>12.8299</v>
+        <v>12.5766</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.91</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.397</v>
+        <v>-0.365</v>
       </c>
       <c r="J266" t="n">
-        <v>-6.749</v>
+        <v>-6.205</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>0.86</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.1558</v>
+        <v>-0.1397</v>
       </c>
       <c r="J267" t="n">
-        <v>-2.6486</v>
+        <v>-2.3749</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>0.83</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.189</v>
+        <v>-0.1734</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.213</v>
+        <v>-2.9478</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>0.78</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.241</v>
+        <v>-0.2266</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.097</v>
+        <v>-3.8522</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.58</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4222</v>
+        <v>-0.413</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.1774</v>
+        <v>-7.021</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.4</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5799</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.8583</v>
+        <v>-10.0164</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>1.69</v>
       </c>
       <c r="I272" t="n">
-        <v>0.8047</v>
+        <v>0.7337</v>
       </c>
       <c r="J272" t="n">
-        <v>14.4846</v>
+        <v>13.2066</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>1.43</v>
       </c>
       <c r="I273" t="n">
-        <v>0.5468</v>
+        <v>0.4774</v>
       </c>
       <c r="J273" t="n">
-        <v>9.8424</v>
+        <v>8.5932</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>1.26</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3648</v>
+        <v>0.307</v>
       </c>
       <c r="J274" t="n">
-        <v>6.5664</v>
+        <v>5.526</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>0.96</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.0917</v>
+        <v>-0.0762</v>
       </c>
       <c r="J275" t="n">
-        <v>-1.6506</v>
+        <v>-1.3716</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.89</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.178</v>
+        <v>-0.1589</v>
       </c>
       <c r="J276" t="n">
-        <v>-3.204</v>
+        <v>-2.8602</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>0.96</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.0559</v>
+        <v>-0.0452</v>
       </c>
       <c r="J277" t="n">
-        <v>-1.0062</v>
+        <v>-0.8136</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>0.92</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.1087</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="J278" t="n">
-        <v>-1.9566</v>
+        <v>-1.6974</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>0.79</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2455</v>
+        <v>-0.2273</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.419</v>
+        <v>-4.0914</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>0.79</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2455</v>
+        <v>-0.2273</v>
       </c>
       <c r="J280" t="n">
-        <v>-4.419</v>
+        <v>-4.0914</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>0.66</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3668</v>
+        <v>-0.3527</v>
       </c>
       <c r="J281" t="n">
-        <v>-6.6024</v>
+        <v>-6.3486</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>1.32</v>
       </c>
       <c r="I282" t="n">
-        <v>0.6522</v>
+        <v>0.5977</v>
       </c>
       <c r="J282" t="n">
-        <v>15.6528</v>
+        <v>14.3448</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>1.17</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3999</v>
+        <v>0.3444</v>
       </c>
       <c r="J283" t="n">
-        <v>9.5976</v>
+        <v>8.265599999999999</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>0.91</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1297</v>
+        <v>-0.1121</v>
       </c>
       <c r="J284" t="n">
-        <v>-3.1128</v>
+        <v>-2.6904</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>0.71</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3317</v>
+        <v>-0.3154</v>
       </c>
       <c r="J285" t="n">
-        <v>-7.9608</v>
+        <v>-7.5696</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.53</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4918</v>
+        <v>-0.4914</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.8032</v>
+        <v>-11.7936</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1.52</v>
       </c>
       <c r="I287" t="n">
-        <v>1.124</v>
+        <v>1.1363</v>
       </c>
       <c r="J287" t="n">
-        <v>26.976</v>
+        <v>27.2712</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>1.45</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0252</v>
+        <v>1.0271</v>
       </c>
       <c r="J288" t="n">
-        <v>24.6048</v>
+        <v>24.6504</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>1.22</v>
       </c>
       <c r="I289" t="n">
-        <v>0.5843</v>
+        <v>0.5527</v>
       </c>
       <c r="J289" t="n">
-        <v>14.0232</v>
+        <v>13.2648</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>1.15</v>
       </c>
       <c r="I290" t="n">
-        <v>0.4283</v>
+        <v>0.395</v>
       </c>
       <c r="J290" t="n">
-        <v>10.2792</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>0.84</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5375</v>
+        <v>-0.5003</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.9</v>
+        <v>-12.0072</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.49</v>
       </c>
       <c r="I292" t="n">
-        <v>0.8995</v>
+        <v>0.8581</v>
       </c>
       <c r="J292" t="n">
-        <v>20.6885</v>
+        <v>19.7363</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>0.99</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.023</v>
+        <v>-0.017</v>
       </c>
       <c r="J293" t="n">
-        <v>-0.529</v>
+        <v>-0.391</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>0.97</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.0561</v>
+        <v>-0.0446</v>
       </c>
       <c r="J294" t="n">
-        <v>-1.2903</v>
+        <v>-1.0258</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.96</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.0701</v>
+        <v>-0.0569</v>
       </c>
       <c r="J295" t="n">
-        <v>-1.6123</v>
+        <v>-1.3087</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.39</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6116</v>
+        <v>-0.6303</v>
       </c>
       <c r="J296" t="n">
-        <v>-14.0668</v>
+        <v>-14.4969</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>1.76</v>
       </c>
       <c r="I297" t="n">
-        <v>1.46</v>
+        <v>1.4941</v>
       </c>
       <c r="J297" t="n">
-        <v>33.58</v>
+        <v>34.3643</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.17</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4831</v>
+        <v>0.4466</v>
       </c>
       <c r="J298" t="n">
-        <v>11.1113</v>
+        <v>10.2718</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.12</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3666</v>
+        <v>0.3313</v>
       </c>
       <c r="J299" t="n">
-        <v>8.431800000000001</v>
+        <v>7.6199</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>0.99</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.066</v>
       </c>
       <c r="J300" t="n">
-        <v>-2.001</v>
+        <v>-1.518</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>0.78</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6647</v>
+        <v>-0.6324</v>
       </c>
       <c r="J301" t="n">
-        <v>-15.2881</v>
+        <v>-14.5452</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>1.32</v>
       </c>
       <c r="I302" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.7774</v>
       </c>
       <c r="J302" t="n">
-        <v>19.2696</v>
+        <v>18.6576</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>1.31</v>
       </c>
       <c r="I303" t="n">
-        <v>0.7826</v>
+        <v>0.7557</v>
       </c>
       <c r="J303" t="n">
-        <v>18.7824</v>
+        <v>18.1368</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>1.29</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7416</v>
+        <v>0.7123</v>
       </c>
       <c r="J304" t="n">
-        <v>17.7984</v>
+        <v>17.0952</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>0.96</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1975</v>
+        <v>-0.1628</v>
       </c>
       <c r="J305" t="n">
-        <v>-4.74</v>
+        <v>-3.9072</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>0.9</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3722</v>
+        <v>-0.3304</v>
       </c>
       <c r="J306" t="n">
-        <v>-8.9328</v>
+        <v>-7.9296</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>1.32</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6178</v>
+        <v>0.5584</v>
       </c>
       <c r="J307" t="n">
-        <v>14.8272</v>
+        <v>13.4016</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>1.1</v>
       </c>
       <c r="I308" t="n">
-        <v>0.246</v>
+        <v>0.2009</v>
       </c>
       <c r="J308" t="n">
-        <v>5.904</v>
+        <v>4.8216</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>1.08</v>
       </c>
       <c r="I309" t="n">
-        <v>0.2065</v>
+        <v>0.1658</v>
       </c>
       <c r="J309" t="n">
-        <v>4.956</v>
+        <v>3.9792</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>1.05</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1431</v>
+        <v>0.111</v>
       </c>
       <c r="J310" t="n">
-        <v>3.4344</v>
+        <v>2.664</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.65</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3963</v>
+        <v>-0.3862</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.511200000000001</v>
+        <v>-9.268800000000001</v>
       </c>
     </row>
     <row r="312">
@@ -14875,10 +14875,10 @@
         <v>1.77</v>
       </c>
       <c r="I312" t="n">
-        <v>1.4845</v>
+        <v>1.523</v>
       </c>
       <c r="J312" t="n">
-        <v>32.659</v>
+        <v>33.506</v>
       </c>
     </row>
     <row r="313">
@@ -14915,10 +14915,10 @@
         <v>1.44</v>
       </c>
       <c r="I313" t="n">
-        <v>1.034</v>
+        <v>1.037</v>
       </c>
       <c r="J313" t="n">
-        <v>22.748</v>
+        <v>22.814</v>
       </c>
     </row>
     <row r="314">
@@ -14955,10 +14955,10 @@
         <v>1.1</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3209</v>
+        <v>0.2855</v>
       </c>
       <c r="J314" t="n">
-        <v>7.0598</v>
+        <v>6.281</v>
       </c>
     </row>
     <row r="315">
@@ -14995,10 +14995,10 @@
         <v>0.79</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.636</v>
+        <v>-0.6011</v>
       </c>
       <c r="J315" t="n">
-        <v>-13.992</v>
+        <v>-13.2242</v>
       </c>
     </row>
     <row r="316">
@@ -15035,10 +15035,10 @@
         <v>0.55</v>
       </c>
       <c r="I316" t="n">
-        <v>-1.1391</v>
+        <v>-1.1583</v>
       </c>
       <c r="J316" t="n">
-        <v>-25.0602</v>
+        <v>-25.4826</v>
       </c>
     </row>
     <row r="317">
@@ -15075,10 +15075,10 @@
         <v>1.37</v>
       </c>
       <c r="I317" t="n">
-        <v>0.7295</v>
+        <v>0.6782</v>
       </c>
       <c r="J317" t="n">
-        <v>16.049</v>
+        <v>14.9204</v>
       </c>
     </row>
     <row r="318">
@@ -15115,10 +15115,10 @@
         <v>1.02</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0838</v>
+        <v>0.0598</v>
       </c>
       <c r="J318" t="n">
-        <v>1.8436</v>
+        <v>1.3156</v>
       </c>
     </row>
     <row r="319">
@@ -15155,10 +15155,10 @@
         <v>0.93</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1067</v>
+        <v>-0.0906</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.3474</v>
+        <v>-1.9932</v>
       </c>
     </row>
     <row r="320">
@@ -15195,10 +15195,10 @@
         <v>0.75</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2945</v>
+        <v>-0.2762</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.479</v>
+        <v>-6.0764</v>
       </c>
     </row>
     <row r="321">
@@ -15235,10 +15235,10 @@
         <v>0.59</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4401</v>
+        <v>-0.4334</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.6822</v>
+        <v>-9.534800000000001</v>
       </c>
     </row>
     <row r="322">
@@ -15275,10 +15275,10 @@
         <v>1.51</v>
       </c>
       <c r="I322" t="n">
-        <v>1.1375</v>
+        <v>1.1513</v>
       </c>
       <c r="J322" t="n">
-        <v>39.8125</v>
+        <v>40.2955</v>
       </c>
     </row>
     <row r="323">
@@ -15315,10 +15315,10 @@
         <v>1.17</v>
       </c>
       <c r="I323" t="n">
-        <v>0.4891</v>
+        <v>0.4503</v>
       </c>
       <c r="J323" t="n">
-        <v>17.1185</v>
+        <v>15.7605</v>
       </c>
     </row>
     <row r="324">
@@ -15355,10 +15355,10 @@
         <v>1.13</v>
       </c>
       <c r="I324" t="n">
-        <v>0.3956</v>
+        <v>0.3576</v>
       </c>
       <c r="J324" t="n">
-        <v>13.846</v>
+        <v>12.516</v>
       </c>
     </row>
     <row r="325">
@@ -15395,10 +15395,10 @@
         <v>1.09</v>
       </c>
       <c r="I325" t="n">
-        <v>0.2963</v>
+        <v>0.2614</v>
       </c>
       <c r="J325" t="n">
-        <v>10.3705</v>
+        <v>9.148999999999999</v>
       </c>
     </row>
     <row r="326">
@@ -15435,10 +15435,10 @@
         <v>0.7</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.8318</v>
+        <v>-0.8123</v>
       </c>
       <c r="J326" t="n">
-        <v>-29.113</v>
+        <v>-28.4305</v>
       </c>
     </row>
     <row r="327">
@@ -15475,10 +15475,10 @@
         <v>1.17</v>
       </c>
       <c r="I327" t="n">
-        <v>0.3893</v>
+        <v>0.3335</v>
       </c>
       <c r="J327" t="n">
-        <v>13.6255</v>
+        <v>11.6725</v>
       </c>
     </row>
     <row r="328">
@@ -15515,10 +15515,10 @@
         <v>1.1</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2587</v>
+        <v>0.2113</v>
       </c>
       <c r="J328" t="n">
-        <v>9.054500000000001</v>
+        <v>7.3955</v>
       </c>
     </row>
     <row r="329">
@@ -15555,10 +15555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.0805</v>
       </c>
       <c r="J329" t="n">
-        <v>-3.381</v>
+        <v>-2.8175</v>
       </c>
     </row>
     <row r="330">
@@ -15595,10 +15595,10 @@
         <v>0.88</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1665</v>
+        <v>-0.1465</v>
       </c>
       <c r="J330" t="n">
-        <v>-5.8275</v>
+        <v>-5.1275</v>
       </c>
     </row>
     <row r="331">
@@ -15635,10 +15635,10 @@
         <v>0.75</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.298</v>
+        <v>-0.2799</v>
       </c>
       <c r="J331" t="n">
-        <v>-10.43</v>
+        <v>-9.7965</v>
       </c>
     </row>
     <row r="332">
@@ -15675,10 +15675,10 @@
         <v>1.62</v>
       </c>
       <c r="I332" t="n">
-        <v>1.2281</v>
+        <v>1.245</v>
       </c>
       <c r="J332" t="n">
-        <v>22.1058</v>
+        <v>22.41</v>
       </c>
     </row>
     <row r="333">
@@ -15715,10 +15715,10 @@
         <v>1.45</v>
       </c>
       <c r="I333" t="n">
-        <v>1.0009</v>
+        <v>1.004</v>
       </c>
       <c r="J333" t="n">
-        <v>18.0162</v>
+        <v>18.072</v>
       </c>
     </row>
     <row r="334">
@@ -15755,10 +15755,10 @@
         <v>1.39</v>
       </c>
       <c r="I334" t="n">
-        <v>0.8995</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="J334" t="n">
-        <v>16.191</v>
+        <v>16.0308</v>
       </c>
     </row>
     <row r="335">
@@ -15795,10 +15795,10 @@
         <v>1.34</v>
       </c>
       <c r="I335" t="n">
-        <v>0.8069</v>
+        <v>0.792</v>
       </c>
       <c r="J335" t="n">
-        <v>14.5242</v>
+        <v>14.256</v>
       </c>
     </row>
     <row r="336">
@@ -15835,10 +15835,10 @@
         <v>1.14</v>
       </c>
       <c r="I336" t="n">
-        <v>0.3807</v>
+        <v>0.3488</v>
       </c>
       <c r="J336" t="n">
-        <v>6.8526</v>
+        <v>6.2784</v>
       </c>
     </row>
     <row r="337">
@@ -15875,10 +15875,10 @@
         <v>1.35</v>
       </c>
       <c r="I337" t="n">
-        <v>0.7968</v>
+        <v>0.7778</v>
       </c>
       <c r="J337" t="n">
-        <v>14.3424</v>
+        <v>14.0004</v>
       </c>
     </row>
     <row r="338">
@@ -15915,10 +15915,10 @@
         <v>0.66</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.3571</v>
+        <v>-0.3433</v>
       </c>
       <c r="J338" t="n">
-        <v>-6.4278</v>
+        <v>-6.1794</v>
       </c>
     </row>
     <row r="339">
@@ -15955,10 +15955,10 @@
         <v>0.59</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.4197</v>
+        <v>-0.4099</v>
       </c>
       <c r="J339" t="n">
-        <v>-7.5546</v>
+        <v>-7.3782</v>
       </c>
     </row>
     <row r="340">
@@ -15995,10 +15995,10 @@
         <v>0.57</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4374</v>
+        <v>-0.4292</v>
       </c>
       <c r="J340" t="n">
-        <v>-7.8732</v>
+        <v>-7.7256</v>
       </c>
     </row>
     <row r="341">
@@ -16035,10 +16035,10 @@
         <v>0.53</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4727</v>
+        <v>-0.468</v>
       </c>
       <c r="J341" t="n">
-        <v>-8.508599999999999</v>
+        <v>-8.423999999999999</v>
       </c>
     </row>
   </sheetData>
